--- a/benchmarks/resultsv8/dentist-plain.xlsx
+++ b/benchmarks/resultsv8/dentist-plain.xlsx
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="38">
   <si>
     <t>instances/size-1</t>
   </si>
@@ -107,6 +107,9 @@
   </si>
   <si>
     <t>SATISFIABLE</t>
+  </si>
+  <si>
+    <t>UNKNOWN</t>
   </si>
   <si>
     <t>rules</t>
@@ -522,7 +525,7 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -531,7 +534,7 @@
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
       <c r="P1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
@@ -540,7 +543,7 @@
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
       <c r="W1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X1" s="1"/>
       <c r="Y1" s="1"/>
@@ -549,7 +552,7 @@
       <c r="AB1" s="1"/>
       <c r="AC1" s="1"/>
       <c r="AD1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AE1" s="1"/>
       <c r="AF1" s="1"/>
@@ -558,7 +561,7 @@
       <c r="AI1" s="1"/>
       <c r="AJ1" s="1"/>
       <c r="AK1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AL1" s="1"/>
       <c r="AM1" s="1"/>
@@ -567,7 +570,7 @@
       <c r="AP1" s="1"/>
       <c r="AQ1" s="1"/>
       <c r="AR1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AS1" s="1"/>
       <c r="AT1" s="1"/>
@@ -575,7 +578,7 @@
       <c r="AV1" s="1"/>
       <c r="AW1" s="1"/>
       <c r="AX1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AY1" s="1"/>
       <c r="AZ1" s="1"/>
@@ -583,7 +586,7 @@
       <c r="BB1" s="1"/>
       <c r="BC1" s="1"/>
       <c r="BD1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="BE1" s="1"/>
       <c r="BF1" s="1"/>
@@ -603,16 +606,16 @@
         <v>21</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>19</v>
@@ -624,16 +627,16 @@
         <v>21</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P2" s="1" t="s">
         <v>19</v>
@@ -645,16 +648,16 @@
         <v>21</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="W2" s="1" t="s">
         <v>19</v>
@@ -666,16 +669,16 @@
         <v>21</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA2" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AB2" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AC2" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AD2" s="1" t="s">
         <v>19</v>
@@ -687,16 +690,16 @@
         <v>21</v>
       </c>
       <c r="AG2" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AH2" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI2" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AJ2" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AK2" s="1" t="s">
         <v>19</v>
@@ -708,16 +711,16 @@
         <v>21</v>
       </c>
       <c r="AN2" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO2" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AP2" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ2" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AR2" s="1" t="s">
         <v>19</v>
@@ -726,16 +729,16 @@
         <v>20</v>
       </c>
       <c r="AT2" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AU2" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AV2" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AW2" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AX2" s="1" t="s">
         <v>19</v>
@@ -744,16 +747,16 @@
         <v>20</v>
       </c>
       <c r="AZ2" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BA2" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BB2" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BC2" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BD2" s="1" t="s">
         <v>19</v>
@@ -762,16 +765,16 @@
         <v>20</v>
       </c>
       <c r="BF2" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BG2" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BH2" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BI2" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:61">
@@ -779,7 +782,7 @@
         <v>0</v>
       </c>
       <c r="B3" s="1">
-        <v>7.1</v>
+        <v>7.58</v>
       </c>
       <c r="C3" s="1">
         <v>0.03</v>
@@ -791,7 +794,7 @@
         <v>297383</v>
       </c>
       <c r="F3" s="1">
-        <v>1.213</v>
+        <v>1.099</v>
       </c>
       <c r="G3" s="1">
         <v>0.01</v>
@@ -800,7 +803,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="1">
-        <v>6.24</v>
+        <v>6.47</v>
       </c>
       <c r="J3" s="1">
         <v>0.01</v>
@@ -812,7 +815,7 @@
         <v>2337</v>
       </c>
       <c r="M3" s="1">
-        <v>0.162</v>
+        <v>0.15</v>
       </c>
       <c r="N3" s="1">
         <v>0</v>
@@ -821,7 +824,7 @@
         <v>0</v>
       </c>
       <c r="P3" s="1">
-        <v>5.85</v>
+        <v>6.92</v>
       </c>
       <c r="Q3" s="1">
         <v>0.01</v>
@@ -842,7 +845,7 @@
         <v>0</v>
       </c>
       <c r="W3" s="1">
-        <v>6.78</v>
+        <v>7.64</v>
       </c>
       <c r="X3" s="1">
         <v>0.29</v>
@@ -854,7 +857,7 @@
         <v>334458</v>
       </c>
       <c r="AA3" s="1">
-        <v>0.927</v>
+        <v>0.901</v>
       </c>
       <c r="AB3" s="1">
         <v>0.02</v>
@@ -863,7 +866,7 @@
         <v>0</v>
       </c>
       <c r="AD3" s="1">
-        <v>5.81</v>
+        <v>6.68</v>
       </c>
       <c r="AE3" s="1">
         <v>0.01</v>
@@ -875,7 +878,7 @@
         <v>2572</v>
       </c>
       <c r="AH3" s="1">
-        <v>0.168</v>
+        <v>0.228</v>
       </c>
       <c r="AI3" s="1">
         <v>0</v>
@@ -884,7 +887,7 @@
         <v>0</v>
       </c>
       <c r="AK3" s="1">
-        <v>5.69</v>
+        <v>6.62</v>
       </c>
       <c r="AL3" s="1">
         <v>0.01</v>
@@ -896,7 +899,7 @@
         <v>2572</v>
       </c>
       <c r="AO3" s="1">
-        <v>0.153</v>
+        <v>0.171</v>
       </c>
       <c r="AP3" s="1">
         <v>0</v>
@@ -984,66 +987,126 @@
       <c r="B4" s="1">
         <v>1200</v>
       </c>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
+      <c r="C4" s="1">
+        <v>0</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="1">
+        <v>0</v>
+      </c>
+      <c r="F4" s="1">
+        <v>175.53</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0</v>
+      </c>
       <c r="H4" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" s="1">
-        <v>1200</v>
-      </c>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-      <c r="N4" s="1"/>
+        <v>6.35</v>
+      </c>
+      <c r="J4" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L4" s="1">
+        <v>2337</v>
+      </c>
+      <c r="M4" s="1">
+        <v>0.157</v>
+      </c>
+      <c r="N4" s="1">
+        <v>0</v>
+      </c>
       <c r="O4" s="1">
         <v>0</v>
       </c>
       <c r="P4" s="1">
-        <v>1200</v>
-      </c>
-      <c r="Q4" s="1"/>
-      <c r="R4" s="1"/>
-      <c r="S4" s="1"/>
-      <c r="T4" s="1"/>
-      <c r="U4" s="1"/>
+        <v>6.99</v>
+      </c>
+      <c r="Q4" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="R4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="S4" s="1">
+        <v>2337</v>
+      </c>
+      <c r="T4" s="1">
+        <v>0.19</v>
+      </c>
+      <c r="U4" s="1">
+        <v>0</v>
+      </c>
       <c r="V4" s="1">
         <v>0</v>
       </c>
       <c r="W4" s="1">
         <v>1200</v>
       </c>
-      <c r="X4" s="1"/>
-      <c r="Y4" s="1"/>
-      <c r="Z4" s="1"/>
-      <c r="AA4" s="1"/>
-      <c r="AB4" s="1"/>
+      <c r="X4" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="1">
+        <v>167.461</v>
+      </c>
+      <c r="AB4" s="1">
+        <v>0</v>
+      </c>
       <c r="AC4" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD4" s="1">
-        <v>1200</v>
-      </c>
-      <c r="AE4" s="1"/>
-      <c r="AF4" s="1"/>
-      <c r="AG4" s="1"/>
-      <c r="AH4" s="1"/>
-      <c r="AI4" s="1"/>
+        <v>6.8</v>
+      </c>
+      <c r="AE4" s="1">
+        <v>0.02</v>
+      </c>
+      <c r="AF4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="AG4" s="1">
+        <v>2572</v>
+      </c>
+      <c r="AH4" s="1">
+        <v>0.208</v>
+      </c>
+      <c r="AI4" s="1">
+        <v>0</v>
+      </c>
       <c r="AJ4" s="1">
         <v>0</v>
       </c>
       <c r="AK4" s="1">
-        <v>1200</v>
-      </c>
-      <c r="AL4" s="1"/>
-      <c r="AM4" s="1"/>
-      <c r="AN4" s="1"/>
-      <c r="AO4" s="1"/>
-      <c r="AP4" s="1"/>
+        <v>8.02</v>
+      </c>
+      <c r="AL4" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="AM4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="AN4" s="1">
+        <v>2572</v>
+      </c>
+      <c r="AO4" s="1">
+        <v>0.241</v>
+      </c>
+      <c r="AP4" s="1">
+        <v>0</v>
+      </c>
       <c r="AQ4" s="1">
         <v>0</v>
       </c>
@@ -1051,10 +1114,22 @@
         <f>MIN($B4,$I4,$P4,$W4,$AD4,$AK4)</f>
         <v>0</v>
       </c>
-      <c r="AS4" s="1"/>
-      <c r="AT4" s="1"/>
-      <c r="AU4" s="1"/>
-      <c r="AV4" s="1"/>
+      <c r="AS4" s="1">
+        <f>MIN($C4,$J4,$Q4,$X4,$AE4,$AL4)</f>
+        <v>0</v>
+      </c>
+      <c r="AT4" s="1">
+        <f>MIN($E4,$L4,$S4,$Z4,$AG4,$AN4)</f>
+        <v>0</v>
+      </c>
+      <c r="AU4" s="1">
+        <f>MIN($F4,$M4,$T4,$AA4,$AH4,$AO4)</f>
+        <v>0</v>
+      </c>
+      <c r="AV4" s="1">
+        <f>MIN($G4,$N4,$U4,$AB4,$AI4,$AP4)</f>
+        <v>0</v>
+      </c>
       <c r="AW4" s="1">
         <f>MIN($H4,$O4,$V4,$AC4,$AJ4,$AQ4)</f>
         <v>0</v>
@@ -1063,10 +1138,22 @@
         <f>MEDIAN($B4,$I4,$P4,$W4,$AD4,$AK4)</f>
         <v>0</v>
       </c>
-      <c r="AY4" s="1"/>
-      <c r="AZ4" s="1"/>
-      <c r="BA4" s="1"/>
-      <c r="BB4" s="1"/>
+      <c r="AY4" s="1">
+        <f>MEDIAN($C4,$J4,$Q4,$X4,$AE4,$AL4)</f>
+        <v>0</v>
+      </c>
+      <c r="AZ4" s="1">
+        <f>MEDIAN($E4,$L4,$S4,$Z4,$AG4,$AN4)</f>
+        <v>0</v>
+      </c>
+      <c r="BA4" s="1">
+        <f>MEDIAN($F4,$M4,$T4,$AA4,$AH4,$AO4)</f>
+        <v>0</v>
+      </c>
+      <c r="BB4" s="1">
+        <f>MEDIAN($G4,$N4,$U4,$AB4,$AI4,$AP4)</f>
+        <v>0</v>
+      </c>
       <c r="BC4" s="1">
         <f>MEDIAN($H4,$O4,$V4,$AC4,$AJ4,$AQ4)</f>
         <v>0</v>
@@ -1075,10 +1162,22 @@
         <f>MAX($B4,$I4,$P4,$W4,$AD4,$AK4)</f>
         <v>0</v>
       </c>
-      <c r="BE4" s="1"/>
-      <c r="BF4" s="1"/>
-      <c r="BG4" s="1"/>
-      <c r="BH4" s="1"/>
+      <c r="BE4" s="1">
+        <f>MAX($C4,$J4,$Q4,$X4,$AE4,$AL4)</f>
+        <v>0</v>
+      </c>
+      <c r="BF4" s="1">
+        <f>MAX($E4,$L4,$S4,$Z4,$AG4,$AN4)</f>
+        <v>0</v>
+      </c>
+      <c r="BG4" s="1">
+        <f>MAX($F4,$M4,$T4,$AA4,$AH4,$AO4)</f>
+        <v>0</v>
+      </c>
+      <c r="BH4" s="1">
+        <f>MAX($G4,$N4,$U4,$AB4,$AI4,$AP4)</f>
+        <v>0</v>
+      </c>
       <c r="BI4" s="1">
         <f>MAX($H4,$O4,$V4,$AC4,$AJ4,$AQ4)</f>
         <v>0</v>
@@ -1089,68 +1188,128 @@
         <v>2</v>
       </c>
       <c r="B5" s="1">
-        <v>1200</v>
-      </c>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
+        <v>12.91</v>
+      </c>
+      <c r="C5" s="1">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="1">
+        <v>1197443</v>
+      </c>
+      <c r="F5" s="1">
+        <v>5.437</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0.09</v>
+      </c>
       <c r="H5" s="1">
         <v>0</v>
       </c>
       <c r="I5" s="1">
-        <v>1200</v>
-      </c>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="1"/>
+        <v>6.77</v>
+      </c>
+      <c r="J5" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L5" s="1">
+        <v>2337</v>
+      </c>
+      <c r="M5" s="1">
+        <v>0.151</v>
+      </c>
+      <c r="N5" s="1">
+        <v>0</v>
+      </c>
       <c r="O5" s="1">
         <v>0</v>
       </c>
       <c r="P5" s="1">
-        <v>1200</v>
-      </c>
-      <c r="Q5" s="1"/>
-      <c r="R5" s="1"/>
-      <c r="S5" s="1"/>
-      <c r="T5" s="1"/>
-      <c r="U5" s="1"/>
+        <v>6.42</v>
+      </c>
+      <c r="Q5" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="R5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="S5" s="1">
+        <v>2337</v>
+      </c>
+      <c r="T5" s="1">
+        <v>0.141</v>
+      </c>
+      <c r="U5" s="1">
+        <v>0</v>
+      </c>
       <c r="V5" s="1">
         <v>0</v>
       </c>
       <c r="W5" s="1">
-        <v>1200</v>
-      </c>
-      <c r="X5" s="1"/>
-      <c r="Y5" s="1"/>
-      <c r="Z5" s="1"/>
-      <c r="AA5" s="1"/>
-      <c r="AB5" s="1"/>
+        <v>25.56</v>
+      </c>
+      <c r="X5" s="1">
+        <v>16.62</v>
+      </c>
+      <c r="Y5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z5" s="1">
+        <v>1344008</v>
+      </c>
+      <c r="AA5" s="1">
+        <v>19.264</v>
+      </c>
+      <c r="AB5" s="1">
+        <v>0.19</v>
+      </c>
       <c r="AC5" s="1">
         <v>0</v>
       </c>
       <c r="AD5" s="1">
-        <v>1200</v>
-      </c>
-      <c r="AE5" s="1"/>
-      <c r="AF5" s="1"/>
-      <c r="AG5" s="1"/>
-      <c r="AH5" s="1"/>
-      <c r="AI5" s="1"/>
+        <v>6.96</v>
+      </c>
+      <c r="AE5" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="AF5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="AG5" s="1">
+        <v>2572</v>
+      </c>
+      <c r="AH5" s="1">
+        <v>0.166</v>
+      </c>
+      <c r="AI5" s="1">
+        <v>0</v>
+      </c>
       <c r="AJ5" s="1">
         <v>0</v>
       </c>
       <c r="AK5" s="1">
-        <v>1200</v>
-      </c>
-      <c r="AL5" s="1"/>
-      <c r="AM5" s="1"/>
-      <c r="AN5" s="1"/>
-      <c r="AO5" s="1"/>
-      <c r="AP5" s="1"/>
+        <v>6.55</v>
+      </c>
+      <c r="AL5" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="AM5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="AN5" s="1">
+        <v>2572</v>
+      </c>
+      <c r="AO5" s="1">
+        <v>0.224</v>
+      </c>
+      <c r="AP5" s="1">
+        <v>0</v>
+      </c>
       <c r="AQ5" s="1">
         <v>0</v>
       </c>
@@ -1158,10 +1317,22 @@
         <f>MIN($B5,$I5,$P5,$W5,$AD5,$AK5)</f>
         <v>0</v>
       </c>
-      <c r="AS5" s="1"/>
-      <c r="AT5" s="1"/>
-      <c r="AU5" s="1"/>
-      <c r="AV5" s="1"/>
+      <c r="AS5" s="1">
+        <f>MIN($C5,$J5,$Q5,$X5,$AE5,$AL5)</f>
+        <v>0</v>
+      </c>
+      <c r="AT5" s="1">
+        <f>MIN($E5,$L5,$S5,$Z5,$AG5,$AN5)</f>
+        <v>0</v>
+      </c>
+      <c r="AU5" s="1">
+        <f>MIN($F5,$M5,$T5,$AA5,$AH5,$AO5)</f>
+        <v>0</v>
+      </c>
+      <c r="AV5" s="1">
+        <f>MIN($G5,$N5,$U5,$AB5,$AI5,$AP5)</f>
+        <v>0</v>
+      </c>
       <c r="AW5" s="1">
         <f>MIN($H5,$O5,$V5,$AC5,$AJ5,$AQ5)</f>
         <v>0</v>
@@ -1170,10 +1341,22 @@
         <f>MEDIAN($B5,$I5,$P5,$W5,$AD5,$AK5)</f>
         <v>0</v>
       </c>
-      <c r="AY5" s="1"/>
-      <c r="AZ5" s="1"/>
-      <c r="BA5" s="1"/>
-      <c r="BB5" s="1"/>
+      <c r="AY5" s="1">
+        <f>MEDIAN($C5,$J5,$Q5,$X5,$AE5,$AL5)</f>
+        <v>0</v>
+      </c>
+      <c r="AZ5" s="1">
+        <f>MEDIAN($E5,$L5,$S5,$Z5,$AG5,$AN5)</f>
+        <v>0</v>
+      </c>
+      <c r="BA5" s="1">
+        <f>MEDIAN($F5,$M5,$T5,$AA5,$AH5,$AO5)</f>
+        <v>0</v>
+      </c>
+      <c r="BB5" s="1">
+        <f>MEDIAN($G5,$N5,$U5,$AB5,$AI5,$AP5)</f>
+        <v>0</v>
+      </c>
       <c r="BC5" s="1">
         <f>MEDIAN($H5,$O5,$V5,$AC5,$AJ5,$AQ5)</f>
         <v>0</v>
@@ -1182,10 +1365,22 @@
         <f>MAX($B5,$I5,$P5,$W5,$AD5,$AK5)</f>
         <v>0</v>
       </c>
-      <c r="BE5" s="1"/>
-      <c r="BF5" s="1"/>
-      <c r="BG5" s="1"/>
-      <c r="BH5" s="1"/>
+      <c r="BE5" s="1">
+        <f>MAX($C5,$J5,$Q5,$X5,$AE5,$AL5)</f>
+        <v>0</v>
+      </c>
+      <c r="BF5" s="1">
+        <f>MAX($E5,$L5,$S5,$Z5,$AG5,$AN5)</f>
+        <v>0</v>
+      </c>
+      <c r="BG5" s="1">
+        <f>MAX($F5,$M5,$T5,$AA5,$AH5,$AO5)</f>
+        <v>0</v>
+      </c>
+      <c r="BH5" s="1">
+        <f>MAX($G5,$N5,$U5,$AB5,$AI5,$AP5)</f>
+        <v>0</v>
+      </c>
       <c r="BI5" s="1">
         <f>MAX($H5,$O5,$V5,$AC5,$AJ5,$AQ5)</f>
         <v>0</v>
@@ -1196,68 +1391,128 @@
         <v>3</v>
       </c>
       <c r="B6" s="1">
-        <v>1200</v>
-      </c>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
+        <v>25.76</v>
+      </c>
+      <c r="C6" s="1">
+        <v>7.58</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="1">
+        <v>2702503</v>
+      </c>
+      <c r="F6" s="1">
+        <v>19.074</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0.38</v>
+      </c>
       <c r="H6" s="1">
         <v>0</v>
       </c>
       <c r="I6" s="1">
-        <v>1200</v>
-      </c>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="1"/>
+        <v>6.6</v>
+      </c>
+      <c r="J6" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L6" s="1">
+        <v>2337</v>
+      </c>
+      <c r="M6" s="1">
+        <v>0.159</v>
+      </c>
+      <c r="N6" s="1">
+        <v>0</v>
+      </c>
       <c r="O6" s="1">
         <v>0</v>
       </c>
       <c r="P6" s="1">
-        <v>1200</v>
-      </c>
-      <c r="Q6" s="1"/>
-      <c r="R6" s="1"/>
-      <c r="S6" s="1"/>
-      <c r="T6" s="1"/>
-      <c r="U6" s="1"/>
+        <v>8.27</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="R6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="S6" s="1">
+        <v>2337</v>
+      </c>
+      <c r="T6" s="1">
+        <v>0.155</v>
+      </c>
+      <c r="U6" s="1">
+        <v>0</v>
+      </c>
       <c r="V6" s="1">
         <v>0</v>
       </c>
       <c r="W6" s="1">
-        <v>1200</v>
-      </c>
-      <c r="X6" s="1"/>
-      <c r="Y6" s="1"/>
-      <c r="Z6" s="1"/>
-      <c r="AA6" s="1"/>
-      <c r="AB6" s="1"/>
+        <v>65.40000000000001</v>
+      </c>
+      <c r="X6" s="1">
+        <v>51.68</v>
+      </c>
+      <c r="Y6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z6" s="1">
+        <v>3031158</v>
+      </c>
+      <c r="AA6" s="1">
+        <v>58.669</v>
+      </c>
+      <c r="AB6" s="1">
+        <v>0.66</v>
+      </c>
       <c r="AC6" s="1">
         <v>0</v>
       </c>
       <c r="AD6" s="1">
-        <v>1200</v>
-      </c>
-      <c r="AE6" s="1"/>
-      <c r="AF6" s="1"/>
-      <c r="AG6" s="1"/>
-      <c r="AH6" s="1"/>
-      <c r="AI6" s="1"/>
+        <v>6.34</v>
+      </c>
+      <c r="AE6" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="AF6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="AG6" s="1">
+        <v>2572</v>
+      </c>
+      <c r="AH6" s="1">
+        <v>0.181</v>
+      </c>
+      <c r="AI6" s="1">
+        <v>0</v>
+      </c>
       <c r="AJ6" s="1">
         <v>0</v>
       </c>
       <c r="AK6" s="1">
-        <v>1200</v>
-      </c>
-      <c r="AL6" s="1"/>
-      <c r="AM6" s="1"/>
-      <c r="AN6" s="1"/>
-      <c r="AO6" s="1"/>
-      <c r="AP6" s="1"/>
+        <v>8.01</v>
+      </c>
+      <c r="AL6" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="AM6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="AN6" s="1">
+        <v>2572</v>
+      </c>
+      <c r="AO6" s="1">
+        <v>0.245</v>
+      </c>
+      <c r="AP6" s="1">
+        <v>0</v>
+      </c>
       <c r="AQ6" s="1">
         <v>0</v>
       </c>
@@ -1265,10 +1520,22 @@
         <f>MIN($B6,$I6,$P6,$W6,$AD6,$AK6)</f>
         <v>0</v>
       </c>
-      <c r="AS6" s="1"/>
-      <c r="AT6" s="1"/>
-      <c r="AU6" s="1"/>
-      <c r="AV6" s="1"/>
+      <c r="AS6" s="1">
+        <f>MIN($C6,$J6,$Q6,$X6,$AE6,$AL6)</f>
+        <v>0</v>
+      </c>
+      <c r="AT6" s="1">
+        <f>MIN($E6,$L6,$S6,$Z6,$AG6,$AN6)</f>
+        <v>0</v>
+      </c>
+      <c r="AU6" s="1">
+        <f>MIN($F6,$M6,$T6,$AA6,$AH6,$AO6)</f>
+        <v>0</v>
+      </c>
+      <c r="AV6" s="1">
+        <f>MIN($G6,$N6,$U6,$AB6,$AI6,$AP6)</f>
+        <v>0</v>
+      </c>
       <c r="AW6" s="1">
         <f>MIN($H6,$O6,$V6,$AC6,$AJ6,$AQ6)</f>
         <v>0</v>
@@ -1277,10 +1544,22 @@
         <f>MEDIAN($B6,$I6,$P6,$W6,$AD6,$AK6)</f>
         <v>0</v>
       </c>
-      <c r="AY6" s="1"/>
-      <c r="AZ6" s="1"/>
-      <c r="BA6" s="1"/>
-      <c r="BB6" s="1"/>
+      <c r="AY6" s="1">
+        <f>MEDIAN($C6,$J6,$Q6,$X6,$AE6,$AL6)</f>
+        <v>0</v>
+      </c>
+      <c r="AZ6" s="1">
+        <f>MEDIAN($E6,$L6,$S6,$Z6,$AG6,$AN6)</f>
+        <v>0</v>
+      </c>
+      <c r="BA6" s="1">
+        <f>MEDIAN($F6,$M6,$T6,$AA6,$AH6,$AO6)</f>
+        <v>0</v>
+      </c>
+      <c r="BB6" s="1">
+        <f>MEDIAN($G6,$N6,$U6,$AB6,$AI6,$AP6)</f>
+        <v>0</v>
+      </c>
       <c r="BC6" s="1">
         <f>MEDIAN($H6,$O6,$V6,$AC6,$AJ6,$AQ6)</f>
         <v>0</v>
@@ -1289,10 +1568,22 @@
         <f>MAX($B6,$I6,$P6,$W6,$AD6,$AK6)</f>
         <v>0</v>
       </c>
-      <c r="BE6" s="1"/>
-      <c r="BF6" s="1"/>
-      <c r="BG6" s="1"/>
-      <c r="BH6" s="1"/>
+      <c r="BE6" s="1">
+        <f>MAX($C6,$J6,$Q6,$X6,$AE6,$AL6)</f>
+        <v>0</v>
+      </c>
+      <c r="BF6" s="1">
+        <f>MAX($E6,$L6,$S6,$Z6,$AG6,$AN6)</f>
+        <v>0</v>
+      </c>
+      <c r="BG6" s="1">
+        <f>MAX($F6,$M6,$T6,$AA6,$AH6,$AO6)</f>
+        <v>0</v>
+      </c>
+      <c r="BH6" s="1">
+        <f>MAX($G6,$N6,$U6,$AB6,$AI6,$AP6)</f>
+        <v>0</v>
+      </c>
       <c r="BI6" s="1">
         <f>MAX($H6,$O6,$V6,$AC6,$AJ6,$AQ6)</f>
         <v>0</v>
@@ -1303,68 +1594,128 @@
         <v>4</v>
       </c>
       <c r="B7" s="1">
-        <v>1200</v>
-      </c>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
+        <v>29.86</v>
+      </c>
+      <c r="C7" s="1">
+        <v>1.65</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="1">
+        <v>4812563</v>
+      </c>
+      <c r="F7" s="1">
+        <v>23.26</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0.95</v>
+      </c>
       <c r="H7" s="1">
         <v>0</v>
       </c>
       <c r="I7" s="1">
-        <v>1200</v>
-      </c>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
-      <c r="N7" s="1"/>
+        <v>7.43</v>
+      </c>
+      <c r="J7" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L7" s="1">
+        <v>2337</v>
+      </c>
+      <c r="M7" s="1">
+        <v>0.186</v>
+      </c>
+      <c r="N7" s="1">
+        <v>0</v>
+      </c>
       <c r="O7" s="1">
         <v>0</v>
       </c>
       <c r="P7" s="1">
-        <v>1200</v>
-      </c>
-      <c r="Q7" s="1"/>
-      <c r="R7" s="1"/>
-      <c r="S7" s="1"/>
-      <c r="T7" s="1"/>
-      <c r="U7" s="1"/>
+        <v>8.42</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="R7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="S7" s="1">
+        <v>2337</v>
+      </c>
+      <c r="T7" s="1">
+        <v>0.152</v>
+      </c>
+      <c r="U7" s="1">
+        <v>0</v>
+      </c>
       <c r="V7" s="1">
         <v>0</v>
       </c>
       <c r="W7" s="1">
-        <v>1200</v>
-      </c>
-      <c r="X7" s="1"/>
-      <c r="Y7" s="1"/>
-      <c r="Z7" s="1"/>
-      <c r="AA7" s="1"/>
-      <c r="AB7" s="1"/>
+        <v>64.47</v>
+      </c>
+      <c r="X7" s="1">
+        <v>36.37</v>
+      </c>
+      <c r="Y7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z7" s="1">
+        <v>5395908</v>
+      </c>
+      <c r="AA7" s="1">
+        <v>52.168</v>
+      </c>
+      <c r="AB7" s="1">
+        <v>1.79</v>
+      </c>
       <c r="AC7" s="1">
         <v>0</v>
       </c>
       <c r="AD7" s="1">
-        <v>1200</v>
-      </c>
-      <c r="AE7" s="1"/>
-      <c r="AF7" s="1"/>
-      <c r="AG7" s="1"/>
-      <c r="AH7" s="1"/>
-      <c r="AI7" s="1"/>
+        <v>6.41</v>
+      </c>
+      <c r="AE7" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="AF7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="AG7" s="1">
+        <v>2572</v>
+      </c>
+      <c r="AH7" s="1">
+        <v>0.202</v>
+      </c>
+      <c r="AI7" s="1">
+        <v>0</v>
+      </c>
       <c r="AJ7" s="1">
         <v>0</v>
       </c>
       <c r="AK7" s="1">
-        <v>1200</v>
-      </c>
-      <c r="AL7" s="1"/>
-      <c r="AM7" s="1"/>
-      <c r="AN7" s="1"/>
-      <c r="AO7" s="1"/>
-      <c r="AP7" s="1"/>
+        <v>6.54</v>
+      </c>
+      <c r="AL7" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="AM7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="AN7" s="1">
+        <v>2572</v>
+      </c>
+      <c r="AO7" s="1">
+        <v>0.197</v>
+      </c>
+      <c r="AP7" s="1">
+        <v>0</v>
+      </c>
       <c r="AQ7" s="1">
         <v>0</v>
       </c>
@@ -1372,10 +1723,22 @@
         <f>MIN($B7,$I7,$P7,$W7,$AD7,$AK7)</f>
         <v>0</v>
       </c>
-      <c r="AS7" s="1"/>
-      <c r="AT7" s="1"/>
-      <c r="AU7" s="1"/>
-      <c r="AV7" s="1"/>
+      <c r="AS7" s="1">
+        <f>MIN($C7,$J7,$Q7,$X7,$AE7,$AL7)</f>
+        <v>0</v>
+      </c>
+      <c r="AT7" s="1">
+        <f>MIN($E7,$L7,$S7,$Z7,$AG7,$AN7)</f>
+        <v>0</v>
+      </c>
+      <c r="AU7" s="1">
+        <f>MIN($F7,$M7,$T7,$AA7,$AH7,$AO7)</f>
+        <v>0</v>
+      </c>
+      <c r="AV7" s="1">
+        <f>MIN($G7,$N7,$U7,$AB7,$AI7,$AP7)</f>
+        <v>0</v>
+      </c>
       <c r="AW7" s="1">
         <f>MIN($H7,$O7,$V7,$AC7,$AJ7,$AQ7)</f>
         <v>0</v>
@@ -1384,10 +1747,22 @@
         <f>MEDIAN($B7,$I7,$P7,$W7,$AD7,$AK7)</f>
         <v>0</v>
       </c>
-      <c r="AY7" s="1"/>
-      <c r="AZ7" s="1"/>
-      <c r="BA7" s="1"/>
-      <c r="BB7" s="1"/>
+      <c r="AY7" s="1">
+        <f>MEDIAN($C7,$J7,$Q7,$X7,$AE7,$AL7)</f>
+        <v>0</v>
+      </c>
+      <c r="AZ7" s="1">
+        <f>MEDIAN($E7,$L7,$S7,$Z7,$AG7,$AN7)</f>
+        <v>0</v>
+      </c>
+      <c r="BA7" s="1">
+        <f>MEDIAN($F7,$M7,$T7,$AA7,$AH7,$AO7)</f>
+        <v>0</v>
+      </c>
+      <c r="BB7" s="1">
+        <f>MEDIAN($G7,$N7,$U7,$AB7,$AI7,$AP7)</f>
+        <v>0</v>
+      </c>
       <c r="BC7" s="1">
         <f>MEDIAN($H7,$O7,$V7,$AC7,$AJ7,$AQ7)</f>
         <v>0</v>
@@ -1396,10 +1771,22 @@
         <f>MAX($B7,$I7,$P7,$W7,$AD7,$AK7)</f>
         <v>0</v>
       </c>
-      <c r="BE7" s="1"/>
-      <c r="BF7" s="1"/>
-      <c r="BG7" s="1"/>
-      <c r="BH7" s="1"/>
+      <c r="BE7" s="1">
+        <f>MAX($C7,$J7,$Q7,$X7,$AE7,$AL7)</f>
+        <v>0</v>
+      </c>
+      <c r="BF7" s="1">
+        <f>MAX($E7,$L7,$S7,$Z7,$AG7,$AN7)</f>
+        <v>0</v>
+      </c>
+      <c r="BG7" s="1">
+        <f>MAX($F7,$M7,$T7,$AA7,$AH7,$AO7)</f>
+        <v>0</v>
+      </c>
+      <c r="BH7" s="1">
+        <f>MAX($G7,$N7,$U7,$AB7,$AI7,$AP7)</f>
+        <v>0</v>
+      </c>
       <c r="BI7" s="1">
         <f>MAX($H7,$O7,$V7,$AC7,$AJ7,$AQ7)</f>
         <v>0</v>
@@ -1410,68 +1797,128 @@
         <v>5</v>
       </c>
       <c r="B8" s="1">
-        <v>1200</v>
-      </c>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
+        <v>62.09</v>
+      </c>
+      <c r="C8" s="1">
+        <v>18.73</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="1">
+        <v>7527623</v>
+      </c>
+      <c r="F8" s="1">
+        <v>54.164</v>
+      </c>
+      <c r="G8" s="1">
+        <v>2.31</v>
+      </c>
       <c r="H8" s="1">
         <v>0</v>
       </c>
       <c r="I8" s="1">
-        <v>1200</v>
-      </c>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
+        <v>8.34</v>
+      </c>
+      <c r="J8" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L8" s="1">
+        <v>2337</v>
+      </c>
+      <c r="M8" s="1">
+        <v>0.149</v>
+      </c>
+      <c r="N8" s="1">
+        <v>0</v>
+      </c>
       <c r="O8" s="1">
         <v>0</v>
       </c>
       <c r="P8" s="1">
-        <v>1200</v>
-      </c>
-      <c r="Q8" s="1"/>
-      <c r="R8" s="1"/>
-      <c r="S8" s="1"/>
-      <c r="T8" s="1"/>
-      <c r="U8" s="1"/>
+        <v>6.53</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="R8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="S8" s="1">
+        <v>2337</v>
+      </c>
+      <c r="T8" s="1">
+        <v>0.16</v>
+      </c>
+      <c r="U8" s="1">
+        <v>0</v>
+      </c>
       <c r="V8" s="1">
         <v>0</v>
       </c>
       <c r="W8" s="1">
-        <v>1200</v>
-      </c>
-      <c r="X8" s="1"/>
-      <c r="Y8" s="1"/>
-      <c r="Z8" s="1"/>
-      <c r="AA8" s="1"/>
-      <c r="AB8" s="1"/>
+        <v>41.13</v>
+      </c>
+      <c r="X8" s="1">
+        <v>7.8</v>
+      </c>
+      <c r="Y8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z8" s="1">
+        <v>8438258</v>
+      </c>
+      <c r="AA8" s="1">
+        <v>34.346</v>
+      </c>
+      <c r="AB8" s="1">
+        <v>2.69</v>
+      </c>
       <c r="AC8" s="1">
         <v>0</v>
       </c>
       <c r="AD8" s="1">
-        <v>1200</v>
-      </c>
-      <c r="AE8" s="1"/>
-      <c r="AF8" s="1"/>
-      <c r="AG8" s="1"/>
-      <c r="AH8" s="1"/>
-      <c r="AI8" s="1"/>
+        <v>6.56</v>
+      </c>
+      <c r="AE8" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="AF8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="AG8" s="1">
+        <v>2572</v>
+      </c>
+      <c r="AH8" s="1">
+        <v>0.176</v>
+      </c>
+      <c r="AI8" s="1">
+        <v>0</v>
+      </c>
       <c r="AJ8" s="1">
         <v>0</v>
       </c>
       <c r="AK8" s="1">
-        <v>1200</v>
-      </c>
-      <c r="AL8" s="1"/>
-      <c r="AM8" s="1"/>
-      <c r="AN8" s="1"/>
-      <c r="AO8" s="1"/>
-      <c r="AP8" s="1"/>
+        <v>7.19</v>
+      </c>
+      <c r="AL8" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="AM8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="AN8" s="1">
+        <v>2572</v>
+      </c>
+      <c r="AO8" s="1">
+        <v>0.236</v>
+      </c>
+      <c r="AP8" s="1">
+        <v>0</v>
+      </c>
       <c r="AQ8" s="1">
         <v>0</v>
       </c>
@@ -1479,10 +1926,22 @@
         <f>MIN($B8,$I8,$P8,$W8,$AD8,$AK8)</f>
         <v>0</v>
       </c>
-      <c r="AS8" s="1"/>
-      <c r="AT8" s="1"/>
-      <c r="AU8" s="1"/>
-      <c r="AV8" s="1"/>
+      <c r="AS8" s="1">
+        <f>MIN($C8,$J8,$Q8,$X8,$AE8,$AL8)</f>
+        <v>0</v>
+      </c>
+      <c r="AT8" s="1">
+        <f>MIN($E8,$L8,$S8,$Z8,$AG8,$AN8)</f>
+        <v>0</v>
+      </c>
+      <c r="AU8" s="1">
+        <f>MIN($F8,$M8,$T8,$AA8,$AH8,$AO8)</f>
+        <v>0</v>
+      </c>
+      <c r="AV8" s="1">
+        <f>MIN($G8,$N8,$U8,$AB8,$AI8,$AP8)</f>
+        <v>0</v>
+      </c>
       <c r="AW8" s="1">
         <f>MIN($H8,$O8,$V8,$AC8,$AJ8,$AQ8)</f>
         <v>0</v>
@@ -1491,10 +1950,22 @@
         <f>MEDIAN($B8,$I8,$P8,$W8,$AD8,$AK8)</f>
         <v>0</v>
       </c>
-      <c r="AY8" s="1"/>
-      <c r="AZ8" s="1"/>
-      <c r="BA8" s="1"/>
-      <c r="BB8" s="1"/>
+      <c r="AY8" s="1">
+        <f>MEDIAN($C8,$J8,$Q8,$X8,$AE8,$AL8)</f>
+        <v>0</v>
+      </c>
+      <c r="AZ8" s="1">
+        <f>MEDIAN($E8,$L8,$S8,$Z8,$AG8,$AN8)</f>
+        <v>0</v>
+      </c>
+      <c r="BA8" s="1">
+        <f>MEDIAN($F8,$M8,$T8,$AA8,$AH8,$AO8)</f>
+        <v>0</v>
+      </c>
+      <c r="BB8" s="1">
+        <f>MEDIAN($G8,$N8,$U8,$AB8,$AI8,$AP8)</f>
+        <v>0</v>
+      </c>
       <c r="BC8" s="1">
         <f>MEDIAN($H8,$O8,$V8,$AC8,$AJ8,$AQ8)</f>
         <v>0</v>
@@ -1503,10 +1974,22 @@
         <f>MAX($B8,$I8,$P8,$W8,$AD8,$AK8)</f>
         <v>0</v>
       </c>
-      <c r="BE8" s="1"/>
-      <c r="BF8" s="1"/>
-      <c r="BG8" s="1"/>
-      <c r="BH8" s="1"/>
+      <c r="BE8" s="1">
+        <f>MAX($C8,$J8,$Q8,$X8,$AE8,$AL8)</f>
+        <v>0</v>
+      </c>
+      <c r="BF8" s="1">
+        <f>MAX($E8,$L8,$S8,$Z8,$AG8,$AN8)</f>
+        <v>0</v>
+      </c>
+      <c r="BG8" s="1">
+        <f>MAX($F8,$M8,$T8,$AA8,$AH8,$AO8)</f>
+        <v>0</v>
+      </c>
+      <c r="BH8" s="1">
+        <f>MAX($G8,$N8,$U8,$AB8,$AI8,$AP8)</f>
+        <v>0</v>
+      </c>
       <c r="BI8" s="1">
         <f>MAX($H8,$O8,$V8,$AC8,$AJ8,$AQ8)</f>
         <v>0</v>
@@ -1517,68 +2000,128 @@
         <v>6</v>
       </c>
       <c r="B9" s="1">
-        <v>1200</v>
-      </c>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
+        <v>72.83</v>
+      </c>
+      <c r="C9" s="1">
+        <v>9.369999999999999</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="1">
+        <v>10847683</v>
+      </c>
+      <c r="F9" s="1">
+        <v>66.026</v>
+      </c>
+      <c r="G9" s="1">
+        <v>3.64</v>
+      </c>
       <c r="H9" s="1">
         <v>0</v>
       </c>
       <c r="I9" s="1">
-        <v>1200</v>
-      </c>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
-      <c r="N9" s="1"/>
+        <v>7.4</v>
+      </c>
+      <c r="J9" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L9" s="1">
+        <v>2337</v>
+      </c>
+      <c r="M9" s="1">
+        <v>0.153</v>
+      </c>
+      <c r="N9" s="1">
+        <v>0</v>
+      </c>
       <c r="O9" s="1">
         <v>0</v>
       </c>
       <c r="P9" s="1">
-        <v>1200</v>
-      </c>
-      <c r="Q9" s="1"/>
-      <c r="R9" s="1"/>
-      <c r="S9" s="1"/>
-      <c r="T9" s="1"/>
-      <c r="U9" s="1"/>
+        <v>6.42</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="R9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="S9" s="1">
+        <v>2337</v>
+      </c>
+      <c r="T9" s="1">
+        <v>0.163</v>
+      </c>
+      <c r="U9" s="1">
+        <v>0</v>
+      </c>
       <c r="V9" s="1">
         <v>0</v>
       </c>
       <c r="W9" s="1">
-        <v>1200</v>
-      </c>
-      <c r="X9" s="1"/>
-      <c r="Y9" s="1"/>
-      <c r="Z9" s="1"/>
-      <c r="AA9" s="1"/>
-      <c r="AB9" s="1"/>
+        <v>155.18</v>
+      </c>
+      <c r="X9" s="1">
+        <v>103.89</v>
+      </c>
+      <c r="Y9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z9" s="1">
+        <v>12158208</v>
+      </c>
+      <c r="AA9" s="1">
+        <v>146.862</v>
+      </c>
+      <c r="AB9" s="1">
+        <v>5.96</v>
+      </c>
       <c r="AC9" s="1">
         <v>0</v>
       </c>
       <c r="AD9" s="1">
-        <v>1200</v>
-      </c>
-      <c r="AE9" s="1"/>
-      <c r="AF9" s="1"/>
-      <c r="AG9" s="1"/>
-      <c r="AH9" s="1"/>
-      <c r="AI9" s="1"/>
+        <v>7.13</v>
+      </c>
+      <c r="AE9" s="1">
+        <v>0.02</v>
+      </c>
+      <c r="AF9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="AG9" s="1">
+        <v>2572</v>
+      </c>
+      <c r="AH9" s="1">
+        <v>0.233</v>
+      </c>
+      <c r="AI9" s="1">
+        <v>0</v>
+      </c>
       <c r="AJ9" s="1">
         <v>0</v>
       </c>
       <c r="AK9" s="1">
-        <v>1200</v>
-      </c>
-      <c r="AL9" s="1"/>
-      <c r="AM9" s="1"/>
-      <c r="AN9" s="1"/>
-      <c r="AO9" s="1"/>
-      <c r="AP9" s="1"/>
+        <v>7.5</v>
+      </c>
+      <c r="AL9" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="AM9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="AN9" s="1">
+        <v>2572</v>
+      </c>
+      <c r="AO9" s="1">
+        <v>0.173</v>
+      </c>
+      <c r="AP9" s="1">
+        <v>0</v>
+      </c>
       <c r="AQ9" s="1">
         <v>0</v>
       </c>
@@ -1586,10 +2129,22 @@
         <f>MIN($B9,$I9,$P9,$W9,$AD9,$AK9)</f>
         <v>0</v>
       </c>
-      <c r="AS9" s="1"/>
-      <c r="AT9" s="1"/>
-      <c r="AU9" s="1"/>
-      <c r="AV9" s="1"/>
+      <c r="AS9" s="1">
+        <f>MIN($C9,$J9,$Q9,$X9,$AE9,$AL9)</f>
+        <v>0</v>
+      </c>
+      <c r="AT9" s="1">
+        <f>MIN($E9,$L9,$S9,$Z9,$AG9,$AN9)</f>
+        <v>0</v>
+      </c>
+      <c r="AU9" s="1">
+        <f>MIN($F9,$M9,$T9,$AA9,$AH9,$AO9)</f>
+        <v>0</v>
+      </c>
+      <c r="AV9" s="1">
+        <f>MIN($G9,$N9,$U9,$AB9,$AI9,$AP9)</f>
+        <v>0</v>
+      </c>
       <c r="AW9" s="1">
         <f>MIN($H9,$O9,$V9,$AC9,$AJ9,$AQ9)</f>
         <v>0</v>
@@ -1598,10 +2153,22 @@
         <f>MEDIAN($B9,$I9,$P9,$W9,$AD9,$AK9)</f>
         <v>0</v>
       </c>
-      <c r="AY9" s="1"/>
-      <c r="AZ9" s="1"/>
-      <c r="BA9" s="1"/>
-      <c r="BB9" s="1"/>
+      <c r="AY9" s="1">
+        <f>MEDIAN($C9,$J9,$Q9,$X9,$AE9,$AL9)</f>
+        <v>0</v>
+      </c>
+      <c r="AZ9" s="1">
+        <f>MEDIAN($E9,$L9,$S9,$Z9,$AG9,$AN9)</f>
+        <v>0</v>
+      </c>
+      <c r="BA9" s="1">
+        <f>MEDIAN($F9,$M9,$T9,$AA9,$AH9,$AO9)</f>
+        <v>0</v>
+      </c>
+      <c r="BB9" s="1">
+        <f>MEDIAN($G9,$N9,$U9,$AB9,$AI9,$AP9)</f>
+        <v>0</v>
+      </c>
       <c r="BC9" s="1">
         <f>MEDIAN($H9,$O9,$V9,$AC9,$AJ9,$AQ9)</f>
         <v>0</v>
@@ -1610,10 +2177,22 @@
         <f>MAX($B9,$I9,$P9,$W9,$AD9,$AK9)</f>
         <v>0</v>
       </c>
-      <c r="BE9" s="1"/>
-      <c r="BF9" s="1"/>
-      <c r="BG9" s="1"/>
-      <c r="BH9" s="1"/>
+      <c r="BE9" s="1">
+        <f>MAX($C9,$J9,$Q9,$X9,$AE9,$AL9)</f>
+        <v>0</v>
+      </c>
+      <c r="BF9" s="1">
+        <f>MAX($E9,$L9,$S9,$Z9,$AG9,$AN9)</f>
+        <v>0</v>
+      </c>
+      <c r="BG9" s="1">
+        <f>MAX($F9,$M9,$T9,$AA9,$AH9,$AO9)</f>
+        <v>0</v>
+      </c>
+      <c r="BH9" s="1">
+        <f>MAX($G9,$N9,$U9,$AB9,$AI9,$AP9)</f>
+        <v>0</v>
+      </c>
       <c r="BI9" s="1">
         <f>MAX($H9,$O9,$V9,$AC9,$AJ9,$AQ9)</f>
         <v>0</v>
@@ -1624,68 +2203,128 @@
         <v>7</v>
       </c>
       <c r="B10" s="1">
-        <v>1200</v>
-      </c>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
+        <v>102.73</v>
+      </c>
+      <c r="C10" s="1">
+        <v>16.58</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="1">
+        <v>14772743</v>
+      </c>
+      <c r="F10" s="1">
+        <v>95.929</v>
+      </c>
+      <c r="G10" s="1">
+        <v>5.33</v>
+      </c>
       <c r="H10" s="1">
         <v>0</v>
       </c>
       <c r="I10" s="1">
-        <v>1200</v>
-      </c>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
-      <c r="M10" s="1"/>
-      <c r="N10" s="1"/>
+        <v>8.42</v>
+      </c>
+      <c r="J10" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L10" s="1">
+        <v>2337</v>
+      </c>
+      <c r="M10" s="1">
+        <v>0.147</v>
+      </c>
+      <c r="N10" s="1">
+        <v>0</v>
+      </c>
       <c r="O10" s="1">
         <v>0</v>
       </c>
       <c r="P10" s="1">
-        <v>1200</v>
-      </c>
-      <c r="Q10" s="1"/>
-      <c r="R10" s="1"/>
-      <c r="S10" s="1"/>
-      <c r="T10" s="1"/>
-      <c r="U10" s="1"/>
+        <v>6.92</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="R10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="S10" s="1">
+        <v>2337</v>
+      </c>
+      <c r="T10" s="1">
+        <v>0.139</v>
+      </c>
+      <c r="U10" s="1">
+        <v>0</v>
+      </c>
       <c r="V10" s="1">
         <v>0</v>
       </c>
       <c r="W10" s="1">
-        <v>1200</v>
-      </c>
-      <c r="X10" s="1"/>
-      <c r="Y10" s="1"/>
-      <c r="Z10" s="1"/>
-      <c r="AA10" s="1"/>
-      <c r="AB10" s="1"/>
+        <v>156.92</v>
+      </c>
+      <c r="X10" s="1">
+        <v>81.56</v>
+      </c>
+      <c r="Y10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z10" s="1">
+        <v>16555758</v>
+      </c>
+      <c r="AA10" s="1">
+        <v>149.108</v>
+      </c>
+      <c r="AB10" s="1">
+        <v>7.13</v>
+      </c>
       <c r="AC10" s="1">
         <v>0</v>
       </c>
       <c r="AD10" s="1">
-        <v>1200</v>
-      </c>
-      <c r="AE10" s="1"/>
-      <c r="AF10" s="1"/>
-      <c r="AG10" s="1"/>
-      <c r="AH10" s="1"/>
-      <c r="AI10" s="1"/>
+        <v>6.92</v>
+      </c>
+      <c r="AE10" s="1">
+        <v>0.02</v>
+      </c>
+      <c r="AF10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="AG10" s="1">
+        <v>2572</v>
+      </c>
+      <c r="AH10" s="1">
+        <v>0.229</v>
+      </c>
+      <c r="AI10" s="1">
+        <v>0</v>
+      </c>
       <c r="AJ10" s="1">
         <v>0</v>
       </c>
       <c r="AK10" s="1">
-        <v>1200</v>
-      </c>
-      <c r="AL10" s="1"/>
-      <c r="AM10" s="1"/>
-      <c r="AN10" s="1"/>
-      <c r="AO10" s="1"/>
-      <c r="AP10" s="1"/>
+        <v>6.57</v>
+      </c>
+      <c r="AL10" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="AM10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="AN10" s="1">
+        <v>2572</v>
+      </c>
+      <c r="AO10" s="1">
+        <v>0.167</v>
+      </c>
+      <c r="AP10" s="1">
+        <v>0</v>
+      </c>
       <c r="AQ10" s="1">
         <v>0</v>
       </c>
@@ -1693,10 +2332,22 @@
         <f>MIN($B10,$I10,$P10,$W10,$AD10,$AK10)</f>
         <v>0</v>
       </c>
-      <c r="AS10" s="1"/>
-      <c r="AT10" s="1"/>
-      <c r="AU10" s="1"/>
-      <c r="AV10" s="1"/>
+      <c r="AS10" s="1">
+        <f>MIN($C10,$J10,$Q10,$X10,$AE10,$AL10)</f>
+        <v>0</v>
+      </c>
+      <c r="AT10" s="1">
+        <f>MIN($E10,$L10,$S10,$Z10,$AG10,$AN10)</f>
+        <v>0</v>
+      </c>
+      <c r="AU10" s="1">
+        <f>MIN($F10,$M10,$T10,$AA10,$AH10,$AO10)</f>
+        <v>0</v>
+      </c>
+      <c r="AV10" s="1">
+        <f>MIN($G10,$N10,$U10,$AB10,$AI10,$AP10)</f>
+        <v>0</v>
+      </c>
       <c r="AW10" s="1">
         <f>MIN($H10,$O10,$V10,$AC10,$AJ10,$AQ10)</f>
         <v>0</v>
@@ -1705,10 +2356,22 @@
         <f>MEDIAN($B10,$I10,$P10,$W10,$AD10,$AK10)</f>
         <v>0</v>
       </c>
-      <c r="AY10" s="1"/>
-      <c r="AZ10" s="1"/>
-      <c r="BA10" s="1"/>
-      <c r="BB10" s="1"/>
+      <c r="AY10" s="1">
+        <f>MEDIAN($C10,$J10,$Q10,$X10,$AE10,$AL10)</f>
+        <v>0</v>
+      </c>
+      <c r="AZ10" s="1">
+        <f>MEDIAN($E10,$L10,$S10,$Z10,$AG10,$AN10)</f>
+        <v>0</v>
+      </c>
+      <c r="BA10" s="1">
+        <f>MEDIAN($F10,$M10,$T10,$AA10,$AH10,$AO10)</f>
+        <v>0</v>
+      </c>
+      <c r="BB10" s="1">
+        <f>MEDIAN($G10,$N10,$U10,$AB10,$AI10,$AP10)</f>
+        <v>0</v>
+      </c>
       <c r="BC10" s="1">
         <f>MEDIAN($H10,$O10,$V10,$AC10,$AJ10,$AQ10)</f>
         <v>0</v>
@@ -1717,10 +2380,22 @@
         <f>MAX($B10,$I10,$P10,$W10,$AD10,$AK10)</f>
         <v>0</v>
       </c>
-      <c r="BE10" s="1"/>
-      <c r="BF10" s="1"/>
-      <c r="BG10" s="1"/>
-      <c r="BH10" s="1"/>
+      <c r="BE10" s="1">
+        <f>MAX($C10,$J10,$Q10,$X10,$AE10,$AL10)</f>
+        <v>0</v>
+      </c>
+      <c r="BF10" s="1">
+        <f>MAX($E10,$L10,$S10,$Z10,$AG10,$AN10)</f>
+        <v>0</v>
+      </c>
+      <c r="BG10" s="1">
+        <f>MAX($F10,$M10,$T10,$AA10,$AH10,$AO10)</f>
+        <v>0</v>
+      </c>
+      <c r="BH10" s="1">
+        <f>MAX($G10,$N10,$U10,$AB10,$AI10,$AP10)</f>
+        <v>0</v>
+      </c>
       <c r="BI10" s="1">
         <f>MAX($H10,$O10,$V10,$AC10,$AJ10,$AQ10)</f>
         <v>0</v>
@@ -1731,68 +2406,128 @@
         <v>8</v>
       </c>
       <c r="B11" s="1">
-        <v>1200</v>
-      </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
+        <v>152.86</v>
+      </c>
+      <c r="C11" s="1">
+        <v>30.86</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" s="1">
+        <v>19302803</v>
+      </c>
+      <c r="F11" s="1">
+        <v>145.843</v>
+      </c>
+      <c r="G11" s="1">
+        <v>7.33</v>
+      </c>
       <c r="H11" s="1">
         <v>0</v>
       </c>
       <c r="I11" s="1">
-        <v>1200</v>
-      </c>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
-      <c r="N11" s="1"/>
+        <v>7.46</v>
+      </c>
+      <c r="J11" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L11" s="1">
+        <v>2337</v>
+      </c>
+      <c r="M11" s="1">
+        <v>0.154</v>
+      </c>
+      <c r="N11" s="1">
+        <v>0</v>
+      </c>
       <c r="O11" s="1">
         <v>0</v>
       </c>
       <c r="P11" s="1">
-        <v>1200</v>
-      </c>
-      <c r="Q11" s="1"/>
-      <c r="R11" s="1"/>
-      <c r="S11" s="1"/>
-      <c r="T11" s="1"/>
-      <c r="U11" s="1"/>
+        <v>12.17</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="R11" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="S11" s="1">
+        <v>2337</v>
+      </c>
+      <c r="T11" s="1">
+        <v>0.334</v>
+      </c>
+      <c r="U11" s="1">
+        <v>0</v>
+      </c>
       <c r="V11" s="1">
         <v>0</v>
       </c>
       <c r="W11" s="1">
-        <v>1200</v>
-      </c>
-      <c r="X11" s="1"/>
-      <c r="Y11" s="1"/>
-      <c r="Z11" s="1"/>
-      <c r="AA11" s="1"/>
-      <c r="AB11" s="1"/>
+        <v>328.61</v>
+      </c>
+      <c r="X11" s="1">
+        <v>222.72</v>
+      </c>
+      <c r="Y11" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z11" s="1">
+        <v>21630908</v>
+      </c>
+      <c r="AA11" s="1">
+        <v>321.284</v>
+      </c>
+      <c r="AB11" s="1">
+        <v>18.53</v>
+      </c>
       <c r="AC11" s="1">
         <v>0</v>
       </c>
       <c r="AD11" s="1">
-        <v>1200</v>
-      </c>
-      <c r="AE11" s="1"/>
-      <c r="AF11" s="1"/>
-      <c r="AG11" s="1"/>
-      <c r="AH11" s="1"/>
-      <c r="AI11" s="1"/>
+        <v>6.88</v>
+      </c>
+      <c r="AE11" s="1">
+        <v>0.02</v>
+      </c>
+      <c r="AF11" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="AG11" s="1">
+        <v>2572</v>
+      </c>
+      <c r="AH11" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="AI11" s="1">
+        <v>0</v>
+      </c>
       <c r="AJ11" s="1">
         <v>0</v>
       </c>
       <c r="AK11" s="1">
-        <v>1200</v>
-      </c>
-      <c r="AL11" s="1"/>
-      <c r="AM11" s="1"/>
-      <c r="AN11" s="1"/>
-      <c r="AO11" s="1"/>
-      <c r="AP11" s="1"/>
+        <v>6.76</v>
+      </c>
+      <c r="AL11" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="AM11" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="AN11" s="1">
+        <v>2572</v>
+      </c>
+      <c r="AO11" s="1">
+        <v>0.169</v>
+      </c>
+      <c r="AP11" s="1">
+        <v>0</v>
+      </c>
       <c r="AQ11" s="1">
         <v>0</v>
       </c>
@@ -1800,10 +2535,22 @@
         <f>MIN($B11,$I11,$P11,$W11,$AD11,$AK11)</f>
         <v>0</v>
       </c>
-      <c r="AS11" s="1"/>
-      <c r="AT11" s="1"/>
-      <c r="AU11" s="1"/>
-      <c r="AV11" s="1"/>
+      <c r="AS11" s="1">
+        <f>MIN($C11,$J11,$Q11,$X11,$AE11,$AL11)</f>
+        <v>0</v>
+      </c>
+      <c r="AT11" s="1">
+        <f>MIN($E11,$L11,$S11,$Z11,$AG11,$AN11)</f>
+        <v>0</v>
+      </c>
+      <c r="AU11" s="1">
+        <f>MIN($F11,$M11,$T11,$AA11,$AH11,$AO11)</f>
+        <v>0</v>
+      </c>
+      <c r="AV11" s="1">
+        <f>MIN($G11,$N11,$U11,$AB11,$AI11,$AP11)</f>
+        <v>0</v>
+      </c>
       <c r="AW11" s="1">
         <f>MIN($H11,$O11,$V11,$AC11,$AJ11,$AQ11)</f>
         <v>0</v>
@@ -1812,10 +2559,22 @@
         <f>MEDIAN($B11,$I11,$P11,$W11,$AD11,$AK11)</f>
         <v>0</v>
       </c>
-      <c r="AY11" s="1"/>
-      <c r="AZ11" s="1"/>
-      <c r="BA11" s="1"/>
-      <c r="BB11" s="1"/>
+      <c r="AY11" s="1">
+        <f>MEDIAN($C11,$J11,$Q11,$X11,$AE11,$AL11)</f>
+        <v>0</v>
+      </c>
+      <c r="AZ11" s="1">
+        <f>MEDIAN($E11,$L11,$S11,$Z11,$AG11,$AN11)</f>
+        <v>0</v>
+      </c>
+      <c r="BA11" s="1">
+        <f>MEDIAN($F11,$M11,$T11,$AA11,$AH11,$AO11)</f>
+        <v>0</v>
+      </c>
+      <c r="BB11" s="1">
+        <f>MEDIAN($G11,$N11,$U11,$AB11,$AI11,$AP11)</f>
+        <v>0</v>
+      </c>
       <c r="BC11" s="1">
         <f>MEDIAN($H11,$O11,$V11,$AC11,$AJ11,$AQ11)</f>
         <v>0</v>
@@ -1824,10 +2583,22 @@
         <f>MAX($B11,$I11,$P11,$W11,$AD11,$AK11)</f>
         <v>0</v>
       </c>
-      <c r="BE11" s="1"/>
-      <c r="BF11" s="1"/>
-      <c r="BG11" s="1"/>
-      <c r="BH11" s="1"/>
+      <c r="BE11" s="1">
+        <f>MAX($C11,$J11,$Q11,$X11,$AE11,$AL11)</f>
+        <v>0</v>
+      </c>
+      <c r="BF11" s="1">
+        <f>MAX($E11,$L11,$S11,$Z11,$AG11,$AN11)</f>
+        <v>0</v>
+      </c>
+      <c r="BG11" s="1">
+        <f>MAX($F11,$M11,$T11,$AA11,$AH11,$AO11)</f>
+        <v>0</v>
+      </c>
+      <c r="BH11" s="1">
+        <f>MAX($G11,$N11,$U11,$AB11,$AI11,$AP11)</f>
+        <v>0</v>
+      </c>
       <c r="BI11" s="1">
         <f>MAX($H11,$O11,$V11,$AC11,$AJ11,$AQ11)</f>
         <v>0</v>
@@ -1838,68 +2609,128 @@
         <v>9</v>
       </c>
       <c r="B12" s="1">
-        <v>1200</v>
-      </c>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
+        <v>214.65</v>
+      </c>
+      <c r="C12" s="1">
+        <v>46.04</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" s="1">
+        <v>24437863</v>
+      </c>
+      <c r="F12" s="1">
+        <v>206.43</v>
+      </c>
+      <c r="G12" s="1">
+        <v>10.7</v>
+      </c>
       <c r="H12" s="1">
         <v>0</v>
       </c>
       <c r="I12" s="1">
-        <v>1200</v>
-      </c>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-      <c r="L12" s="1"/>
-      <c r="M12" s="1"/>
-      <c r="N12" s="1"/>
+        <v>6.82</v>
+      </c>
+      <c r="J12" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L12" s="1">
+        <v>2337</v>
+      </c>
+      <c r="M12" s="1">
+        <v>0.155</v>
+      </c>
+      <c r="N12" s="1">
+        <v>0</v>
+      </c>
       <c r="O12" s="1">
         <v>0</v>
       </c>
       <c r="P12" s="1">
-        <v>1200</v>
-      </c>
-      <c r="Q12" s="1"/>
-      <c r="R12" s="1"/>
-      <c r="S12" s="1"/>
-      <c r="T12" s="1"/>
-      <c r="U12" s="1"/>
+        <v>6.21</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="R12" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="S12" s="1">
+        <v>2337</v>
+      </c>
+      <c r="T12" s="1">
+        <v>0.144</v>
+      </c>
+      <c r="U12" s="1">
+        <v>0</v>
+      </c>
       <c r="V12" s="1">
         <v>0</v>
       </c>
       <c r="W12" s="1">
-        <v>1200</v>
-      </c>
-      <c r="X12" s="1"/>
-      <c r="Y12" s="1"/>
-      <c r="Z12" s="1"/>
-      <c r="AA12" s="1"/>
-      <c r="AB12" s="1"/>
+        <v>370.41</v>
+      </c>
+      <c r="X12" s="1">
+        <v>222.09</v>
+      </c>
+      <c r="Y12" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z12" s="1">
+        <v>27383658</v>
+      </c>
+      <c r="AA12" s="1">
+        <v>362.821</v>
+      </c>
+      <c r="AB12" s="1">
+        <v>32.94</v>
+      </c>
       <c r="AC12" s="1">
         <v>0</v>
       </c>
       <c r="AD12" s="1">
-        <v>1200</v>
-      </c>
-      <c r="AE12" s="1"/>
-      <c r="AF12" s="1"/>
-      <c r="AG12" s="1"/>
-      <c r="AH12" s="1"/>
-      <c r="AI12" s="1"/>
+        <v>7.22</v>
+      </c>
+      <c r="AE12" s="1">
+        <v>0.02</v>
+      </c>
+      <c r="AF12" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="AG12" s="1">
+        <v>2572</v>
+      </c>
+      <c r="AH12" s="1">
+        <v>0.217</v>
+      </c>
+      <c r="AI12" s="1">
+        <v>0</v>
+      </c>
       <c r="AJ12" s="1">
         <v>0</v>
       </c>
       <c r="AK12" s="1">
-        <v>1200</v>
-      </c>
-      <c r="AL12" s="1"/>
-      <c r="AM12" s="1"/>
-      <c r="AN12" s="1"/>
-      <c r="AO12" s="1"/>
-      <c r="AP12" s="1"/>
+        <v>6.53</v>
+      </c>
+      <c r="AL12" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="AM12" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="AN12" s="1">
+        <v>2572</v>
+      </c>
+      <c r="AO12" s="1">
+        <v>0.17</v>
+      </c>
+      <c r="AP12" s="1">
+        <v>0</v>
+      </c>
       <c r="AQ12" s="1">
         <v>0</v>
       </c>
@@ -1907,10 +2738,22 @@
         <f>MIN($B12,$I12,$P12,$W12,$AD12,$AK12)</f>
         <v>0</v>
       </c>
-      <c r="AS12" s="1"/>
-      <c r="AT12" s="1"/>
-      <c r="AU12" s="1"/>
-      <c r="AV12" s="1"/>
+      <c r="AS12" s="1">
+        <f>MIN($C12,$J12,$Q12,$X12,$AE12,$AL12)</f>
+        <v>0</v>
+      </c>
+      <c r="AT12" s="1">
+        <f>MIN($E12,$L12,$S12,$Z12,$AG12,$AN12)</f>
+        <v>0</v>
+      </c>
+      <c r="AU12" s="1">
+        <f>MIN($F12,$M12,$T12,$AA12,$AH12,$AO12)</f>
+        <v>0</v>
+      </c>
+      <c r="AV12" s="1">
+        <f>MIN($G12,$N12,$U12,$AB12,$AI12,$AP12)</f>
+        <v>0</v>
+      </c>
       <c r="AW12" s="1">
         <f>MIN($H12,$O12,$V12,$AC12,$AJ12,$AQ12)</f>
         <v>0</v>
@@ -1919,10 +2762,22 @@
         <f>MEDIAN($B12,$I12,$P12,$W12,$AD12,$AK12)</f>
         <v>0</v>
       </c>
-      <c r="AY12" s="1"/>
-      <c r="AZ12" s="1"/>
-      <c r="BA12" s="1"/>
-      <c r="BB12" s="1"/>
+      <c r="AY12" s="1">
+        <f>MEDIAN($C12,$J12,$Q12,$X12,$AE12,$AL12)</f>
+        <v>0</v>
+      </c>
+      <c r="AZ12" s="1">
+        <f>MEDIAN($E12,$L12,$S12,$Z12,$AG12,$AN12)</f>
+        <v>0</v>
+      </c>
+      <c r="BA12" s="1">
+        <f>MEDIAN($F12,$M12,$T12,$AA12,$AH12,$AO12)</f>
+        <v>0</v>
+      </c>
+      <c r="BB12" s="1">
+        <f>MEDIAN($G12,$N12,$U12,$AB12,$AI12,$AP12)</f>
+        <v>0</v>
+      </c>
       <c r="BC12" s="1">
         <f>MEDIAN($H12,$O12,$V12,$AC12,$AJ12,$AQ12)</f>
         <v>0</v>
@@ -1931,10 +2786,22 @@
         <f>MAX($B12,$I12,$P12,$W12,$AD12,$AK12)</f>
         <v>0</v>
       </c>
-      <c r="BE12" s="1"/>
-      <c r="BF12" s="1"/>
-      <c r="BG12" s="1"/>
-      <c r="BH12" s="1"/>
+      <c r="BE12" s="1">
+        <f>MAX($C12,$J12,$Q12,$X12,$AE12,$AL12)</f>
+        <v>0</v>
+      </c>
+      <c r="BF12" s="1">
+        <f>MAX($E12,$L12,$S12,$Z12,$AG12,$AN12)</f>
+        <v>0</v>
+      </c>
+      <c r="BG12" s="1">
+        <f>MAX($F12,$M12,$T12,$AA12,$AH12,$AO12)</f>
+        <v>0</v>
+      </c>
+      <c r="BH12" s="1">
+        <f>MAX($G12,$N12,$U12,$AB12,$AI12,$AP12)</f>
+        <v>0</v>
+      </c>
       <c r="BI12" s="1">
         <f>MAX($H12,$O12,$V12,$AC12,$AJ12,$AQ12)</f>
         <v>0</v>
@@ -3565,7 +4432,7 @@
   <sheetData>
     <row r="1" spans="1:61">
       <c r="A1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>18</v>
@@ -3577,7 +4444,7 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -3586,7 +4453,7 @@
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
       <c r="P1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
@@ -3595,7 +4462,7 @@
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
       <c r="W1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X1" s="1"/>
       <c r="Y1" s="1"/>
@@ -3604,7 +4471,7 @@
       <c r="AB1" s="1"/>
       <c r="AC1" s="1"/>
       <c r="AD1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AE1" s="1"/>
       <c r="AF1" s="1"/>
@@ -3613,7 +4480,7 @@
       <c r="AI1" s="1"/>
       <c r="AJ1" s="1"/>
       <c r="AK1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AL1" s="1"/>
       <c r="AM1" s="1"/>
@@ -3622,7 +4489,7 @@
       <c r="AP1" s="1"/>
       <c r="AQ1" s="1"/>
       <c r="AR1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AS1" s="1"/>
       <c r="AT1" s="1"/>
@@ -3630,7 +4497,7 @@
       <c r="AV1" s="1"/>
       <c r="AW1" s="1"/>
       <c r="AX1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AY1" s="1"/>
       <c r="AZ1" s="1"/>
@@ -3638,7 +4505,7 @@
       <c r="BB1" s="1"/>
       <c r="BC1" s="1"/>
       <c r="BD1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="BE1" s="1"/>
       <c r="BF1" s="1"/>
@@ -3648,7 +4515,7 @@
     </row>
     <row r="2" spans="1:61">
       <c r="A2" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>19</v>
@@ -3660,16 +4527,16 @@
         <v>21</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>19</v>
@@ -3681,16 +4548,16 @@
         <v>21</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P2" s="1" t="s">
         <v>19</v>
@@ -3702,16 +4569,16 @@
         <v>21</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="W2" s="1" t="s">
         <v>19</v>
@@ -3723,16 +4590,16 @@
         <v>21</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA2" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AB2" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AC2" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AD2" s="1" t="s">
         <v>19</v>
@@ -3744,16 +4611,16 @@
         <v>21</v>
       </c>
       <c r="AG2" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AH2" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI2" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AJ2" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AK2" s="1" t="s">
         <v>19</v>
@@ -3765,16 +4632,16 @@
         <v>21</v>
       </c>
       <c r="AN2" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO2" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AP2" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ2" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AR2" s="1" t="s">
         <v>19</v>
@@ -3783,16 +4650,16 @@
         <v>20</v>
       </c>
       <c r="AT2" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AU2" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AV2" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AW2" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AX2" s="1" t="s">
         <v>19</v>
@@ -3801,16 +4668,16 @@
         <v>20</v>
       </c>
       <c r="AZ2" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BA2" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BB2" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BC2" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BD2" s="1" t="s">
         <v>19</v>
@@ -3819,16 +4686,16 @@
         <v>20</v>
       </c>
       <c r="BF2" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BG2" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BH2" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BI2" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:61">
@@ -4066,11 +4933,23 @@
         <f t="array" ref="B4">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!B4:Instances!B4),"median", MEDIAN(Instances!B4:Instances!B4),"min", MIN(Instances!B4:Instances!B4),"max", MAX(Instances!B4:Instances!B4),"diff", MAX(Instances!B4:Instances!B4)-MIN(Instances!B4:Instances!B4))</f>
         <v>0</v>
       </c>
-      <c r="C4" s="1"/>
+      <c r="C4" s="1" cm="1">
+        <f t="array" ref="C4">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!C4:Instances!C4),"median", MEDIAN(Instances!C4:Instances!C4),"min", MIN(Instances!C4:Instances!C4),"max", MAX(Instances!C4:Instances!C4),"diff", MAX(Instances!C4:Instances!C4)-MIN(Instances!C4:Instances!C4))</f>
+        <v>0</v>
+      </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
+      <c r="E4" s="1" cm="1">
+        <f t="array" ref="E4">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!E4:Instances!E4),"median", MEDIAN(Instances!E4:Instances!E4),"min", MIN(Instances!E4:Instances!E4),"max", MAX(Instances!E4:Instances!E4),"diff", MAX(Instances!E4:Instances!E4)-MIN(Instances!E4:Instances!E4))</f>
+        <v>0</v>
+      </c>
+      <c r="F4" s="1" cm="1">
+        <f t="array" ref="F4">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!F4:Instances!F4),"median", MEDIAN(Instances!F4:Instances!F4),"min", MIN(Instances!F4:Instances!F4),"max", MAX(Instances!F4:Instances!F4),"diff", MAX(Instances!F4:Instances!F4)-MIN(Instances!F4:Instances!F4))</f>
+        <v>0</v>
+      </c>
+      <c r="G4" s="1" cm="1">
+        <f t="array" ref="G4">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!G4:Instances!G4),"median", MEDIAN(Instances!G4:Instances!G4),"min", MIN(Instances!G4:Instances!G4),"max", MAX(Instances!G4:Instances!G4),"diff", MAX(Instances!G4:Instances!G4)-MIN(Instances!G4:Instances!G4))</f>
+        <v>0</v>
+      </c>
       <c r="H4" s="1" cm="1">
         <f t="array" ref="H4">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!H4:Instances!H4),"median", MEDIAN(Instances!H4:Instances!H4),"min", MIN(Instances!H4:Instances!H4),"max", MAX(Instances!H4:Instances!H4),"diff", MAX(Instances!H4:Instances!H4)-MIN(Instances!H4:Instances!H4))</f>
         <v>0</v>
@@ -4079,11 +4958,23 @@
         <f t="array" ref="I4">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!I4:Instances!I4),"median", MEDIAN(Instances!I4:Instances!I4),"min", MIN(Instances!I4:Instances!I4),"max", MAX(Instances!I4:Instances!I4),"diff", MAX(Instances!I4:Instances!I4)-MIN(Instances!I4:Instances!I4))</f>
         <v>0</v>
       </c>
-      <c r="J4" s="1"/>
+      <c r="J4" s="1" cm="1">
+        <f t="array" ref="J4">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!J4:Instances!J4),"median", MEDIAN(Instances!J4:Instances!J4),"min", MIN(Instances!J4:Instances!J4),"max", MAX(Instances!J4:Instances!J4),"diff", MAX(Instances!J4:Instances!J4)-MIN(Instances!J4:Instances!J4))</f>
+        <v>0</v>
+      </c>
       <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-      <c r="N4" s="1"/>
+      <c r="L4" s="1" cm="1">
+        <f t="array" ref="L4">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!L4:Instances!L4),"median", MEDIAN(Instances!L4:Instances!L4),"min", MIN(Instances!L4:Instances!L4),"max", MAX(Instances!L4:Instances!L4),"diff", MAX(Instances!L4:Instances!L4)-MIN(Instances!L4:Instances!L4))</f>
+        <v>0</v>
+      </c>
+      <c r="M4" s="1" cm="1">
+        <f t="array" ref="M4">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!M4:Instances!M4),"median", MEDIAN(Instances!M4:Instances!M4),"min", MIN(Instances!M4:Instances!M4),"max", MAX(Instances!M4:Instances!M4),"diff", MAX(Instances!M4:Instances!M4)-MIN(Instances!M4:Instances!M4))</f>
+        <v>0</v>
+      </c>
+      <c r="N4" s="1" cm="1">
+        <f t="array" ref="N4">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!N4:Instances!N4),"median", MEDIAN(Instances!N4:Instances!N4),"min", MIN(Instances!N4:Instances!N4),"max", MAX(Instances!N4:Instances!N4),"diff", MAX(Instances!N4:Instances!N4)-MIN(Instances!N4:Instances!N4))</f>
+        <v>0</v>
+      </c>
       <c r="O4" s="1" cm="1">
         <f t="array" ref="O4">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!O4:Instances!O4),"median", MEDIAN(Instances!O4:Instances!O4),"min", MIN(Instances!O4:Instances!O4),"max", MAX(Instances!O4:Instances!O4),"diff", MAX(Instances!O4:Instances!O4)-MIN(Instances!O4:Instances!O4))</f>
         <v>0</v>
@@ -4092,11 +4983,23 @@
         <f t="array" ref="P4">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!P4:Instances!P4),"median", MEDIAN(Instances!P4:Instances!P4),"min", MIN(Instances!P4:Instances!P4),"max", MAX(Instances!P4:Instances!P4),"diff", MAX(Instances!P4:Instances!P4)-MIN(Instances!P4:Instances!P4))</f>
         <v>0</v>
       </c>
-      <c r="Q4" s="1"/>
+      <c r="Q4" s="1" cm="1">
+        <f t="array" ref="Q4">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!Q4:Instances!Q4),"median", MEDIAN(Instances!Q4:Instances!Q4),"min", MIN(Instances!Q4:Instances!Q4),"max", MAX(Instances!Q4:Instances!Q4),"diff", MAX(Instances!Q4:Instances!Q4)-MIN(Instances!Q4:Instances!Q4))</f>
+        <v>0</v>
+      </c>
       <c r="R4" s="1"/>
-      <c r="S4" s="1"/>
-      <c r="T4" s="1"/>
-      <c r="U4" s="1"/>
+      <c r="S4" s="1" cm="1">
+        <f t="array" ref="S4">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!S4:Instances!S4),"median", MEDIAN(Instances!S4:Instances!S4),"min", MIN(Instances!S4:Instances!S4),"max", MAX(Instances!S4:Instances!S4),"diff", MAX(Instances!S4:Instances!S4)-MIN(Instances!S4:Instances!S4))</f>
+        <v>0</v>
+      </c>
+      <c r="T4" s="1" cm="1">
+        <f t="array" ref="T4">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!T4:Instances!T4),"median", MEDIAN(Instances!T4:Instances!T4),"min", MIN(Instances!T4:Instances!T4),"max", MAX(Instances!T4:Instances!T4),"diff", MAX(Instances!T4:Instances!T4)-MIN(Instances!T4:Instances!T4))</f>
+        <v>0</v>
+      </c>
+      <c r="U4" s="1" cm="1">
+        <f t="array" ref="U4">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!U4:Instances!U4),"median", MEDIAN(Instances!U4:Instances!U4),"min", MIN(Instances!U4:Instances!U4),"max", MAX(Instances!U4:Instances!U4),"diff", MAX(Instances!U4:Instances!U4)-MIN(Instances!U4:Instances!U4))</f>
+        <v>0</v>
+      </c>
       <c r="V4" s="1" cm="1">
         <f t="array" ref="V4">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!V4:Instances!V4),"median", MEDIAN(Instances!V4:Instances!V4),"min", MIN(Instances!V4:Instances!V4),"max", MAX(Instances!V4:Instances!V4),"diff", MAX(Instances!V4:Instances!V4)-MIN(Instances!V4:Instances!V4))</f>
         <v>0</v>
@@ -4105,11 +5008,23 @@
         <f t="array" ref="W4">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!W4:Instances!W4),"median", MEDIAN(Instances!W4:Instances!W4),"min", MIN(Instances!W4:Instances!W4),"max", MAX(Instances!W4:Instances!W4),"diff", MAX(Instances!W4:Instances!W4)-MIN(Instances!W4:Instances!W4))</f>
         <v>0</v>
       </c>
-      <c r="X4" s="1"/>
+      <c r="X4" s="1" cm="1">
+        <f t="array" ref="X4">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!X4:Instances!X4),"median", MEDIAN(Instances!X4:Instances!X4),"min", MIN(Instances!X4:Instances!X4),"max", MAX(Instances!X4:Instances!X4),"diff", MAX(Instances!X4:Instances!X4)-MIN(Instances!X4:Instances!X4))</f>
+        <v>0</v>
+      </c>
       <c r="Y4" s="1"/>
-      <c r="Z4" s="1"/>
-      <c r="AA4" s="1"/>
-      <c r="AB4" s="1"/>
+      <c r="Z4" s="1" cm="1">
+        <f t="array" ref="Z4">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!Z4:Instances!Z4),"median", MEDIAN(Instances!Z4:Instances!Z4),"min", MIN(Instances!Z4:Instances!Z4),"max", MAX(Instances!Z4:Instances!Z4),"diff", MAX(Instances!Z4:Instances!Z4)-MIN(Instances!Z4:Instances!Z4))</f>
+        <v>0</v>
+      </c>
+      <c r="AA4" s="1" cm="1">
+        <f t="array" ref="AA4">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AA4:Instances!AA4),"median", MEDIAN(Instances!AA4:Instances!AA4),"min", MIN(Instances!AA4:Instances!AA4),"max", MAX(Instances!AA4:Instances!AA4),"diff", MAX(Instances!AA4:Instances!AA4)-MIN(Instances!AA4:Instances!AA4))</f>
+        <v>0</v>
+      </c>
+      <c r="AB4" s="1" cm="1">
+        <f t="array" ref="AB4">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AB4:Instances!AB4),"median", MEDIAN(Instances!AB4:Instances!AB4),"min", MIN(Instances!AB4:Instances!AB4),"max", MAX(Instances!AB4:Instances!AB4),"diff", MAX(Instances!AB4:Instances!AB4)-MIN(Instances!AB4:Instances!AB4))</f>
+        <v>0</v>
+      </c>
       <c r="AC4" s="1" cm="1">
         <f t="array" ref="AC4">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AC4:Instances!AC4),"median", MEDIAN(Instances!AC4:Instances!AC4),"min", MIN(Instances!AC4:Instances!AC4),"max", MAX(Instances!AC4:Instances!AC4),"diff", MAX(Instances!AC4:Instances!AC4)-MIN(Instances!AC4:Instances!AC4))</f>
         <v>0</v>
@@ -4118,11 +5033,23 @@
         <f t="array" ref="AD4">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AD4:Instances!AD4),"median", MEDIAN(Instances!AD4:Instances!AD4),"min", MIN(Instances!AD4:Instances!AD4),"max", MAX(Instances!AD4:Instances!AD4),"diff", MAX(Instances!AD4:Instances!AD4)-MIN(Instances!AD4:Instances!AD4))</f>
         <v>0</v>
       </c>
-      <c r="AE4" s="1"/>
+      <c r="AE4" s="1" cm="1">
+        <f t="array" ref="AE4">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AE4:Instances!AE4),"median", MEDIAN(Instances!AE4:Instances!AE4),"min", MIN(Instances!AE4:Instances!AE4),"max", MAX(Instances!AE4:Instances!AE4),"diff", MAX(Instances!AE4:Instances!AE4)-MIN(Instances!AE4:Instances!AE4))</f>
+        <v>0</v>
+      </c>
       <c r="AF4" s="1"/>
-      <c r="AG4" s="1"/>
-      <c r="AH4" s="1"/>
-      <c r="AI4" s="1"/>
+      <c r="AG4" s="1" cm="1">
+        <f t="array" ref="AG4">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AG4:Instances!AG4),"median", MEDIAN(Instances!AG4:Instances!AG4),"min", MIN(Instances!AG4:Instances!AG4),"max", MAX(Instances!AG4:Instances!AG4),"diff", MAX(Instances!AG4:Instances!AG4)-MIN(Instances!AG4:Instances!AG4))</f>
+        <v>0</v>
+      </c>
+      <c r="AH4" s="1" cm="1">
+        <f t="array" ref="AH4">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AH4:Instances!AH4),"median", MEDIAN(Instances!AH4:Instances!AH4),"min", MIN(Instances!AH4:Instances!AH4),"max", MAX(Instances!AH4:Instances!AH4),"diff", MAX(Instances!AH4:Instances!AH4)-MIN(Instances!AH4:Instances!AH4))</f>
+        <v>0</v>
+      </c>
+      <c r="AI4" s="1" cm="1">
+        <f t="array" ref="AI4">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AI4:Instances!AI4),"median", MEDIAN(Instances!AI4:Instances!AI4),"min", MIN(Instances!AI4:Instances!AI4),"max", MAX(Instances!AI4:Instances!AI4),"diff", MAX(Instances!AI4:Instances!AI4)-MIN(Instances!AI4:Instances!AI4))</f>
+        <v>0</v>
+      </c>
       <c r="AJ4" s="1" cm="1">
         <f t="array" ref="AJ4">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AJ4:Instances!AJ4),"median", MEDIAN(Instances!AJ4:Instances!AJ4),"min", MIN(Instances!AJ4:Instances!AJ4),"max", MAX(Instances!AJ4:Instances!AJ4),"diff", MAX(Instances!AJ4:Instances!AJ4)-MIN(Instances!AJ4:Instances!AJ4))</f>
         <v>0</v>
@@ -4131,11 +5058,23 @@
         <f t="array" ref="AK4">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AK4:Instances!AK4),"median", MEDIAN(Instances!AK4:Instances!AK4),"min", MIN(Instances!AK4:Instances!AK4),"max", MAX(Instances!AK4:Instances!AK4),"diff", MAX(Instances!AK4:Instances!AK4)-MIN(Instances!AK4:Instances!AK4))</f>
         <v>0</v>
       </c>
-      <c r="AL4" s="1"/>
+      <c r="AL4" s="1" cm="1">
+        <f t="array" ref="AL4">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AL4:Instances!AL4),"median", MEDIAN(Instances!AL4:Instances!AL4),"min", MIN(Instances!AL4:Instances!AL4),"max", MAX(Instances!AL4:Instances!AL4),"diff", MAX(Instances!AL4:Instances!AL4)-MIN(Instances!AL4:Instances!AL4))</f>
+        <v>0</v>
+      </c>
       <c r="AM4" s="1"/>
-      <c r="AN4" s="1"/>
-      <c r="AO4" s="1"/>
-      <c r="AP4" s="1"/>
+      <c r="AN4" s="1" cm="1">
+        <f t="array" ref="AN4">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AN4:Instances!AN4),"median", MEDIAN(Instances!AN4:Instances!AN4),"min", MIN(Instances!AN4:Instances!AN4),"max", MAX(Instances!AN4:Instances!AN4),"diff", MAX(Instances!AN4:Instances!AN4)-MIN(Instances!AN4:Instances!AN4))</f>
+        <v>0</v>
+      </c>
+      <c r="AO4" s="1" cm="1">
+        <f t="array" ref="AO4">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AO4:Instances!AO4),"median", MEDIAN(Instances!AO4:Instances!AO4),"min", MIN(Instances!AO4:Instances!AO4),"max", MAX(Instances!AO4:Instances!AO4),"diff", MAX(Instances!AO4:Instances!AO4)-MIN(Instances!AO4:Instances!AO4))</f>
+        <v>0</v>
+      </c>
+      <c r="AP4" s="1" cm="1">
+        <f t="array" ref="AP4">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AP4:Instances!AP4),"median", MEDIAN(Instances!AP4:Instances!AP4),"min", MIN(Instances!AP4:Instances!AP4),"max", MAX(Instances!AP4:Instances!AP4),"diff", MAX(Instances!AP4:Instances!AP4)-MIN(Instances!AP4:Instances!AP4))</f>
+        <v>0</v>
+      </c>
       <c r="AQ4" s="1" cm="1">
         <f t="array" ref="AQ4">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AQ4:Instances!AQ4),"median", MEDIAN(Instances!AQ4:Instances!AQ4),"min", MIN(Instances!AQ4:Instances!AQ4),"max", MAX(Instances!AQ4:Instances!AQ4),"diff", MAX(Instances!AQ4:Instances!AQ4)-MIN(Instances!AQ4:Instances!AQ4))</f>
         <v>0</v>
@@ -4144,10 +5083,22 @@
         <f>MIN($B4,$I4,$P4,$W4,$AD4,$AK4)</f>
         <v>0</v>
       </c>
-      <c r="AS4" s="1"/>
-      <c r="AT4" s="1"/>
-      <c r="AU4" s="1"/>
-      <c r="AV4" s="1"/>
+      <c r="AS4" s="1">
+        <f>MIN($C4,$J4,$Q4,$X4,$AE4,$AL4)</f>
+        <v>0</v>
+      </c>
+      <c r="AT4" s="1">
+        <f>MIN($E4,$L4,$S4,$Z4,$AG4,$AN4)</f>
+        <v>0</v>
+      </c>
+      <c r="AU4" s="1">
+        <f>MIN($F4,$M4,$T4,$AA4,$AH4,$AO4)</f>
+        <v>0</v>
+      </c>
+      <c r="AV4" s="1">
+        <f>MIN($G4,$N4,$U4,$AB4,$AI4,$AP4)</f>
+        <v>0</v>
+      </c>
       <c r="AW4" s="1">
         <f>MIN($H4,$O4,$V4,$AC4,$AJ4,$AQ4)</f>
         <v>0</v>
@@ -4156,10 +5107,22 @@
         <f>MEDIAN($B4,$I4,$P4,$W4,$AD4,$AK4)</f>
         <v>0</v>
       </c>
-      <c r="AY4" s="1"/>
-      <c r="AZ4" s="1"/>
-      <c r="BA4" s="1"/>
-      <c r="BB4" s="1"/>
+      <c r="AY4" s="1">
+        <f>MEDIAN($C4,$J4,$Q4,$X4,$AE4,$AL4)</f>
+        <v>0</v>
+      </c>
+      <c r="AZ4" s="1">
+        <f>MEDIAN($E4,$L4,$S4,$Z4,$AG4,$AN4)</f>
+        <v>0</v>
+      </c>
+      <c r="BA4" s="1">
+        <f>MEDIAN($F4,$M4,$T4,$AA4,$AH4,$AO4)</f>
+        <v>0</v>
+      </c>
+      <c r="BB4" s="1">
+        <f>MEDIAN($G4,$N4,$U4,$AB4,$AI4,$AP4)</f>
+        <v>0</v>
+      </c>
       <c r="BC4" s="1">
         <f>MEDIAN($H4,$O4,$V4,$AC4,$AJ4,$AQ4)</f>
         <v>0</v>
@@ -4168,10 +5131,22 @@
         <f>MAX($B4,$I4,$P4,$W4,$AD4,$AK4)</f>
         <v>0</v>
       </c>
-      <c r="BE4" s="1"/>
-      <c r="BF4" s="1"/>
-      <c r="BG4" s="1"/>
-      <c r="BH4" s="1"/>
+      <c r="BE4" s="1">
+        <f>MAX($C4,$J4,$Q4,$X4,$AE4,$AL4)</f>
+        <v>0</v>
+      </c>
+      <c r="BF4" s="1">
+        <f>MAX($E4,$L4,$S4,$Z4,$AG4,$AN4)</f>
+        <v>0</v>
+      </c>
+      <c r="BG4" s="1">
+        <f>MAX($F4,$M4,$T4,$AA4,$AH4,$AO4)</f>
+        <v>0</v>
+      </c>
+      <c r="BH4" s="1">
+        <f>MAX($G4,$N4,$U4,$AB4,$AI4,$AP4)</f>
+        <v>0</v>
+      </c>
       <c r="BI4" s="1">
         <f>MAX($H4,$O4,$V4,$AC4,$AJ4,$AQ4)</f>
         <v>0</v>
@@ -4185,11 +5160,23 @@
         <f t="array" ref="B5">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!B5:Instances!B5),"median", MEDIAN(Instances!B5:Instances!B5),"min", MIN(Instances!B5:Instances!B5),"max", MAX(Instances!B5:Instances!B5),"diff", MAX(Instances!B5:Instances!B5)-MIN(Instances!B5:Instances!B5))</f>
         <v>0</v>
       </c>
-      <c r="C5" s="1"/>
+      <c r="C5" s="1" cm="1">
+        <f t="array" ref="C5">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!C5:Instances!C5),"median", MEDIAN(Instances!C5:Instances!C5),"min", MIN(Instances!C5:Instances!C5),"max", MAX(Instances!C5:Instances!C5),"diff", MAX(Instances!C5:Instances!C5)-MIN(Instances!C5:Instances!C5))</f>
+        <v>0</v>
+      </c>
       <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
+      <c r="E5" s="1" cm="1">
+        <f t="array" ref="E5">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!E5:Instances!E5),"median", MEDIAN(Instances!E5:Instances!E5),"min", MIN(Instances!E5:Instances!E5),"max", MAX(Instances!E5:Instances!E5),"diff", MAX(Instances!E5:Instances!E5)-MIN(Instances!E5:Instances!E5))</f>
+        <v>0</v>
+      </c>
+      <c r="F5" s="1" cm="1">
+        <f t="array" ref="F5">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!F5:Instances!F5),"median", MEDIAN(Instances!F5:Instances!F5),"min", MIN(Instances!F5:Instances!F5),"max", MAX(Instances!F5:Instances!F5),"diff", MAX(Instances!F5:Instances!F5)-MIN(Instances!F5:Instances!F5))</f>
+        <v>0</v>
+      </c>
+      <c r="G5" s="1" cm="1">
+        <f t="array" ref="G5">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!G5:Instances!G5),"median", MEDIAN(Instances!G5:Instances!G5),"min", MIN(Instances!G5:Instances!G5),"max", MAX(Instances!G5:Instances!G5),"diff", MAX(Instances!G5:Instances!G5)-MIN(Instances!G5:Instances!G5))</f>
+        <v>0</v>
+      </c>
       <c r="H5" s="1" cm="1">
         <f t="array" ref="H5">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!H5:Instances!H5),"median", MEDIAN(Instances!H5:Instances!H5),"min", MIN(Instances!H5:Instances!H5),"max", MAX(Instances!H5:Instances!H5),"diff", MAX(Instances!H5:Instances!H5)-MIN(Instances!H5:Instances!H5))</f>
         <v>0</v>
@@ -4198,11 +5185,23 @@
         <f t="array" ref="I5">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!I5:Instances!I5),"median", MEDIAN(Instances!I5:Instances!I5),"min", MIN(Instances!I5:Instances!I5),"max", MAX(Instances!I5:Instances!I5),"diff", MAX(Instances!I5:Instances!I5)-MIN(Instances!I5:Instances!I5))</f>
         <v>0</v>
       </c>
-      <c r="J5" s="1"/>
+      <c r="J5" s="1" cm="1">
+        <f t="array" ref="J5">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!J5:Instances!J5),"median", MEDIAN(Instances!J5:Instances!J5),"min", MIN(Instances!J5:Instances!J5),"max", MAX(Instances!J5:Instances!J5),"diff", MAX(Instances!J5:Instances!J5)-MIN(Instances!J5:Instances!J5))</f>
+        <v>0</v>
+      </c>
       <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="1"/>
+      <c r="L5" s="1" cm="1">
+        <f t="array" ref="L5">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!L5:Instances!L5),"median", MEDIAN(Instances!L5:Instances!L5),"min", MIN(Instances!L5:Instances!L5),"max", MAX(Instances!L5:Instances!L5),"diff", MAX(Instances!L5:Instances!L5)-MIN(Instances!L5:Instances!L5))</f>
+        <v>0</v>
+      </c>
+      <c r="M5" s="1" cm="1">
+        <f t="array" ref="M5">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!M5:Instances!M5),"median", MEDIAN(Instances!M5:Instances!M5),"min", MIN(Instances!M5:Instances!M5),"max", MAX(Instances!M5:Instances!M5),"diff", MAX(Instances!M5:Instances!M5)-MIN(Instances!M5:Instances!M5))</f>
+        <v>0</v>
+      </c>
+      <c r="N5" s="1" cm="1">
+        <f t="array" ref="N5">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!N5:Instances!N5),"median", MEDIAN(Instances!N5:Instances!N5),"min", MIN(Instances!N5:Instances!N5),"max", MAX(Instances!N5:Instances!N5),"diff", MAX(Instances!N5:Instances!N5)-MIN(Instances!N5:Instances!N5))</f>
+        <v>0</v>
+      </c>
       <c r="O5" s="1" cm="1">
         <f t="array" ref="O5">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!O5:Instances!O5),"median", MEDIAN(Instances!O5:Instances!O5),"min", MIN(Instances!O5:Instances!O5),"max", MAX(Instances!O5:Instances!O5),"diff", MAX(Instances!O5:Instances!O5)-MIN(Instances!O5:Instances!O5))</f>
         <v>0</v>
@@ -4211,11 +5210,23 @@
         <f t="array" ref="P5">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!P5:Instances!P5),"median", MEDIAN(Instances!P5:Instances!P5),"min", MIN(Instances!P5:Instances!P5),"max", MAX(Instances!P5:Instances!P5),"diff", MAX(Instances!P5:Instances!P5)-MIN(Instances!P5:Instances!P5))</f>
         <v>0</v>
       </c>
-      <c r="Q5" s="1"/>
+      <c r="Q5" s="1" cm="1">
+        <f t="array" ref="Q5">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!Q5:Instances!Q5),"median", MEDIAN(Instances!Q5:Instances!Q5),"min", MIN(Instances!Q5:Instances!Q5),"max", MAX(Instances!Q5:Instances!Q5),"diff", MAX(Instances!Q5:Instances!Q5)-MIN(Instances!Q5:Instances!Q5))</f>
+        <v>0</v>
+      </c>
       <c r="R5" s="1"/>
-      <c r="S5" s="1"/>
-      <c r="T5" s="1"/>
-      <c r="U5" s="1"/>
+      <c r="S5" s="1" cm="1">
+        <f t="array" ref="S5">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!S5:Instances!S5),"median", MEDIAN(Instances!S5:Instances!S5),"min", MIN(Instances!S5:Instances!S5),"max", MAX(Instances!S5:Instances!S5),"diff", MAX(Instances!S5:Instances!S5)-MIN(Instances!S5:Instances!S5))</f>
+        <v>0</v>
+      </c>
+      <c r="T5" s="1" cm="1">
+        <f t="array" ref="T5">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!T5:Instances!T5),"median", MEDIAN(Instances!T5:Instances!T5),"min", MIN(Instances!T5:Instances!T5),"max", MAX(Instances!T5:Instances!T5),"diff", MAX(Instances!T5:Instances!T5)-MIN(Instances!T5:Instances!T5))</f>
+        <v>0</v>
+      </c>
+      <c r="U5" s="1" cm="1">
+        <f t="array" ref="U5">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!U5:Instances!U5),"median", MEDIAN(Instances!U5:Instances!U5),"min", MIN(Instances!U5:Instances!U5),"max", MAX(Instances!U5:Instances!U5),"diff", MAX(Instances!U5:Instances!U5)-MIN(Instances!U5:Instances!U5))</f>
+        <v>0</v>
+      </c>
       <c r="V5" s="1" cm="1">
         <f t="array" ref="V5">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!V5:Instances!V5),"median", MEDIAN(Instances!V5:Instances!V5),"min", MIN(Instances!V5:Instances!V5),"max", MAX(Instances!V5:Instances!V5),"diff", MAX(Instances!V5:Instances!V5)-MIN(Instances!V5:Instances!V5))</f>
         <v>0</v>
@@ -4224,11 +5235,23 @@
         <f t="array" ref="W5">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!W5:Instances!W5),"median", MEDIAN(Instances!W5:Instances!W5),"min", MIN(Instances!W5:Instances!W5),"max", MAX(Instances!W5:Instances!W5),"diff", MAX(Instances!W5:Instances!W5)-MIN(Instances!W5:Instances!W5))</f>
         <v>0</v>
       </c>
-      <c r="X5" s="1"/>
+      <c r="X5" s="1" cm="1">
+        <f t="array" ref="X5">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!X5:Instances!X5),"median", MEDIAN(Instances!X5:Instances!X5),"min", MIN(Instances!X5:Instances!X5),"max", MAX(Instances!X5:Instances!X5),"diff", MAX(Instances!X5:Instances!X5)-MIN(Instances!X5:Instances!X5))</f>
+        <v>0</v>
+      </c>
       <c r="Y5" s="1"/>
-      <c r="Z5" s="1"/>
-      <c r="AA5" s="1"/>
-      <c r="AB5" s="1"/>
+      <c r="Z5" s="1" cm="1">
+        <f t="array" ref="Z5">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!Z5:Instances!Z5),"median", MEDIAN(Instances!Z5:Instances!Z5),"min", MIN(Instances!Z5:Instances!Z5),"max", MAX(Instances!Z5:Instances!Z5),"diff", MAX(Instances!Z5:Instances!Z5)-MIN(Instances!Z5:Instances!Z5))</f>
+        <v>0</v>
+      </c>
+      <c r="AA5" s="1" cm="1">
+        <f t="array" ref="AA5">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AA5:Instances!AA5),"median", MEDIAN(Instances!AA5:Instances!AA5),"min", MIN(Instances!AA5:Instances!AA5),"max", MAX(Instances!AA5:Instances!AA5),"diff", MAX(Instances!AA5:Instances!AA5)-MIN(Instances!AA5:Instances!AA5))</f>
+        <v>0</v>
+      </c>
+      <c r="AB5" s="1" cm="1">
+        <f t="array" ref="AB5">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AB5:Instances!AB5),"median", MEDIAN(Instances!AB5:Instances!AB5),"min", MIN(Instances!AB5:Instances!AB5),"max", MAX(Instances!AB5:Instances!AB5),"diff", MAX(Instances!AB5:Instances!AB5)-MIN(Instances!AB5:Instances!AB5))</f>
+        <v>0</v>
+      </c>
       <c r="AC5" s="1" cm="1">
         <f t="array" ref="AC5">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AC5:Instances!AC5),"median", MEDIAN(Instances!AC5:Instances!AC5),"min", MIN(Instances!AC5:Instances!AC5),"max", MAX(Instances!AC5:Instances!AC5),"diff", MAX(Instances!AC5:Instances!AC5)-MIN(Instances!AC5:Instances!AC5))</f>
         <v>0</v>
@@ -4237,11 +5260,23 @@
         <f t="array" ref="AD5">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AD5:Instances!AD5),"median", MEDIAN(Instances!AD5:Instances!AD5),"min", MIN(Instances!AD5:Instances!AD5),"max", MAX(Instances!AD5:Instances!AD5),"diff", MAX(Instances!AD5:Instances!AD5)-MIN(Instances!AD5:Instances!AD5))</f>
         <v>0</v>
       </c>
-      <c r="AE5" s="1"/>
+      <c r="AE5" s="1" cm="1">
+        <f t="array" ref="AE5">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AE5:Instances!AE5),"median", MEDIAN(Instances!AE5:Instances!AE5),"min", MIN(Instances!AE5:Instances!AE5),"max", MAX(Instances!AE5:Instances!AE5),"diff", MAX(Instances!AE5:Instances!AE5)-MIN(Instances!AE5:Instances!AE5))</f>
+        <v>0</v>
+      </c>
       <c r="AF5" s="1"/>
-      <c r="AG5" s="1"/>
-      <c r="AH5" s="1"/>
-      <c r="AI5" s="1"/>
+      <c r="AG5" s="1" cm="1">
+        <f t="array" ref="AG5">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AG5:Instances!AG5),"median", MEDIAN(Instances!AG5:Instances!AG5),"min", MIN(Instances!AG5:Instances!AG5),"max", MAX(Instances!AG5:Instances!AG5),"diff", MAX(Instances!AG5:Instances!AG5)-MIN(Instances!AG5:Instances!AG5))</f>
+        <v>0</v>
+      </c>
+      <c r="AH5" s="1" cm="1">
+        <f t="array" ref="AH5">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AH5:Instances!AH5),"median", MEDIAN(Instances!AH5:Instances!AH5),"min", MIN(Instances!AH5:Instances!AH5),"max", MAX(Instances!AH5:Instances!AH5),"diff", MAX(Instances!AH5:Instances!AH5)-MIN(Instances!AH5:Instances!AH5))</f>
+        <v>0</v>
+      </c>
+      <c r="AI5" s="1" cm="1">
+        <f t="array" ref="AI5">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AI5:Instances!AI5),"median", MEDIAN(Instances!AI5:Instances!AI5),"min", MIN(Instances!AI5:Instances!AI5),"max", MAX(Instances!AI5:Instances!AI5),"diff", MAX(Instances!AI5:Instances!AI5)-MIN(Instances!AI5:Instances!AI5))</f>
+        <v>0</v>
+      </c>
       <c r="AJ5" s="1" cm="1">
         <f t="array" ref="AJ5">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AJ5:Instances!AJ5),"median", MEDIAN(Instances!AJ5:Instances!AJ5),"min", MIN(Instances!AJ5:Instances!AJ5),"max", MAX(Instances!AJ5:Instances!AJ5),"diff", MAX(Instances!AJ5:Instances!AJ5)-MIN(Instances!AJ5:Instances!AJ5))</f>
         <v>0</v>
@@ -4250,11 +5285,23 @@
         <f t="array" ref="AK5">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AK5:Instances!AK5),"median", MEDIAN(Instances!AK5:Instances!AK5),"min", MIN(Instances!AK5:Instances!AK5),"max", MAX(Instances!AK5:Instances!AK5),"diff", MAX(Instances!AK5:Instances!AK5)-MIN(Instances!AK5:Instances!AK5))</f>
         <v>0</v>
       </c>
-      <c r="AL5" s="1"/>
+      <c r="AL5" s="1" cm="1">
+        <f t="array" ref="AL5">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AL5:Instances!AL5),"median", MEDIAN(Instances!AL5:Instances!AL5),"min", MIN(Instances!AL5:Instances!AL5),"max", MAX(Instances!AL5:Instances!AL5),"diff", MAX(Instances!AL5:Instances!AL5)-MIN(Instances!AL5:Instances!AL5))</f>
+        <v>0</v>
+      </c>
       <c r="AM5" s="1"/>
-      <c r="AN5" s="1"/>
-      <c r="AO5" s="1"/>
-      <c r="AP5" s="1"/>
+      <c r="AN5" s="1" cm="1">
+        <f t="array" ref="AN5">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AN5:Instances!AN5),"median", MEDIAN(Instances!AN5:Instances!AN5),"min", MIN(Instances!AN5:Instances!AN5),"max", MAX(Instances!AN5:Instances!AN5),"diff", MAX(Instances!AN5:Instances!AN5)-MIN(Instances!AN5:Instances!AN5))</f>
+        <v>0</v>
+      </c>
+      <c r="AO5" s="1" cm="1">
+        <f t="array" ref="AO5">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AO5:Instances!AO5),"median", MEDIAN(Instances!AO5:Instances!AO5),"min", MIN(Instances!AO5:Instances!AO5),"max", MAX(Instances!AO5:Instances!AO5),"diff", MAX(Instances!AO5:Instances!AO5)-MIN(Instances!AO5:Instances!AO5))</f>
+        <v>0</v>
+      </c>
+      <c r="AP5" s="1" cm="1">
+        <f t="array" ref="AP5">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AP5:Instances!AP5),"median", MEDIAN(Instances!AP5:Instances!AP5),"min", MIN(Instances!AP5:Instances!AP5),"max", MAX(Instances!AP5:Instances!AP5),"diff", MAX(Instances!AP5:Instances!AP5)-MIN(Instances!AP5:Instances!AP5))</f>
+        <v>0</v>
+      </c>
       <c r="AQ5" s="1" cm="1">
         <f t="array" ref="AQ5">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AQ5:Instances!AQ5),"median", MEDIAN(Instances!AQ5:Instances!AQ5),"min", MIN(Instances!AQ5:Instances!AQ5),"max", MAX(Instances!AQ5:Instances!AQ5),"diff", MAX(Instances!AQ5:Instances!AQ5)-MIN(Instances!AQ5:Instances!AQ5))</f>
         <v>0</v>
@@ -4263,10 +5310,22 @@
         <f>MIN($B5,$I5,$P5,$W5,$AD5,$AK5)</f>
         <v>0</v>
       </c>
-      <c r="AS5" s="1"/>
-      <c r="AT5" s="1"/>
-      <c r="AU5" s="1"/>
-      <c r="AV5" s="1"/>
+      <c r="AS5" s="1">
+        <f>MIN($C5,$J5,$Q5,$X5,$AE5,$AL5)</f>
+        <v>0</v>
+      </c>
+      <c r="AT5" s="1">
+        <f>MIN($E5,$L5,$S5,$Z5,$AG5,$AN5)</f>
+        <v>0</v>
+      </c>
+      <c r="AU5" s="1">
+        <f>MIN($F5,$M5,$T5,$AA5,$AH5,$AO5)</f>
+        <v>0</v>
+      </c>
+      <c r="AV5" s="1">
+        <f>MIN($G5,$N5,$U5,$AB5,$AI5,$AP5)</f>
+        <v>0</v>
+      </c>
       <c r="AW5" s="1">
         <f>MIN($H5,$O5,$V5,$AC5,$AJ5,$AQ5)</f>
         <v>0</v>
@@ -4275,10 +5334,22 @@
         <f>MEDIAN($B5,$I5,$P5,$W5,$AD5,$AK5)</f>
         <v>0</v>
       </c>
-      <c r="AY5" s="1"/>
-      <c r="AZ5" s="1"/>
-      <c r="BA5" s="1"/>
-      <c r="BB5" s="1"/>
+      <c r="AY5" s="1">
+        <f>MEDIAN($C5,$J5,$Q5,$X5,$AE5,$AL5)</f>
+        <v>0</v>
+      </c>
+      <c r="AZ5" s="1">
+        <f>MEDIAN($E5,$L5,$S5,$Z5,$AG5,$AN5)</f>
+        <v>0</v>
+      </c>
+      <c r="BA5" s="1">
+        <f>MEDIAN($F5,$M5,$T5,$AA5,$AH5,$AO5)</f>
+        <v>0</v>
+      </c>
+      <c r="BB5" s="1">
+        <f>MEDIAN($G5,$N5,$U5,$AB5,$AI5,$AP5)</f>
+        <v>0</v>
+      </c>
       <c r="BC5" s="1">
         <f>MEDIAN($H5,$O5,$V5,$AC5,$AJ5,$AQ5)</f>
         <v>0</v>
@@ -4287,10 +5358,22 @@
         <f>MAX($B5,$I5,$P5,$W5,$AD5,$AK5)</f>
         <v>0</v>
       </c>
-      <c r="BE5" s="1"/>
-      <c r="BF5" s="1"/>
-      <c r="BG5" s="1"/>
-      <c r="BH5" s="1"/>
+      <c r="BE5" s="1">
+        <f>MAX($C5,$J5,$Q5,$X5,$AE5,$AL5)</f>
+        <v>0</v>
+      </c>
+      <c r="BF5" s="1">
+        <f>MAX($E5,$L5,$S5,$Z5,$AG5,$AN5)</f>
+        <v>0</v>
+      </c>
+      <c r="BG5" s="1">
+        <f>MAX($F5,$M5,$T5,$AA5,$AH5,$AO5)</f>
+        <v>0</v>
+      </c>
+      <c r="BH5" s="1">
+        <f>MAX($G5,$N5,$U5,$AB5,$AI5,$AP5)</f>
+        <v>0</v>
+      </c>
       <c r="BI5" s="1">
         <f>MAX($H5,$O5,$V5,$AC5,$AJ5,$AQ5)</f>
         <v>0</v>
@@ -4304,11 +5387,23 @@
         <f t="array" ref="B6">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!B6:Instances!B6),"median", MEDIAN(Instances!B6:Instances!B6),"min", MIN(Instances!B6:Instances!B6),"max", MAX(Instances!B6:Instances!B6),"diff", MAX(Instances!B6:Instances!B6)-MIN(Instances!B6:Instances!B6))</f>
         <v>0</v>
       </c>
-      <c r="C6" s="1"/>
+      <c r="C6" s="1" cm="1">
+        <f t="array" ref="C6">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!C6:Instances!C6),"median", MEDIAN(Instances!C6:Instances!C6),"min", MIN(Instances!C6:Instances!C6),"max", MAX(Instances!C6:Instances!C6),"diff", MAX(Instances!C6:Instances!C6)-MIN(Instances!C6:Instances!C6))</f>
+        <v>0</v>
+      </c>
       <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
+      <c r="E6" s="1" cm="1">
+        <f t="array" ref="E6">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!E6:Instances!E6),"median", MEDIAN(Instances!E6:Instances!E6),"min", MIN(Instances!E6:Instances!E6),"max", MAX(Instances!E6:Instances!E6),"diff", MAX(Instances!E6:Instances!E6)-MIN(Instances!E6:Instances!E6))</f>
+        <v>0</v>
+      </c>
+      <c r="F6" s="1" cm="1">
+        <f t="array" ref="F6">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!F6:Instances!F6),"median", MEDIAN(Instances!F6:Instances!F6),"min", MIN(Instances!F6:Instances!F6),"max", MAX(Instances!F6:Instances!F6),"diff", MAX(Instances!F6:Instances!F6)-MIN(Instances!F6:Instances!F6))</f>
+        <v>0</v>
+      </c>
+      <c r="G6" s="1" cm="1">
+        <f t="array" ref="G6">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!G6:Instances!G6),"median", MEDIAN(Instances!G6:Instances!G6),"min", MIN(Instances!G6:Instances!G6),"max", MAX(Instances!G6:Instances!G6),"diff", MAX(Instances!G6:Instances!G6)-MIN(Instances!G6:Instances!G6))</f>
+        <v>0</v>
+      </c>
       <c r="H6" s="1" cm="1">
         <f t="array" ref="H6">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!H6:Instances!H6),"median", MEDIAN(Instances!H6:Instances!H6),"min", MIN(Instances!H6:Instances!H6),"max", MAX(Instances!H6:Instances!H6),"diff", MAX(Instances!H6:Instances!H6)-MIN(Instances!H6:Instances!H6))</f>
         <v>0</v>
@@ -4317,11 +5412,23 @@
         <f t="array" ref="I6">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!I6:Instances!I6),"median", MEDIAN(Instances!I6:Instances!I6),"min", MIN(Instances!I6:Instances!I6),"max", MAX(Instances!I6:Instances!I6),"diff", MAX(Instances!I6:Instances!I6)-MIN(Instances!I6:Instances!I6))</f>
         <v>0</v>
       </c>
-      <c r="J6" s="1"/>
+      <c r="J6" s="1" cm="1">
+        <f t="array" ref="J6">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!J6:Instances!J6),"median", MEDIAN(Instances!J6:Instances!J6),"min", MIN(Instances!J6:Instances!J6),"max", MAX(Instances!J6:Instances!J6),"diff", MAX(Instances!J6:Instances!J6)-MIN(Instances!J6:Instances!J6))</f>
+        <v>0</v>
+      </c>
       <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="1"/>
+      <c r="L6" s="1" cm="1">
+        <f t="array" ref="L6">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!L6:Instances!L6),"median", MEDIAN(Instances!L6:Instances!L6),"min", MIN(Instances!L6:Instances!L6),"max", MAX(Instances!L6:Instances!L6),"diff", MAX(Instances!L6:Instances!L6)-MIN(Instances!L6:Instances!L6))</f>
+        <v>0</v>
+      </c>
+      <c r="M6" s="1" cm="1">
+        <f t="array" ref="M6">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!M6:Instances!M6),"median", MEDIAN(Instances!M6:Instances!M6),"min", MIN(Instances!M6:Instances!M6),"max", MAX(Instances!M6:Instances!M6),"diff", MAX(Instances!M6:Instances!M6)-MIN(Instances!M6:Instances!M6))</f>
+        <v>0</v>
+      </c>
+      <c r="N6" s="1" cm="1">
+        <f t="array" ref="N6">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!N6:Instances!N6),"median", MEDIAN(Instances!N6:Instances!N6),"min", MIN(Instances!N6:Instances!N6),"max", MAX(Instances!N6:Instances!N6),"diff", MAX(Instances!N6:Instances!N6)-MIN(Instances!N6:Instances!N6))</f>
+        <v>0</v>
+      </c>
       <c r="O6" s="1" cm="1">
         <f t="array" ref="O6">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!O6:Instances!O6),"median", MEDIAN(Instances!O6:Instances!O6),"min", MIN(Instances!O6:Instances!O6),"max", MAX(Instances!O6:Instances!O6),"diff", MAX(Instances!O6:Instances!O6)-MIN(Instances!O6:Instances!O6))</f>
         <v>0</v>
@@ -4330,11 +5437,23 @@
         <f t="array" ref="P6">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!P6:Instances!P6),"median", MEDIAN(Instances!P6:Instances!P6),"min", MIN(Instances!P6:Instances!P6),"max", MAX(Instances!P6:Instances!P6),"diff", MAX(Instances!P6:Instances!P6)-MIN(Instances!P6:Instances!P6))</f>
         <v>0</v>
       </c>
-      <c r="Q6" s="1"/>
+      <c r="Q6" s="1" cm="1">
+        <f t="array" ref="Q6">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!Q6:Instances!Q6),"median", MEDIAN(Instances!Q6:Instances!Q6),"min", MIN(Instances!Q6:Instances!Q6),"max", MAX(Instances!Q6:Instances!Q6),"diff", MAX(Instances!Q6:Instances!Q6)-MIN(Instances!Q6:Instances!Q6))</f>
+        <v>0</v>
+      </c>
       <c r="R6" s="1"/>
-      <c r="S6" s="1"/>
-      <c r="T6" s="1"/>
-      <c r="U6" s="1"/>
+      <c r="S6" s="1" cm="1">
+        <f t="array" ref="S6">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!S6:Instances!S6),"median", MEDIAN(Instances!S6:Instances!S6),"min", MIN(Instances!S6:Instances!S6),"max", MAX(Instances!S6:Instances!S6),"diff", MAX(Instances!S6:Instances!S6)-MIN(Instances!S6:Instances!S6))</f>
+        <v>0</v>
+      </c>
+      <c r="T6" s="1" cm="1">
+        <f t="array" ref="T6">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!T6:Instances!T6),"median", MEDIAN(Instances!T6:Instances!T6),"min", MIN(Instances!T6:Instances!T6),"max", MAX(Instances!T6:Instances!T6),"diff", MAX(Instances!T6:Instances!T6)-MIN(Instances!T6:Instances!T6))</f>
+        <v>0</v>
+      </c>
+      <c r="U6" s="1" cm="1">
+        <f t="array" ref="U6">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!U6:Instances!U6),"median", MEDIAN(Instances!U6:Instances!U6),"min", MIN(Instances!U6:Instances!U6),"max", MAX(Instances!U6:Instances!U6),"diff", MAX(Instances!U6:Instances!U6)-MIN(Instances!U6:Instances!U6))</f>
+        <v>0</v>
+      </c>
       <c r="V6" s="1" cm="1">
         <f t="array" ref="V6">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!V6:Instances!V6),"median", MEDIAN(Instances!V6:Instances!V6),"min", MIN(Instances!V6:Instances!V6),"max", MAX(Instances!V6:Instances!V6),"diff", MAX(Instances!V6:Instances!V6)-MIN(Instances!V6:Instances!V6))</f>
         <v>0</v>
@@ -4343,11 +5462,23 @@
         <f t="array" ref="W6">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!W6:Instances!W6),"median", MEDIAN(Instances!W6:Instances!W6),"min", MIN(Instances!W6:Instances!W6),"max", MAX(Instances!W6:Instances!W6),"diff", MAX(Instances!W6:Instances!W6)-MIN(Instances!W6:Instances!W6))</f>
         <v>0</v>
       </c>
-      <c r="X6" s="1"/>
+      <c r="X6" s="1" cm="1">
+        <f t="array" ref="X6">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!X6:Instances!X6),"median", MEDIAN(Instances!X6:Instances!X6),"min", MIN(Instances!X6:Instances!X6),"max", MAX(Instances!X6:Instances!X6),"diff", MAX(Instances!X6:Instances!X6)-MIN(Instances!X6:Instances!X6))</f>
+        <v>0</v>
+      </c>
       <c r="Y6" s="1"/>
-      <c r="Z6" s="1"/>
-      <c r="AA6" s="1"/>
-      <c r="AB6" s="1"/>
+      <c r="Z6" s="1" cm="1">
+        <f t="array" ref="Z6">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!Z6:Instances!Z6),"median", MEDIAN(Instances!Z6:Instances!Z6),"min", MIN(Instances!Z6:Instances!Z6),"max", MAX(Instances!Z6:Instances!Z6),"diff", MAX(Instances!Z6:Instances!Z6)-MIN(Instances!Z6:Instances!Z6))</f>
+        <v>0</v>
+      </c>
+      <c r="AA6" s="1" cm="1">
+        <f t="array" ref="AA6">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AA6:Instances!AA6),"median", MEDIAN(Instances!AA6:Instances!AA6),"min", MIN(Instances!AA6:Instances!AA6),"max", MAX(Instances!AA6:Instances!AA6),"diff", MAX(Instances!AA6:Instances!AA6)-MIN(Instances!AA6:Instances!AA6))</f>
+        <v>0</v>
+      </c>
+      <c r="AB6" s="1" cm="1">
+        <f t="array" ref="AB6">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AB6:Instances!AB6),"median", MEDIAN(Instances!AB6:Instances!AB6),"min", MIN(Instances!AB6:Instances!AB6),"max", MAX(Instances!AB6:Instances!AB6),"diff", MAX(Instances!AB6:Instances!AB6)-MIN(Instances!AB6:Instances!AB6))</f>
+        <v>0</v>
+      </c>
       <c r="AC6" s="1" cm="1">
         <f t="array" ref="AC6">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AC6:Instances!AC6),"median", MEDIAN(Instances!AC6:Instances!AC6),"min", MIN(Instances!AC6:Instances!AC6),"max", MAX(Instances!AC6:Instances!AC6),"diff", MAX(Instances!AC6:Instances!AC6)-MIN(Instances!AC6:Instances!AC6))</f>
         <v>0</v>
@@ -4356,11 +5487,23 @@
         <f t="array" ref="AD6">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AD6:Instances!AD6),"median", MEDIAN(Instances!AD6:Instances!AD6),"min", MIN(Instances!AD6:Instances!AD6),"max", MAX(Instances!AD6:Instances!AD6),"diff", MAX(Instances!AD6:Instances!AD6)-MIN(Instances!AD6:Instances!AD6))</f>
         <v>0</v>
       </c>
-      <c r="AE6" s="1"/>
+      <c r="AE6" s="1" cm="1">
+        <f t="array" ref="AE6">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AE6:Instances!AE6),"median", MEDIAN(Instances!AE6:Instances!AE6),"min", MIN(Instances!AE6:Instances!AE6),"max", MAX(Instances!AE6:Instances!AE6),"diff", MAX(Instances!AE6:Instances!AE6)-MIN(Instances!AE6:Instances!AE6))</f>
+        <v>0</v>
+      </c>
       <c r="AF6" s="1"/>
-      <c r="AG6" s="1"/>
-      <c r="AH6" s="1"/>
-      <c r="AI6" s="1"/>
+      <c r="AG6" s="1" cm="1">
+        <f t="array" ref="AG6">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AG6:Instances!AG6),"median", MEDIAN(Instances!AG6:Instances!AG6),"min", MIN(Instances!AG6:Instances!AG6),"max", MAX(Instances!AG6:Instances!AG6),"diff", MAX(Instances!AG6:Instances!AG6)-MIN(Instances!AG6:Instances!AG6))</f>
+        <v>0</v>
+      </c>
+      <c r="AH6" s="1" cm="1">
+        <f t="array" ref="AH6">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AH6:Instances!AH6),"median", MEDIAN(Instances!AH6:Instances!AH6),"min", MIN(Instances!AH6:Instances!AH6),"max", MAX(Instances!AH6:Instances!AH6),"diff", MAX(Instances!AH6:Instances!AH6)-MIN(Instances!AH6:Instances!AH6))</f>
+        <v>0</v>
+      </c>
+      <c r="AI6" s="1" cm="1">
+        <f t="array" ref="AI6">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AI6:Instances!AI6),"median", MEDIAN(Instances!AI6:Instances!AI6),"min", MIN(Instances!AI6:Instances!AI6),"max", MAX(Instances!AI6:Instances!AI6),"diff", MAX(Instances!AI6:Instances!AI6)-MIN(Instances!AI6:Instances!AI6))</f>
+        <v>0</v>
+      </c>
       <c r="AJ6" s="1" cm="1">
         <f t="array" ref="AJ6">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AJ6:Instances!AJ6),"median", MEDIAN(Instances!AJ6:Instances!AJ6),"min", MIN(Instances!AJ6:Instances!AJ6),"max", MAX(Instances!AJ6:Instances!AJ6),"diff", MAX(Instances!AJ6:Instances!AJ6)-MIN(Instances!AJ6:Instances!AJ6))</f>
         <v>0</v>
@@ -4369,11 +5512,23 @@
         <f t="array" ref="AK6">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AK6:Instances!AK6),"median", MEDIAN(Instances!AK6:Instances!AK6),"min", MIN(Instances!AK6:Instances!AK6),"max", MAX(Instances!AK6:Instances!AK6),"diff", MAX(Instances!AK6:Instances!AK6)-MIN(Instances!AK6:Instances!AK6))</f>
         <v>0</v>
       </c>
-      <c r="AL6" s="1"/>
+      <c r="AL6" s="1" cm="1">
+        <f t="array" ref="AL6">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AL6:Instances!AL6),"median", MEDIAN(Instances!AL6:Instances!AL6),"min", MIN(Instances!AL6:Instances!AL6),"max", MAX(Instances!AL6:Instances!AL6),"diff", MAX(Instances!AL6:Instances!AL6)-MIN(Instances!AL6:Instances!AL6))</f>
+        <v>0</v>
+      </c>
       <c r="AM6" s="1"/>
-      <c r="AN6" s="1"/>
-      <c r="AO6" s="1"/>
-      <c r="AP6" s="1"/>
+      <c r="AN6" s="1" cm="1">
+        <f t="array" ref="AN6">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AN6:Instances!AN6),"median", MEDIAN(Instances!AN6:Instances!AN6),"min", MIN(Instances!AN6:Instances!AN6),"max", MAX(Instances!AN6:Instances!AN6),"diff", MAX(Instances!AN6:Instances!AN6)-MIN(Instances!AN6:Instances!AN6))</f>
+        <v>0</v>
+      </c>
+      <c r="AO6" s="1" cm="1">
+        <f t="array" ref="AO6">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AO6:Instances!AO6),"median", MEDIAN(Instances!AO6:Instances!AO6),"min", MIN(Instances!AO6:Instances!AO6),"max", MAX(Instances!AO6:Instances!AO6),"diff", MAX(Instances!AO6:Instances!AO6)-MIN(Instances!AO6:Instances!AO6))</f>
+        <v>0</v>
+      </c>
+      <c r="AP6" s="1" cm="1">
+        <f t="array" ref="AP6">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AP6:Instances!AP6),"median", MEDIAN(Instances!AP6:Instances!AP6),"min", MIN(Instances!AP6:Instances!AP6),"max", MAX(Instances!AP6:Instances!AP6),"diff", MAX(Instances!AP6:Instances!AP6)-MIN(Instances!AP6:Instances!AP6))</f>
+        <v>0</v>
+      </c>
       <c r="AQ6" s="1" cm="1">
         <f t="array" ref="AQ6">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AQ6:Instances!AQ6),"median", MEDIAN(Instances!AQ6:Instances!AQ6),"min", MIN(Instances!AQ6:Instances!AQ6),"max", MAX(Instances!AQ6:Instances!AQ6),"diff", MAX(Instances!AQ6:Instances!AQ6)-MIN(Instances!AQ6:Instances!AQ6))</f>
         <v>0</v>
@@ -4382,10 +5537,22 @@
         <f>MIN($B6,$I6,$P6,$W6,$AD6,$AK6)</f>
         <v>0</v>
       </c>
-      <c r="AS6" s="1"/>
-      <c r="AT6" s="1"/>
-      <c r="AU6" s="1"/>
-      <c r="AV6" s="1"/>
+      <c r="AS6" s="1">
+        <f>MIN($C6,$J6,$Q6,$X6,$AE6,$AL6)</f>
+        <v>0</v>
+      </c>
+      <c r="AT6" s="1">
+        <f>MIN($E6,$L6,$S6,$Z6,$AG6,$AN6)</f>
+        <v>0</v>
+      </c>
+      <c r="AU6" s="1">
+        <f>MIN($F6,$M6,$T6,$AA6,$AH6,$AO6)</f>
+        <v>0</v>
+      </c>
+      <c r="AV6" s="1">
+        <f>MIN($G6,$N6,$U6,$AB6,$AI6,$AP6)</f>
+        <v>0</v>
+      </c>
       <c r="AW6" s="1">
         <f>MIN($H6,$O6,$V6,$AC6,$AJ6,$AQ6)</f>
         <v>0</v>
@@ -4394,10 +5561,22 @@
         <f>MEDIAN($B6,$I6,$P6,$W6,$AD6,$AK6)</f>
         <v>0</v>
       </c>
-      <c r="AY6" s="1"/>
-      <c r="AZ6" s="1"/>
-      <c r="BA6" s="1"/>
-      <c r="BB6" s="1"/>
+      <c r="AY6" s="1">
+        <f>MEDIAN($C6,$J6,$Q6,$X6,$AE6,$AL6)</f>
+        <v>0</v>
+      </c>
+      <c r="AZ6" s="1">
+        <f>MEDIAN($E6,$L6,$S6,$Z6,$AG6,$AN6)</f>
+        <v>0</v>
+      </c>
+      <c r="BA6" s="1">
+        <f>MEDIAN($F6,$M6,$T6,$AA6,$AH6,$AO6)</f>
+        <v>0</v>
+      </c>
+      <c r="BB6" s="1">
+        <f>MEDIAN($G6,$N6,$U6,$AB6,$AI6,$AP6)</f>
+        <v>0</v>
+      </c>
       <c r="BC6" s="1">
         <f>MEDIAN($H6,$O6,$V6,$AC6,$AJ6,$AQ6)</f>
         <v>0</v>
@@ -4406,10 +5585,22 @@
         <f>MAX($B6,$I6,$P6,$W6,$AD6,$AK6)</f>
         <v>0</v>
       </c>
-      <c r="BE6" s="1"/>
-      <c r="BF6" s="1"/>
-      <c r="BG6" s="1"/>
-      <c r="BH6" s="1"/>
+      <c r="BE6" s="1">
+        <f>MAX($C6,$J6,$Q6,$X6,$AE6,$AL6)</f>
+        <v>0</v>
+      </c>
+      <c r="BF6" s="1">
+        <f>MAX($E6,$L6,$S6,$Z6,$AG6,$AN6)</f>
+        <v>0</v>
+      </c>
+      <c r="BG6" s="1">
+        <f>MAX($F6,$M6,$T6,$AA6,$AH6,$AO6)</f>
+        <v>0</v>
+      </c>
+      <c r="BH6" s="1">
+        <f>MAX($G6,$N6,$U6,$AB6,$AI6,$AP6)</f>
+        <v>0</v>
+      </c>
       <c r="BI6" s="1">
         <f>MAX($H6,$O6,$V6,$AC6,$AJ6,$AQ6)</f>
         <v>0</v>
@@ -4423,11 +5614,23 @@
         <f t="array" ref="B7">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!B7:Instances!B7),"median", MEDIAN(Instances!B7:Instances!B7),"min", MIN(Instances!B7:Instances!B7),"max", MAX(Instances!B7:Instances!B7),"diff", MAX(Instances!B7:Instances!B7)-MIN(Instances!B7:Instances!B7))</f>
         <v>0</v>
       </c>
-      <c r="C7" s="1"/>
+      <c r="C7" s="1" cm="1">
+        <f t="array" ref="C7">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!C7:Instances!C7),"median", MEDIAN(Instances!C7:Instances!C7),"min", MIN(Instances!C7:Instances!C7),"max", MAX(Instances!C7:Instances!C7),"diff", MAX(Instances!C7:Instances!C7)-MIN(Instances!C7:Instances!C7))</f>
+        <v>0</v>
+      </c>
       <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
+      <c r="E7" s="1" cm="1">
+        <f t="array" ref="E7">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!E7:Instances!E7),"median", MEDIAN(Instances!E7:Instances!E7),"min", MIN(Instances!E7:Instances!E7),"max", MAX(Instances!E7:Instances!E7),"diff", MAX(Instances!E7:Instances!E7)-MIN(Instances!E7:Instances!E7))</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="1" cm="1">
+        <f t="array" ref="F7">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!F7:Instances!F7),"median", MEDIAN(Instances!F7:Instances!F7),"min", MIN(Instances!F7:Instances!F7),"max", MAX(Instances!F7:Instances!F7),"diff", MAX(Instances!F7:Instances!F7)-MIN(Instances!F7:Instances!F7))</f>
+        <v>0</v>
+      </c>
+      <c r="G7" s="1" cm="1">
+        <f t="array" ref="G7">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!G7:Instances!G7),"median", MEDIAN(Instances!G7:Instances!G7),"min", MIN(Instances!G7:Instances!G7),"max", MAX(Instances!G7:Instances!G7),"diff", MAX(Instances!G7:Instances!G7)-MIN(Instances!G7:Instances!G7))</f>
+        <v>0</v>
+      </c>
       <c r="H7" s="1" cm="1">
         <f t="array" ref="H7">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!H7:Instances!H7),"median", MEDIAN(Instances!H7:Instances!H7),"min", MIN(Instances!H7:Instances!H7),"max", MAX(Instances!H7:Instances!H7),"diff", MAX(Instances!H7:Instances!H7)-MIN(Instances!H7:Instances!H7))</f>
         <v>0</v>
@@ -4436,11 +5639,23 @@
         <f t="array" ref="I7">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!I7:Instances!I7),"median", MEDIAN(Instances!I7:Instances!I7),"min", MIN(Instances!I7:Instances!I7),"max", MAX(Instances!I7:Instances!I7),"diff", MAX(Instances!I7:Instances!I7)-MIN(Instances!I7:Instances!I7))</f>
         <v>0</v>
       </c>
-      <c r="J7" s="1"/>
+      <c r="J7" s="1" cm="1">
+        <f t="array" ref="J7">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!J7:Instances!J7),"median", MEDIAN(Instances!J7:Instances!J7),"min", MIN(Instances!J7:Instances!J7),"max", MAX(Instances!J7:Instances!J7),"diff", MAX(Instances!J7:Instances!J7)-MIN(Instances!J7:Instances!J7))</f>
+        <v>0</v>
+      </c>
       <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
-      <c r="N7" s="1"/>
+      <c r="L7" s="1" cm="1">
+        <f t="array" ref="L7">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!L7:Instances!L7),"median", MEDIAN(Instances!L7:Instances!L7),"min", MIN(Instances!L7:Instances!L7),"max", MAX(Instances!L7:Instances!L7),"diff", MAX(Instances!L7:Instances!L7)-MIN(Instances!L7:Instances!L7))</f>
+        <v>0</v>
+      </c>
+      <c r="M7" s="1" cm="1">
+        <f t="array" ref="M7">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!M7:Instances!M7),"median", MEDIAN(Instances!M7:Instances!M7),"min", MIN(Instances!M7:Instances!M7),"max", MAX(Instances!M7:Instances!M7),"diff", MAX(Instances!M7:Instances!M7)-MIN(Instances!M7:Instances!M7))</f>
+        <v>0</v>
+      </c>
+      <c r="N7" s="1" cm="1">
+        <f t="array" ref="N7">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!N7:Instances!N7),"median", MEDIAN(Instances!N7:Instances!N7),"min", MIN(Instances!N7:Instances!N7),"max", MAX(Instances!N7:Instances!N7),"diff", MAX(Instances!N7:Instances!N7)-MIN(Instances!N7:Instances!N7))</f>
+        <v>0</v>
+      </c>
       <c r="O7" s="1" cm="1">
         <f t="array" ref="O7">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!O7:Instances!O7),"median", MEDIAN(Instances!O7:Instances!O7),"min", MIN(Instances!O7:Instances!O7),"max", MAX(Instances!O7:Instances!O7),"diff", MAX(Instances!O7:Instances!O7)-MIN(Instances!O7:Instances!O7))</f>
         <v>0</v>
@@ -4449,11 +5664,23 @@
         <f t="array" ref="P7">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!P7:Instances!P7),"median", MEDIAN(Instances!P7:Instances!P7),"min", MIN(Instances!P7:Instances!P7),"max", MAX(Instances!P7:Instances!P7),"diff", MAX(Instances!P7:Instances!P7)-MIN(Instances!P7:Instances!P7))</f>
         <v>0</v>
       </c>
-      <c r="Q7" s="1"/>
+      <c r="Q7" s="1" cm="1">
+        <f t="array" ref="Q7">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!Q7:Instances!Q7),"median", MEDIAN(Instances!Q7:Instances!Q7),"min", MIN(Instances!Q7:Instances!Q7),"max", MAX(Instances!Q7:Instances!Q7),"diff", MAX(Instances!Q7:Instances!Q7)-MIN(Instances!Q7:Instances!Q7))</f>
+        <v>0</v>
+      </c>
       <c r="R7" s="1"/>
-      <c r="S7" s="1"/>
-      <c r="T7" s="1"/>
-      <c r="U7" s="1"/>
+      <c r="S7" s="1" cm="1">
+        <f t="array" ref="S7">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!S7:Instances!S7),"median", MEDIAN(Instances!S7:Instances!S7),"min", MIN(Instances!S7:Instances!S7),"max", MAX(Instances!S7:Instances!S7),"diff", MAX(Instances!S7:Instances!S7)-MIN(Instances!S7:Instances!S7))</f>
+        <v>0</v>
+      </c>
+      <c r="T7" s="1" cm="1">
+        <f t="array" ref="T7">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!T7:Instances!T7),"median", MEDIAN(Instances!T7:Instances!T7),"min", MIN(Instances!T7:Instances!T7),"max", MAX(Instances!T7:Instances!T7),"diff", MAX(Instances!T7:Instances!T7)-MIN(Instances!T7:Instances!T7))</f>
+        <v>0</v>
+      </c>
+      <c r="U7" s="1" cm="1">
+        <f t="array" ref="U7">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!U7:Instances!U7),"median", MEDIAN(Instances!U7:Instances!U7),"min", MIN(Instances!U7:Instances!U7),"max", MAX(Instances!U7:Instances!U7),"diff", MAX(Instances!U7:Instances!U7)-MIN(Instances!U7:Instances!U7))</f>
+        <v>0</v>
+      </c>
       <c r="V7" s="1" cm="1">
         <f t="array" ref="V7">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!V7:Instances!V7),"median", MEDIAN(Instances!V7:Instances!V7),"min", MIN(Instances!V7:Instances!V7),"max", MAX(Instances!V7:Instances!V7),"diff", MAX(Instances!V7:Instances!V7)-MIN(Instances!V7:Instances!V7))</f>
         <v>0</v>
@@ -4462,11 +5689,23 @@
         <f t="array" ref="W7">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!W7:Instances!W7),"median", MEDIAN(Instances!W7:Instances!W7),"min", MIN(Instances!W7:Instances!W7),"max", MAX(Instances!W7:Instances!W7),"diff", MAX(Instances!W7:Instances!W7)-MIN(Instances!W7:Instances!W7))</f>
         <v>0</v>
       </c>
-      <c r="X7" s="1"/>
+      <c r="X7" s="1" cm="1">
+        <f t="array" ref="X7">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!X7:Instances!X7),"median", MEDIAN(Instances!X7:Instances!X7),"min", MIN(Instances!X7:Instances!X7),"max", MAX(Instances!X7:Instances!X7),"diff", MAX(Instances!X7:Instances!X7)-MIN(Instances!X7:Instances!X7))</f>
+        <v>0</v>
+      </c>
       <c r="Y7" s="1"/>
-      <c r="Z7" s="1"/>
-      <c r="AA7" s="1"/>
-      <c r="AB7" s="1"/>
+      <c r="Z7" s="1" cm="1">
+        <f t="array" ref="Z7">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!Z7:Instances!Z7),"median", MEDIAN(Instances!Z7:Instances!Z7),"min", MIN(Instances!Z7:Instances!Z7),"max", MAX(Instances!Z7:Instances!Z7),"diff", MAX(Instances!Z7:Instances!Z7)-MIN(Instances!Z7:Instances!Z7))</f>
+        <v>0</v>
+      </c>
+      <c r="AA7" s="1" cm="1">
+        <f t="array" ref="AA7">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AA7:Instances!AA7),"median", MEDIAN(Instances!AA7:Instances!AA7),"min", MIN(Instances!AA7:Instances!AA7),"max", MAX(Instances!AA7:Instances!AA7),"diff", MAX(Instances!AA7:Instances!AA7)-MIN(Instances!AA7:Instances!AA7))</f>
+        <v>0</v>
+      </c>
+      <c r="AB7" s="1" cm="1">
+        <f t="array" ref="AB7">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AB7:Instances!AB7),"median", MEDIAN(Instances!AB7:Instances!AB7),"min", MIN(Instances!AB7:Instances!AB7),"max", MAX(Instances!AB7:Instances!AB7),"diff", MAX(Instances!AB7:Instances!AB7)-MIN(Instances!AB7:Instances!AB7))</f>
+        <v>0</v>
+      </c>
       <c r="AC7" s="1" cm="1">
         <f t="array" ref="AC7">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AC7:Instances!AC7),"median", MEDIAN(Instances!AC7:Instances!AC7),"min", MIN(Instances!AC7:Instances!AC7),"max", MAX(Instances!AC7:Instances!AC7),"diff", MAX(Instances!AC7:Instances!AC7)-MIN(Instances!AC7:Instances!AC7))</f>
         <v>0</v>
@@ -4475,11 +5714,23 @@
         <f t="array" ref="AD7">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AD7:Instances!AD7),"median", MEDIAN(Instances!AD7:Instances!AD7),"min", MIN(Instances!AD7:Instances!AD7),"max", MAX(Instances!AD7:Instances!AD7),"diff", MAX(Instances!AD7:Instances!AD7)-MIN(Instances!AD7:Instances!AD7))</f>
         <v>0</v>
       </c>
-      <c r="AE7" s="1"/>
+      <c r="AE7" s="1" cm="1">
+        <f t="array" ref="AE7">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AE7:Instances!AE7),"median", MEDIAN(Instances!AE7:Instances!AE7),"min", MIN(Instances!AE7:Instances!AE7),"max", MAX(Instances!AE7:Instances!AE7),"diff", MAX(Instances!AE7:Instances!AE7)-MIN(Instances!AE7:Instances!AE7))</f>
+        <v>0</v>
+      </c>
       <c r="AF7" s="1"/>
-      <c r="AG7" s="1"/>
-      <c r="AH7" s="1"/>
-      <c r="AI7" s="1"/>
+      <c r="AG7" s="1" cm="1">
+        <f t="array" ref="AG7">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AG7:Instances!AG7),"median", MEDIAN(Instances!AG7:Instances!AG7),"min", MIN(Instances!AG7:Instances!AG7),"max", MAX(Instances!AG7:Instances!AG7),"diff", MAX(Instances!AG7:Instances!AG7)-MIN(Instances!AG7:Instances!AG7))</f>
+        <v>0</v>
+      </c>
+      <c r="AH7" s="1" cm="1">
+        <f t="array" ref="AH7">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AH7:Instances!AH7),"median", MEDIAN(Instances!AH7:Instances!AH7),"min", MIN(Instances!AH7:Instances!AH7),"max", MAX(Instances!AH7:Instances!AH7),"diff", MAX(Instances!AH7:Instances!AH7)-MIN(Instances!AH7:Instances!AH7))</f>
+        <v>0</v>
+      </c>
+      <c r="AI7" s="1" cm="1">
+        <f t="array" ref="AI7">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AI7:Instances!AI7),"median", MEDIAN(Instances!AI7:Instances!AI7),"min", MIN(Instances!AI7:Instances!AI7),"max", MAX(Instances!AI7:Instances!AI7),"diff", MAX(Instances!AI7:Instances!AI7)-MIN(Instances!AI7:Instances!AI7))</f>
+        <v>0</v>
+      </c>
       <c r="AJ7" s="1" cm="1">
         <f t="array" ref="AJ7">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AJ7:Instances!AJ7),"median", MEDIAN(Instances!AJ7:Instances!AJ7),"min", MIN(Instances!AJ7:Instances!AJ7),"max", MAX(Instances!AJ7:Instances!AJ7),"diff", MAX(Instances!AJ7:Instances!AJ7)-MIN(Instances!AJ7:Instances!AJ7))</f>
         <v>0</v>
@@ -4488,11 +5739,23 @@
         <f t="array" ref="AK7">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AK7:Instances!AK7),"median", MEDIAN(Instances!AK7:Instances!AK7),"min", MIN(Instances!AK7:Instances!AK7),"max", MAX(Instances!AK7:Instances!AK7),"diff", MAX(Instances!AK7:Instances!AK7)-MIN(Instances!AK7:Instances!AK7))</f>
         <v>0</v>
       </c>
-      <c r="AL7" s="1"/>
+      <c r="AL7" s="1" cm="1">
+        <f t="array" ref="AL7">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AL7:Instances!AL7),"median", MEDIAN(Instances!AL7:Instances!AL7),"min", MIN(Instances!AL7:Instances!AL7),"max", MAX(Instances!AL7:Instances!AL7),"diff", MAX(Instances!AL7:Instances!AL7)-MIN(Instances!AL7:Instances!AL7))</f>
+        <v>0</v>
+      </c>
       <c r="AM7" s="1"/>
-      <c r="AN7" s="1"/>
-      <c r="AO7" s="1"/>
-      <c r="AP7" s="1"/>
+      <c r="AN7" s="1" cm="1">
+        <f t="array" ref="AN7">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AN7:Instances!AN7),"median", MEDIAN(Instances!AN7:Instances!AN7),"min", MIN(Instances!AN7:Instances!AN7),"max", MAX(Instances!AN7:Instances!AN7),"diff", MAX(Instances!AN7:Instances!AN7)-MIN(Instances!AN7:Instances!AN7))</f>
+        <v>0</v>
+      </c>
+      <c r="AO7" s="1" cm="1">
+        <f t="array" ref="AO7">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AO7:Instances!AO7),"median", MEDIAN(Instances!AO7:Instances!AO7),"min", MIN(Instances!AO7:Instances!AO7),"max", MAX(Instances!AO7:Instances!AO7),"diff", MAX(Instances!AO7:Instances!AO7)-MIN(Instances!AO7:Instances!AO7))</f>
+        <v>0</v>
+      </c>
+      <c r="AP7" s="1" cm="1">
+        <f t="array" ref="AP7">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AP7:Instances!AP7),"median", MEDIAN(Instances!AP7:Instances!AP7),"min", MIN(Instances!AP7:Instances!AP7),"max", MAX(Instances!AP7:Instances!AP7),"diff", MAX(Instances!AP7:Instances!AP7)-MIN(Instances!AP7:Instances!AP7))</f>
+        <v>0</v>
+      </c>
       <c r="AQ7" s="1" cm="1">
         <f t="array" ref="AQ7">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AQ7:Instances!AQ7),"median", MEDIAN(Instances!AQ7:Instances!AQ7),"min", MIN(Instances!AQ7:Instances!AQ7),"max", MAX(Instances!AQ7:Instances!AQ7),"diff", MAX(Instances!AQ7:Instances!AQ7)-MIN(Instances!AQ7:Instances!AQ7))</f>
         <v>0</v>
@@ -4501,10 +5764,22 @@
         <f>MIN($B7,$I7,$P7,$W7,$AD7,$AK7)</f>
         <v>0</v>
       </c>
-      <c r="AS7" s="1"/>
-      <c r="AT7" s="1"/>
-      <c r="AU7" s="1"/>
-      <c r="AV7" s="1"/>
+      <c r="AS7" s="1">
+        <f>MIN($C7,$J7,$Q7,$X7,$AE7,$AL7)</f>
+        <v>0</v>
+      </c>
+      <c r="AT7" s="1">
+        <f>MIN($E7,$L7,$S7,$Z7,$AG7,$AN7)</f>
+        <v>0</v>
+      </c>
+      <c r="AU7" s="1">
+        <f>MIN($F7,$M7,$T7,$AA7,$AH7,$AO7)</f>
+        <v>0</v>
+      </c>
+      <c r="AV7" s="1">
+        <f>MIN($G7,$N7,$U7,$AB7,$AI7,$AP7)</f>
+        <v>0</v>
+      </c>
       <c r="AW7" s="1">
         <f>MIN($H7,$O7,$V7,$AC7,$AJ7,$AQ7)</f>
         <v>0</v>
@@ -4513,10 +5788,22 @@
         <f>MEDIAN($B7,$I7,$P7,$W7,$AD7,$AK7)</f>
         <v>0</v>
       </c>
-      <c r="AY7" s="1"/>
-      <c r="AZ7" s="1"/>
-      <c r="BA7" s="1"/>
-      <c r="BB7" s="1"/>
+      <c r="AY7" s="1">
+        <f>MEDIAN($C7,$J7,$Q7,$X7,$AE7,$AL7)</f>
+        <v>0</v>
+      </c>
+      <c r="AZ7" s="1">
+        <f>MEDIAN($E7,$L7,$S7,$Z7,$AG7,$AN7)</f>
+        <v>0</v>
+      </c>
+      <c r="BA7" s="1">
+        <f>MEDIAN($F7,$M7,$T7,$AA7,$AH7,$AO7)</f>
+        <v>0</v>
+      </c>
+      <c r="BB7" s="1">
+        <f>MEDIAN($G7,$N7,$U7,$AB7,$AI7,$AP7)</f>
+        <v>0</v>
+      </c>
       <c r="BC7" s="1">
         <f>MEDIAN($H7,$O7,$V7,$AC7,$AJ7,$AQ7)</f>
         <v>0</v>
@@ -4525,10 +5812,22 @@
         <f>MAX($B7,$I7,$P7,$W7,$AD7,$AK7)</f>
         <v>0</v>
       </c>
-      <c r="BE7" s="1"/>
-      <c r="BF7" s="1"/>
-      <c r="BG7" s="1"/>
-      <c r="BH7" s="1"/>
+      <c r="BE7" s="1">
+        <f>MAX($C7,$J7,$Q7,$X7,$AE7,$AL7)</f>
+        <v>0</v>
+      </c>
+      <c r="BF7" s="1">
+        <f>MAX($E7,$L7,$S7,$Z7,$AG7,$AN7)</f>
+        <v>0</v>
+      </c>
+      <c r="BG7" s="1">
+        <f>MAX($F7,$M7,$T7,$AA7,$AH7,$AO7)</f>
+        <v>0</v>
+      </c>
+      <c r="BH7" s="1">
+        <f>MAX($G7,$N7,$U7,$AB7,$AI7,$AP7)</f>
+        <v>0</v>
+      </c>
       <c r="BI7" s="1">
         <f>MAX($H7,$O7,$V7,$AC7,$AJ7,$AQ7)</f>
         <v>0</v>
@@ -4542,11 +5841,23 @@
         <f t="array" ref="B8">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!B8:Instances!B8),"median", MEDIAN(Instances!B8:Instances!B8),"min", MIN(Instances!B8:Instances!B8),"max", MAX(Instances!B8:Instances!B8),"diff", MAX(Instances!B8:Instances!B8)-MIN(Instances!B8:Instances!B8))</f>
         <v>0</v>
       </c>
-      <c r="C8" s="1"/>
+      <c r="C8" s="1" cm="1">
+        <f t="array" ref="C8">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!C8:Instances!C8),"median", MEDIAN(Instances!C8:Instances!C8),"min", MIN(Instances!C8:Instances!C8),"max", MAX(Instances!C8:Instances!C8),"diff", MAX(Instances!C8:Instances!C8)-MIN(Instances!C8:Instances!C8))</f>
+        <v>0</v>
+      </c>
       <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
+      <c r="E8" s="1" cm="1">
+        <f t="array" ref="E8">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!E8:Instances!E8),"median", MEDIAN(Instances!E8:Instances!E8),"min", MIN(Instances!E8:Instances!E8),"max", MAX(Instances!E8:Instances!E8),"diff", MAX(Instances!E8:Instances!E8)-MIN(Instances!E8:Instances!E8))</f>
+        <v>0</v>
+      </c>
+      <c r="F8" s="1" cm="1">
+        <f t="array" ref="F8">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!F8:Instances!F8),"median", MEDIAN(Instances!F8:Instances!F8),"min", MIN(Instances!F8:Instances!F8),"max", MAX(Instances!F8:Instances!F8),"diff", MAX(Instances!F8:Instances!F8)-MIN(Instances!F8:Instances!F8))</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="1" cm="1">
+        <f t="array" ref="G8">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!G8:Instances!G8),"median", MEDIAN(Instances!G8:Instances!G8),"min", MIN(Instances!G8:Instances!G8),"max", MAX(Instances!G8:Instances!G8),"diff", MAX(Instances!G8:Instances!G8)-MIN(Instances!G8:Instances!G8))</f>
+        <v>0</v>
+      </c>
       <c r="H8" s="1" cm="1">
         <f t="array" ref="H8">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!H8:Instances!H8),"median", MEDIAN(Instances!H8:Instances!H8),"min", MIN(Instances!H8:Instances!H8),"max", MAX(Instances!H8:Instances!H8),"diff", MAX(Instances!H8:Instances!H8)-MIN(Instances!H8:Instances!H8))</f>
         <v>0</v>
@@ -4555,11 +5866,23 @@
         <f t="array" ref="I8">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!I8:Instances!I8),"median", MEDIAN(Instances!I8:Instances!I8),"min", MIN(Instances!I8:Instances!I8),"max", MAX(Instances!I8:Instances!I8),"diff", MAX(Instances!I8:Instances!I8)-MIN(Instances!I8:Instances!I8))</f>
         <v>0</v>
       </c>
-      <c r="J8" s="1"/>
+      <c r="J8" s="1" cm="1">
+        <f t="array" ref="J8">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!J8:Instances!J8),"median", MEDIAN(Instances!J8:Instances!J8),"min", MIN(Instances!J8:Instances!J8),"max", MAX(Instances!J8:Instances!J8),"diff", MAX(Instances!J8:Instances!J8)-MIN(Instances!J8:Instances!J8))</f>
+        <v>0</v>
+      </c>
       <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
+      <c r="L8" s="1" cm="1">
+        <f t="array" ref="L8">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!L8:Instances!L8),"median", MEDIAN(Instances!L8:Instances!L8),"min", MIN(Instances!L8:Instances!L8),"max", MAX(Instances!L8:Instances!L8),"diff", MAX(Instances!L8:Instances!L8)-MIN(Instances!L8:Instances!L8))</f>
+        <v>0</v>
+      </c>
+      <c r="M8" s="1" cm="1">
+        <f t="array" ref="M8">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!M8:Instances!M8),"median", MEDIAN(Instances!M8:Instances!M8),"min", MIN(Instances!M8:Instances!M8),"max", MAX(Instances!M8:Instances!M8),"diff", MAX(Instances!M8:Instances!M8)-MIN(Instances!M8:Instances!M8))</f>
+        <v>0</v>
+      </c>
+      <c r="N8" s="1" cm="1">
+        <f t="array" ref="N8">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!N8:Instances!N8),"median", MEDIAN(Instances!N8:Instances!N8),"min", MIN(Instances!N8:Instances!N8),"max", MAX(Instances!N8:Instances!N8),"diff", MAX(Instances!N8:Instances!N8)-MIN(Instances!N8:Instances!N8))</f>
+        <v>0</v>
+      </c>
       <c r="O8" s="1" cm="1">
         <f t="array" ref="O8">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!O8:Instances!O8),"median", MEDIAN(Instances!O8:Instances!O8),"min", MIN(Instances!O8:Instances!O8),"max", MAX(Instances!O8:Instances!O8),"diff", MAX(Instances!O8:Instances!O8)-MIN(Instances!O8:Instances!O8))</f>
         <v>0</v>
@@ -4568,11 +5891,23 @@
         <f t="array" ref="P8">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!P8:Instances!P8),"median", MEDIAN(Instances!P8:Instances!P8),"min", MIN(Instances!P8:Instances!P8),"max", MAX(Instances!P8:Instances!P8),"diff", MAX(Instances!P8:Instances!P8)-MIN(Instances!P8:Instances!P8))</f>
         <v>0</v>
       </c>
-      <c r="Q8" s="1"/>
+      <c r="Q8" s="1" cm="1">
+        <f t="array" ref="Q8">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!Q8:Instances!Q8),"median", MEDIAN(Instances!Q8:Instances!Q8),"min", MIN(Instances!Q8:Instances!Q8),"max", MAX(Instances!Q8:Instances!Q8),"diff", MAX(Instances!Q8:Instances!Q8)-MIN(Instances!Q8:Instances!Q8))</f>
+        <v>0</v>
+      </c>
       <c r="R8" s="1"/>
-      <c r="S8" s="1"/>
-      <c r="T8" s="1"/>
-      <c r="U8" s="1"/>
+      <c r="S8" s="1" cm="1">
+        <f t="array" ref="S8">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!S8:Instances!S8),"median", MEDIAN(Instances!S8:Instances!S8),"min", MIN(Instances!S8:Instances!S8),"max", MAX(Instances!S8:Instances!S8),"diff", MAX(Instances!S8:Instances!S8)-MIN(Instances!S8:Instances!S8))</f>
+        <v>0</v>
+      </c>
+      <c r="T8" s="1" cm="1">
+        <f t="array" ref="T8">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!T8:Instances!T8),"median", MEDIAN(Instances!T8:Instances!T8),"min", MIN(Instances!T8:Instances!T8),"max", MAX(Instances!T8:Instances!T8),"diff", MAX(Instances!T8:Instances!T8)-MIN(Instances!T8:Instances!T8))</f>
+        <v>0</v>
+      </c>
+      <c r="U8" s="1" cm="1">
+        <f t="array" ref="U8">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!U8:Instances!U8),"median", MEDIAN(Instances!U8:Instances!U8),"min", MIN(Instances!U8:Instances!U8),"max", MAX(Instances!U8:Instances!U8),"diff", MAX(Instances!U8:Instances!U8)-MIN(Instances!U8:Instances!U8))</f>
+        <v>0</v>
+      </c>
       <c r="V8" s="1" cm="1">
         <f t="array" ref="V8">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!V8:Instances!V8),"median", MEDIAN(Instances!V8:Instances!V8),"min", MIN(Instances!V8:Instances!V8),"max", MAX(Instances!V8:Instances!V8),"diff", MAX(Instances!V8:Instances!V8)-MIN(Instances!V8:Instances!V8))</f>
         <v>0</v>
@@ -4581,11 +5916,23 @@
         <f t="array" ref="W8">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!W8:Instances!W8),"median", MEDIAN(Instances!W8:Instances!W8),"min", MIN(Instances!W8:Instances!W8),"max", MAX(Instances!W8:Instances!W8),"diff", MAX(Instances!W8:Instances!W8)-MIN(Instances!W8:Instances!W8))</f>
         <v>0</v>
       </c>
-      <c r="X8" s="1"/>
+      <c r="X8" s="1" cm="1">
+        <f t="array" ref="X8">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!X8:Instances!X8),"median", MEDIAN(Instances!X8:Instances!X8),"min", MIN(Instances!X8:Instances!X8),"max", MAX(Instances!X8:Instances!X8),"diff", MAX(Instances!X8:Instances!X8)-MIN(Instances!X8:Instances!X8))</f>
+        <v>0</v>
+      </c>
       <c r="Y8" s="1"/>
-      <c r="Z8" s="1"/>
-      <c r="AA8" s="1"/>
-      <c r="AB8" s="1"/>
+      <c r="Z8" s="1" cm="1">
+        <f t="array" ref="Z8">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!Z8:Instances!Z8),"median", MEDIAN(Instances!Z8:Instances!Z8),"min", MIN(Instances!Z8:Instances!Z8),"max", MAX(Instances!Z8:Instances!Z8),"diff", MAX(Instances!Z8:Instances!Z8)-MIN(Instances!Z8:Instances!Z8))</f>
+        <v>0</v>
+      </c>
+      <c r="AA8" s="1" cm="1">
+        <f t="array" ref="AA8">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AA8:Instances!AA8),"median", MEDIAN(Instances!AA8:Instances!AA8),"min", MIN(Instances!AA8:Instances!AA8),"max", MAX(Instances!AA8:Instances!AA8),"diff", MAX(Instances!AA8:Instances!AA8)-MIN(Instances!AA8:Instances!AA8))</f>
+        <v>0</v>
+      </c>
+      <c r="AB8" s="1" cm="1">
+        <f t="array" ref="AB8">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AB8:Instances!AB8),"median", MEDIAN(Instances!AB8:Instances!AB8),"min", MIN(Instances!AB8:Instances!AB8),"max", MAX(Instances!AB8:Instances!AB8),"diff", MAX(Instances!AB8:Instances!AB8)-MIN(Instances!AB8:Instances!AB8))</f>
+        <v>0</v>
+      </c>
       <c r="AC8" s="1" cm="1">
         <f t="array" ref="AC8">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AC8:Instances!AC8),"median", MEDIAN(Instances!AC8:Instances!AC8),"min", MIN(Instances!AC8:Instances!AC8),"max", MAX(Instances!AC8:Instances!AC8),"diff", MAX(Instances!AC8:Instances!AC8)-MIN(Instances!AC8:Instances!AC8))</f>
         <v>0</v>
@@ -4594,11 +5941,23 @@
         <f t="array" ref="AD8">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AD8:Instances!AD8),"median", MEDIAN(Instances!AD8:Instances!AD8),"min", MIN(Instances!AD8:Instances!AD8),"max", MAX(Instances!AD8:Instances!AD8),"diff", MAX(Instances!AD8:Instances!AD8)-MIN(Instances!AD8:Instances!AD8))</f>
         <v>0</v>
       </c>
-      <c r="AE8" s="1"/>
+      <c r="AE8" s="1" cm="1">
+        <f t="array" ref="AE8">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AE8:Instances!AE8),"median", MEDIAN(Instances!AE8:Instances!AE8),"min", MIN(Instances!AE8:Instances!AE8),"max", MAX(Instances!AE8:Instances!AE8),"diff", MAX(Instances!AE8:Instances!AE8)-MIN(Instances!AE8:Instances!AE8))</f>
+        <v>0</v>
+      </c>
       <c r="AF8" s="1"/>
-      <c r="AG8" s="1"/>
-      <c r="AH8" s="1"/>
-      <c r="AI8" s="1"/>
+      <c r="AG8" s="1" cm="1">
+        <f t="array" ref="AG8">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AG8:Instances!AG8),"median", MEDIAN(Instances!AG8:Instances!AG8),"min", MIN(Instances!AG8:Instances!AG8),"max", MAX(Instances!AG8:Instances!AG8),"diff", MAX(Instances!AG8:Instances!AG8)-MIN(Instances!AG8:Instances!AG8))</f>
+        <v>0</v>
+      </c>
+      <c r="AH8" s="1" cm="1">
+        <f t="array" ref="AH8">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AH8:Instances!AH8),"median", MEDIAN(Instances!AH8:Instances!AH8),"min", MIN(Instances!AH8:Instances!AH8),"max", MAX(Instances!AH8:Instances!AH8),"diff", MAX(Instances!AH8:Instances!AH8)-MIN(Instances!AH8:Instances!AH8))</f>
+        <v>0</v>
+      </c>
+      <c r="AI8" s="1" cm="1">
+        <f t="array" ref="AI8">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AI8:Instances!AI8),"median", MEDIAN(Instances!AI8:Instances!AI8),"min", MIN(Instances!AI8:Instances!AI8),"max", MAX(Instances!AI8:Instances!AI8),"diff", MAX(Instances!AI8:Instances!AI8)-MIN(Instances!AI8:Instances!AI8))</f>
+        <v>0</v>
+      </c>
       <c r="AJ8" s="1" cm="1">
         <f t="array" ref="AJ8">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AJ8:Instances!AJ8),"median", MEDIAN(Instances!AJ8:Instances!AJ8),"min", MIN(Instances!AJ8:Instances!AJ8),"max", MAX(Instances!AJ8:Instances!AJ8),"diff", MAX(Instances!AJ8:Instances!AJ8)-MIN(Instances!AJ8:Instances!AJ8))</f>
         <v>0</v>
@@ -4607,11 +5966,23 @@
         <f t="array" ref="AK8">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AK8:Instances!AK8),"median", MEDIAN(Instances!AK8:Instances!AK8),"min", MIN(Instances!AK8:Instances!AK8),"max", MAX(Instances!AK8:Instances!AK8),"diff", MAX(Instances!AK8:Instances!AK8)-MIN(Instances!AK8:Instances!AK8))</f>
         <v>0</v>
       </c>
-      <c r="AL8" s="1"/>
+      <c r="AL8" s="1" cm="1">
+        <f t="array" ref="AL8">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AL8:Instances!AL8),"median", MEDIAN(Instances!AL8:Instances!AL8),"min", MIN(Instances!AL8:Instances!AL8),"max", MAX(Instances!AL8:Instances!AL8),"diff", MAX(Instances!AL8:Instances!AL8)-MIN(Instances!AL8:Instances!AL8))</f>
+        <v>0</v>
+      </c>
       <c r="AM8" s="1"/>
-      <c r="AN8" s="1"/>
-      <c r="AO8" s="1"/>
-      <c r="AP8" s="1"/>
+      <c r="AN8" s="1" cm="1">
+        <f t="array" ref="AN8">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AN8:Instances!AN8),"median", MEDIAN(Instances!AN8:Instances!AN8),"min", MIN(Instances!AN8:Instances!AN8),"max", MAX(Instances!AN8:Instances!AN8),"diff", MAX(Instances!AN8:Instances!AN8)-MIN(Instances!AN8:Instances!AN8))</f>
+        <v>0</v>
+      </c>
+      <c r="AO8" s="1" cm="1">
+        <f t="array" ref="AO8">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AO8:Instances!AO8),"median", MEDIAN(Instances!AO8:Instances!AO8),"min", MIN(Instances!AO8:Instances!AO8),"max", MAX(Instances!AO8:Instances!AO8),"diff", MAX(Instances!AO8:Instances!AO8)-MIN(Instances!AO8:Instances!AO8))</f>
+        <v>0</v>
+      </c>
+      <c r="AP8" s="1" cm="1">
+        <f t="array" ref="AP8">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AP8:Instances!AP8),"median", MEDIAN(Instances!AP8:Instances!AP8),"min", MIN(Instances!AP8:Instances!AP8),"max", MAX(Instances!AP8:Instances!AP8),"diff", MAX(Instances!AP8:Instances!AP8)-MIN(Instances!AP8:Instances!AP8))</f>
+        <v>0</v>
+      </c>
       <c r="AQ8" s="1" cm="1">
         <f t="array" ref="AQ8">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AQ8:Instances!AQ8),"median", MEDIAN(Instances!AQ8:Instances!AQ8),"min", MIN(Instances!AQ8:Instances!AQ8),"max", MAX(Instances!AQ8:Instances!AQ8),"diff", MAX(Instances!AQ8:Instances!AQ8)-MIN(Instances!AQ8:Instances!AQ8))</f>
         <v>0</v>
@@ -4620,10 +5991,22 @@
         <f>MIN($B8,$I8,$P8,$W8,$AD8,$AK8)</f>
         <v>0</v>
       </c>
-      <c r="AS8" s="1"/>
-      <c r="AT8" s="1"/>
-      <c r="AU8" s="1"/>
-      <c r="AV8" s="1"/>
+      <c r="AS8" s="1">
+        <f>MIN($C8,$J8,$Q8,$X8,$AE8,$AL8)</f>
+        <v>0</v>
+      </c>
+      <c r="AT8" s="1">
+        <f>MIN($E8,$L8,$S8,$Z8,$AG8,$AN8)</f>
+        <v>0</v>
+      </c>
+      <c r="AU8" s="1">
+        <f>MIN($F8,$M8,$T8,$AA8,$AH8,$AO8)</f>
+        <v>0</v>
+      </c>
+      <c r="AV8" s="1">
+        <f>MIN($G8,$N8,$U8,$AB8,$AI8,$AP8)</f>
+        <v>0</v>
+      </c>
       <c r="AW8" s="1">
         <f>MIN($H8,$O8,$V8,$AC8,$AJ8,$AQ8)</f>
         <v>0</v>
@@ -4632,10 +6015,22 @@
         <f>MEDIAN($B8,$I8,$P8,$W8,$AD8,$AK8)</f>
         <v>0</v>
       </c>
-      <c r="AY8" s="1"/>
-      <c r="AZ8" s="1"/>
-      <c r="BA8" s="1"/>
-      <c r="BB8" s="1"/>
+      <c r="AY8" s="1">
+        <f>MEDIAN($C8,$J8,$Q8,$X8,$AE8,$AL8)</f>
+        <v>0</v>
+      </c>
+      <c r="AZ8" s="1">
+        <f>MEDIAN($E8,$L8,$S8,$Z8,$AG8,$AN8)</f>
+        <v>0</v>
+      </c>
+      <c r="BA8" s="1">
+        <f>MEDIAN($F8,$M8,$T8,$AA8,$AH8,$AO8)</f>
+        <v>0</v>
+      </c>
+      <c r="BB8" s="1">
+        <f>MEDIAN($G8,$N8,$U8,$AB8,$AI8,$AP8)</f>
+        <v>0</v>
+      </c>
       <c r="BC8" s="1">
         <f>MEDIAN($H8,$O8,$V8,$AC8,$AJ8,$AQ8)</f>
         <v>0</v>
@@ -4644,10 +6039,22 @@
         <f>MAX($B8,$I8,$P8,$W8,$AD8,$AK8)</f>
         <v>0</v>
       </c>
-      <c r="BE8" s="1"/>
-      <c r="BF8" s="1"/>
-      <c r="BG8" s="1"/>
-      <c r="BH8" s="1"/>
+      <c r="BE8" s="1">
+        <f>MAX($C8,$J8,$Q8,$X8,$AE8,$AL8)</f>
+        <v>0</v>
+      </c>
+      <c r="BF8" s="1">
+        <f>MAX($E8,$L8,$S8,$Z8,$AG8,$AN8)</f>
+        <v>0</v>
+      </c>
+      <c r="BG8" s="1">
+        <f>MAX($F8,$M8,$T8,$AA8,$AH8,$AO8)</f>
+        <v>0</v>
+      </c>
+      <c r="BH8" s="1">
+        <f>MAX($G8,$N8,$U8,$AB8,$AI8,$AP8)</f>
+        <v>0</v>
+      </c>
       <c r="BI8" s="1">
         <f>MAX($H8,$O8,$V8,$AC8,$AJ8,$AQ8)</f>
         <v>0</v>
@@ -4661,11 +6068,23 @@
         <f t="array" ref="B9">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!B9:Instances!B9),"median", MEDIAN(Instances!B9:Instances!B9),"min", MIN(Instances!B9:Instances!B9),"max", MAX(Instances!B9:Instances!B9),"diff", MAX(Instances!B9:Instances!B9)-MIN(Instances!B9:Instances!B9))</f>
         <v>0</v>
       </c>
-      <c r="C9" s="1"/>
+      <c r="C9" s="1" cm="1">
+        <f t="array" ref="C9">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!C9:Instances!C9),"median", MEDIAN(Instances!C9:Instances!C9),"min", MIN(Instances!C9:Instances!C9),"max", MAX(Instances!C9:Instances!C9),"diff", MAX(Instances!C9:Instances!C9)-MIN(Instances!C9:Instances!C9))</f>
+        <v>0</v>
+      </c>
       <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
+      <c r="E9" s="1" cm="1">
+        <f t="array" ref="E9">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!E9:Instances!E9),"median", MEDIAN(Instances!E9:Instances!E9),"min", MIN(Instances!E9:Instances!E9),"max", MAX(Instances!E9:Instances!E9),"diff", MAX(Instances!E9:Instances!E9)-MIN(Instances!E9:Instances!E9))</f>
+        <v>0</v>
+      </c>
+      <c r="F9" s="1" cm="1">
+        <f t="array" ref="F9">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!F9:Instances!F9),"median", MEDIAN(Instances!F9:Instances!F9),"min", MIN(Instances!F9:Instances!F9),"max", MAX(Instances!F9:Instances!F9),"diff", MAX(Instances!F9:Instances!F9)-MIN(Instances!F9:Instances!F9))</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="1" cm="1">
+        <f t="array" ref="G9">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!G9:Instances!G9),"median", MEDIAN(Instances!G9:Instances!G9),"min", MIN(Instances!G9:Instances!G9),"max", MAX(Instances!G9:Instances!G9),"diff", MAX(Instances!G9:Instances!G9)-MIN(Instances!G9:Instances!G9))</f>
+        <v>0</v>
+      </c>
       <c r="H9" s="1" cm="1">
         <f t="array" ref="H9">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!H9:Instances!H9),"median", MEDIAN(Instances!H9:Instances!H9),"min", MIN(Instances!H9:Instances!H9),"max", MAX(Instances!H9:Instances!H9),"diff", MAX(Instances!H9:Instances!H9)-MIN(Instances!H9:Instances!H9))</f>
         <v>0</v>
@@ -4674,11 +6093,23 @@
         <f t="array" ref="I9">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!I9:Instances!I9),"median", MEDIAN(Instances!I9:Instances!I9),"min", MIN(Instances!I9:Instances!I9),"max", MAX(Instances!I9:Instances!I9),"diff", MAX(Instances!I9:Instances!I9)-MIN(Instances!I9:Instances!I9))</f>
         <v>0</v>
       </c>
-      <c r="J9" s="1"/>
+      <c r="J9" s="1" cm="1">
+        <f t="array" ref="J9">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!J9:Instances!J9),"median", MEDIAN(Instances!J9:Instances!J9),"min", MIN(Instances!J9:Instances!J9),"max", MAX(Instances!J9:Instances!J9),"diff", MAX(Instances!J9:Instances!J9)-MIN(Instances!J9:Instances!J9))</f>
+        <v>0</v>
+      </c>
       <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
-      <c r="N9" s="1"/>
+      <c r="L9" s="1" cm="1">
+        <f t="array" ref="L9">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!L9:Instances!L9),"median", MEDIAN(Instances!L9:Instances!L9),"min", MIN(Instances!L9:Instances!L9),"max", MAX(Instances!L9:Instances!L9),"diff", MAX(Instances!L9:Instances!L9)-MIN(Instances!L9:Instances!L9))</f>
+        <v>0</v>
+      </c>
+      <c r="M9" s="1" cm="1">
+        <f t="array" ref="M9">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!M9:Instances!M9),"median", MEDIAN(Instances!M9:Instances!M9),"min", MIN(Instances!M9:Instances!M9),"max", MAX(Instances!M9:Instances!M9),"diff", MAX(Instances!M9:Instances!M9)-MIN(Instances!M9:Instances!M9))</f>
+        <v>0</v>
+      </c>
+      <c r="N9" s="1" cm="1">
+        <f t="array" ref="N9">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!N9:Instances!N9),"median", MEDIAN(Instances!N9:Instances!N9),"min", MIN(Instances!N9:Instances!N9),"max", MAX(Instances!N9:Instances!N9),"diff", MAX(Instances!N9:Instances!N9)-MIN(Instances!N9:Instances!N9))</f>
+        <v>0</v>
+      </c>
       <c r="O9" s="1" cm="1">
         <f t="array" ref="O9">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!O9:Instances!O9),"median", MEDIAN(Instances!O9:Instances!O9),"min", MIN(Instances!O9:Instances!O9),"max", MAX(Instances!O9:Instances!O9),"diff", MAX(Instances!O9:Instances!O9)-MIN(Instances!O9:Instances!O9))</f>
         <v>0</v>
@@ -4687,11 +6118,23 @@
         <f t="array" ref="P9">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!P9:Instances!P9),"median", MEDIAN(Instances!P9:Instances!P9),"min", MIN(Instances!P9:Instances!P9),"max", MAX(Instances!P9:Instances!P9),"diff", MAX(Instances!P9:Instances!P9)-MIN(Instances!P9:Instances!P9))</f>
         <v>0</v>
       </c>
-      <c r="Q9" s="1"/>
+      <c r="Q9" s="1" cm="1">
+        <f t="array" ref="Q9">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!Q9:Instances!Q9),"median", MEDIAN(Instances!Q9:Instances!Q9),"min", MIN(Instances!Q9:Instances!Q9),"max", MAX(Instances!Q9:Instances!Q9),"diff", MAX(Instances!Q9:Instances!Q9)-MIN(Instances!Q9:Instances!Q9))</f>
+        <v>0</v>
+      </c>
       <c r="R9" s="1"/>
-      <c r="S9" s="1"/>
-      <c r="T9" s="1"/>
-      <c r="U9" s="1"/>
+      <c r="S9" s="1" cm="1">
+        <f t="array" ref="S9">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!S9:Instances!S9),"median", MEDIAN(Instances!S9:Instances!S9),"min", MIN(Instances!S9:Instances!S9),"max", MAX(Instances!S9:Instances!S9),"diff", MAX(Instances!S9:Instances!S9)-MIN(Instances!S9:Instances!S9))</f>
+        <v>0</v>
+      </c>
+      <c r="T9" s="1" cm="1">
+        <f t="array" ref="T9">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!T9:Instances!T9),"median", MEDIAN(Instances!T9:Instances!T9),"min", MIN(Instances!T9:Instances!T9),"max", MAX(Instances!T9:Instances!T9),"diff", MAX(Instances!T9:Instances!T9)-MIN(Instances!T9:Instances!T9))</f>
+        <v>0</v>
+      </c>
+      <c r="U9" s="1" cm="1">
+        <f t="array" ref="U9">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!U9:Instances!U9),"median", MEDIAN(Instances!U9:Instances!U9),"min", MIN(Instances!U9:Instances!U9),"max", MAX(Instances!U9:Instances!U9),"diff", MAX(Instances!U9:Instances!U9)-MIN(Instances!U9:Instances!U9))</f>
+        <v>0</v>
+      </c>
       <c r="V9" s="1" cm="1">
         <f t="array" ref="V9">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!V9:Instances!V9),"median", MEDIAN(Instances!V9:Instances!V9),"min", MIN(Instances!V9:Instances!V9),"max", MAX(Instances!V9:Instances!V9),"diff", MAX(Instances!V9:Instances!V9)-MIN(Instances!V9:Instances!V9))</f>
         <v>0</v>
@@ -4700,11 +6143,23 @@
         <f t="array" ref="W9">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!W9:Instances!W9),"median", MEDIAN(Instances!W9:Instances!W9),"min", MIN(Instances!W9:Instances!W9),"max", MAX(Instances!W9:Instances!W9),"diff", MAX(Instances!W9:Instances!W9)-MIN(Instances!W9:Instances!W9))</f>
         <v>0</v>
       </c>
-      <c r="X9" s="1"/>
+      <c r="X9" s="1" cm="1">
+        <f t="array" ref="X9">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!X9:Instances!X9),"median", MEDIAN(Instances!X9:Instances!X9),"min", MIN(Instances!X9:Instances!X9),"max", MAX(Instances!X9:Instances!X9),"diff", MAX(Instances!X9:Instances!X9)-MIN(Instances!X9:Instances!X9))</f>
+        <v>0</v>
+      </c>
       <c r="Y9" s="1"/>
-      <c r="Z9" s="1"/>
-      <c r="AA9" s="1"/>
-      <c r="AB9" s="1"/>
+      <c r="Z9" s="1" cm="1">
+        <f t="array" ref="Z9">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!Z9:Instances!Z9),"median", MEDIAN(Instances!Z9:Instances!Z9),"min", MIN(Instances!Z9:Instances!Z9),"max", MAX(Instances!Z9:Instances!Z9),"diff", MAX(Instances!Z9:Instances!Z9)-MIN(Instances!Z9:Instances!Z9))</f>
+        <v>0</v>
+      </c>
+      <c r="AA9" s="1" cm="1">
+        <f t="array" ref="AA9">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AA9:Instances!AA9),"median", MEDIAN(Instances!AA9:Instances!AA9),"min", MIN(Instances!AA9:Instances!AA9),"max", MAX(Instances!AA9:Instances!AA9),"diff", MAX(Instances!AA9:Instances!AA9)-MIN(Instances!AA9:Instances!AA9))</f>
+        <v>0</v>
+      </c>
+      <c r="AB9" s="1" cm="1">
+        <f t="array" ref="AB9">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AB9:Instances!AB9),"median", MEDIAN(Instances!AB9:Instances!AB9),"min", MIN(Instances!AB9:Instances!AB9),"max", MAX(Instances!AB9:Instances!AB9),"diff", MAX(Instances!AB9:Instances!AB9)-MIN(Instances!AB9:Instances!AB9))</f>
+        <v>0</v>
+      </c>
       <c r="AC9" s="1" cm="1">
         <f t="array" ref="AC9">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AC9:Instances!AC9),"median", MEDIAN(Instances!AC9:Instances!AC9),"min", MIN(Instances!AC9:Instances!AC9),"max", MAX(Instances!AC9:Instances!AC9),"diff", MAX(Instances!AC9:Instances!AC9)-MIN(Instances!AC9:Instances!AC9))</f>
         <v>0</v>
@@ -4713,11 +6168,23 @@
         <f t="array" ref="AD9">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AD9:Instances!AD9),"median", MEDIAN(Instances!AD9:Instances!AD9),"min", MIN(Instances!AD9:Instances!AD9),"max", MAX(Instances!AD9:Instances!AD9),"diff", MAX(Instances!AD9:Instances!AD9)-MIN(Instances!AD9:Instances!AD9))</f>
         <v>0</v>
       </c>
-      <c r="AE9" s="1"/>
+      <c r="AE9" s="1" cm="1">
+        <f t="array" ref="AE9">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AE9:Instances!AE9),"median", MEDIAN(Instances!AE9:Instances!AE9),"min", MIN(Instances!AE9:Instances!AE9),"max", MAX(Instances!AE9:Instances!AE9),"diff", MAX(Instances!AE9:Instances!AE9)-MIN(Instances!AE9:Instances!AE9))</f>
+        <v>0</v>
+      </c>
       <c r="AF9" s="1"/>
-      <c r="AG9" s="1"/>
-      <c r="AH9" s="1"/>
-      <c r="AI9" s="1"/>
+      <c r="AG9" s="1" cm="1">
+        <f t="array" ref="AG9">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AG9:Instances!AG9),"median", MEDIAN(Instances!AG9:Instances!AG9),"min", MIN(Instances!AG9:Instances!AG9),"max", MAX(Instances!AG9:Instances!AG9),"diff", MAX(Instances!AG9:Instances!AG9)-MIN(Instances!AG9:Instances!AG9))</f>
+        <v>0</v>
+      </c>
+      <c r="AH9" s="1" cm="1">
+        <f t="array" ref="AH9">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AH9:Instances!AH9),"median", MEDIAN(Instances!AH9:Instances!AH9),"min", MIN(Instances!AH9:Instances!AH9),"max", MAX(Instances!AH9:Instances!AH9),"diff", MAX(Instances!AH9:Instances!AH9)-MIN(Instances!AH9:Instances!AH9))</f>
+        <v>0</v>
+      </c>
+      <c r="AI9" s="1" cm="1">
+        <f t="array" ref="AI9">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AI9:Instances!AI9),"median", MEDIAN(Instances!AI9:Instances!AI9),"min", MIN(Instances!AI9:Instances!AI9),"max", MAX(Instances!AI9:Instances!AI9),"diff", MAX(Instances!AI9:Instances!AI9)-MIN(Instances!AI9:Instances!AI9))</f>
+        <v>0</v>
+      </c>
       <c r="AJ9" s="1" cm="1">
         <f t="array" ref="AJ9">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AJ9:Instances!AJ9),"median", MEDIAN(Instances!AJ9:Instances!AJ9),"min", MIN(Instances!AJ9:Instances!AJ9),"max", MAX(Instances!AJ9:Instances!AJ9),"diff", MAX(Instances!AJ9:Instances!AJ9)-MIN(Instances!AJ9:Instances!AJ9))</f>
         <v>0</v>
@@ -4726,11 +6193,23 @@
         <f t="array" ref="AK9">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AK9:Instances!AK9),"median", MEDIAN(Instances!AK9:Instances!AK9),"min", MIN(Instances!AK9:Instances!AK9),"max", MAX(Instances!AK9:Instances!AK9),"diff", MAX(Instances!AK9:Instances!AK9)-MIN(Instances!AK9:Instances!AK9))</f>
         <v>0</v>
       </c>
-      <c r="AL9" s="1"/>
+      <c r="AL9" s="1" cm="1">
+        <f t="array" ref="AL9">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AL9:Instances!AL9),"median", MEDIAN(Instances!AL9:Instances!AL9),"min", MIN(Instances!AL9:Instances!AL9),"max", MAX(Instances!AL9:Instances!AL9),"diff", MAX(Instances!AL9:Instances!AL9)-MIN(Instances!AL9:Instances!AL9))</f>
+        <v>0</v>
+      </c>
       <c r="AM9" s="1"/>
-      <c r="AN9" s="1"/>
-      <c r="AO9" s="1"/>
-      <c r="AP9" s="1"/>
+      <c r="AN9" s="1" cm="1">
+        <f t="array" ref="AN9">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AN9:Instances!AN9),"median", MEDIAN(Instances!AN9:Instances!AN9),"min", MIN(Instances!AN9:Instances!AN9),"max", MAX(Instances!AN9:Instances!AN9),"diff", MAX(Instances!AN9:Instances!AN9)-MIN(Instances!AN9:Instances!AN9))</f>
+        <v>0</v>
+      </c>
+      <c r="AO9" s="1" cm="1">
+        <f t="array" ref="AO9">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AO9:Instances!AO9),"median", MEDIAN(Instances!AO9:Instances!AO9),"min", MIN(Instances!AO9:Instances!AO9),"max", MAX(Instances!AO9:Instances!AO9),"diff", MAX(Instances!AO9:Instances!AO9)-MIN(Instances!AO9:Instances!AO9))</f>
+        <v>0</v>
+      </c>
+      <c r="AP9" s="1" cm="1">
+        <f t="array" ref="AP9">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AP9:Instances!AP9),"median", MEDIAN(Instances!AP9:Instances!AP9),"min", MIN(Instances!AP9:Instances!AP9),"max", MAX(Instances!AP9:Instances!AP9),"diff", MAX(Instances!AP9:Instances!AP9)-MIN(Instances!AP9:Instances!AP9))</f>
+        <v>0</v>
+      </c>
       <c r="AQ9" s="1" cm="1">
         <f t="array" ref="AQ9">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AQ9:Instances!AQ9),"median", MEDIAN(Instances!AQ9:Instances!AQ9),"min", MIN(Instances!AQ9:Instances!AQ9),"max", MAX(Instances!AQ9:Instances!AQ9),"diff", MAX(Instances!AQ9:Instances!AQ9)-MIN(Instances!AQ9:Instances!AQ9))</f>
         <v>0</v>
@@ -4739,10 +6218,22 @@
         <f>MIN($B9,$I9,$P9,$W9,$AD9,$AK9)</f>
         <v>0</v>
       </c>
-      <c r="AS9" s="1"/>
-      <c r="AT9" s="1"/>
-      <c r="AU9" s="1"/>
-      <c r="AV9" s="1"/>
+      <c r="AS9" s="1">
+        <f>MIN($C9,$J9,$Q9,$X9,$AE9,$AL9)</f>
+        <v>0</v>
+      </c>
+      <c r="AT9" s="1">
+        <f>MIN($E9,$L9,$S9,$Z9,$AG9,$AN9)</f>
+        <v>0</v>
+      </c>
+      <c r="AU9" s="1">
+        <f>MIN($F9,$M9,$T9,$AA9,$AH9,$AO9)</f>
+        <v>0</v>
+      </c>
+      <c r="AV9" s="1">
+        <f>MIN($G9,$N9,$U9,$AB9,$AI9,$AP9)</f>
+        <v>0</v>
+      </c>
       <c r="AW9" s="1">
         <f>MIN($H9,$O9,$V9,$AC9,$AJ9,$AQ9)</f>
         <v>0</v>
@@ -4751,10 +6242,22 @@
         <f>MEDIAN($B9,$I9,$P9,$W9,$AD9,$AK9)</f>
         <v>0</v>
       </c>
-      <c r="AY9" s="1"/>
-      <c r="AZ9" s="1"/>
-      <c r="BA9" s="1"/>
-      <c r="BB9" s="1"/>
+      <c r="AY9" s="1">
+        <f>MEDIAN($C9,$J9,$Q9,$X9,$AE9,$AL9)</f>
+        <v>0</v>
+      </c>
+      <c r="AZ9" s="1">
+        <f>MEDIAN($E9,$L9,$S9,$Z9,$AG9,$AN9)</f>
+        <v>0</v>
+      </c>
+      <c r="BA9" s="1">
+        <f>MEDIAN($F9,$M9,$T9,$AA9,$AH9,$AO9)</f>
+        <v>0</v>
+      </c>
+      <c r="BB9" s="1">
+        <f>MEDIAN($G9,$N9,$U9,$AB9,$AI9,$AP9)</f>
+        <v>0</v>
+      </c>
       <c r="BC9" s="1">
         <f>MEDIAN($H9,$O9,$V9,$AC9,$AJ9,$AQ9)</f>
         <v>0</v>
@@ -4763,10 +6266,22 @@
         <f>MAX($B9,$I9,$P9,$W9,$AD9,$AK9)</f>
         <v>0</v>
       </c>
-      <c r="BE9" s="1"/>
-      <c r="BF9" s="1"/>
-      <c r="BG9" s="1"/>
-      <c r="BH9" s="1"/>
+      <c r="BE9" s="1">
+        <f>MAX($C9,$J9,$Q9,$X9,$AE9,$AL9)</f>
+        <v>0</v>
+      </c>
+      <c r="BF9" s="1">
+        <f>MAX($E9,$L9,$S9,$Z9,$AG9,$AN9)</f>
+        <v>0</v>
+      </c>
+      <c r="BG9" s="1">
+        <f>MAX($F9,$M9,$T9,$AA9,$AH9,$AO9)</f>
+        <v>0</v>
+      </c>
+      <c r="BH9" s="1">
+        <f>MAX($G9,$N9,$U9,$AB9,$AI9,$AP9)</f>
+        <v>0</v>
+      </c>
       <c r="BI9" s="1">
         <f>MAX($H9,$O9,$V9,$AC9,$AJ9,$AQ9)</f>
         <v>0</v>
@@ -4780,11 +6295,23 @@
         <f t="array" ref="B10">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!B10:Instances!B10),"median", MEDIAN(Instances!B10:Instances!B10),"min", MIN(Instances!B10:Instances!B10),"max", MAX(Instances!B10:Instances!B10),"diff", MAX(Instances!B10:Instances!B10)-MIN(Instances!B10:Instances!B10))</f>
         <v>0</v>
       </c>
-      <c r="C10" s="1"/>
+      <c r="C10" s="1" cm="1">
+        <f t="array" ref="C10">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!C10:Instances!C10),"median", MEDIAN(Instances!C10:Instances!C10),"min", MIN(Instances!C10:Instances!C10),"max", MAX(Instances!C10:Instances!C10),"diff", MAX(Instances!C10:Instances!C10)-MIN(Instances!C10:Instances!C10))</f>
+        <v>0</v>
+      </c>
       <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
+      <c r="E10" s="1" cm="1">
+        <f t="array" ref="E10">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!E10:Instances!E10),"median", MEDIAN(Instances!E10:Instances!E10),"min", MIN(Instances!E10:Instances!E10),"max", MAX(Instances!E10:Instances!E10),"diff", MAX(Instances!E10:Instances!E10)-MIN(Instances!E10:Instances!E10))</f>
+        <v>0</v>
+      </c>
+      <c r="F10" s="1" cm="1">
+        <f t="array" ref="F10">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!F10:Instances!F10),"median", MEDIAN(Instances!F10:Instances!F10),"min", MIN(Instances!F10:Instances!F10),"max", MAX(Instances!F10:Instances!F10),"diff", MAX(Instances!F10:Instances!F10)-MIN(Instances!F10:Instances!F10))</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="1" cm="1">
+        <f t="array" ref="G10">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!G10:Instances!G10),"median", MEDIAN(Instances!G10:Instances!G10),"min", MIN(Instances!G10:Instances!G10),"max", MAX(Instances!G10:Instances!G10),"diff", MAX(Instances!G10:Instances!G10)-MIN(Instances!G10:Instances!G10))</f>
+        <v>0</v>
+      </c>
       <c r="H10" s="1" cm="1">
         <f t="array" ref="H10">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!H10:Instances!H10),"median", MEDIAN(Instances!H10:Instances!H10),"min", MIN(Instances!H10:Instances!H10),"max", MAX(Instances!H10:Instances!H10),"diff", MAX(Instances!H10:Instances!H10)-MIN(Instances!H10:Instances!H10))</f>
         <v>0</v>
@@ -4793,11 +6320,23 @@
         <f t="array" ref="I10">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!I10:Instances!I10),"median", MEDIAN(Instances!I10:Instances!I10),"min", MIN(Instances!I10:Instances!I10),"max", MAX(Instances!I10:Instances!I10),"diff", MAX(Instances!I10:Instances!I10)-MIN(Instances!I10:Instances!I10))</f>
         <v>0</v>
       </c>
-      <c r="J10" s="1"/>
+      <c r="J10" s="1" cm="1">
+        <f t="array" ref="J10">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!J10:Instances!J10),"median", MEDIAN(Instances!J10:Instances!J10),"min", MIN(Instances!J10:Instances!J10),"max", MAX(Instances!J10:Instances!J10),"diff", MAX(Instances!J10:Instances!J10)-MIN(Instances!J10:Instances!J10))</f>
+        <v>0</v>
+      </c>
       <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
-      <c r="M10" s="1"/>
-      <c r="N10" s="1"/>
+      <c r="L10" s="1" cm="1">
+        <f t="array" ref="L10">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!L10:Instances!L10),"median", MEDIAN(Instances!L10:Instances!L10),"min", MIN(Instances!L10:Instances!L10),"max", MAX(Instances!L10:Instances!L10),"diff", MAX(Instances!L10:Instances!L10)-MIN(Instances!L10:Instances!L10))</f>
+        <v>0</v>
+      </c>
+      <c r="M10" s="1" cm="1">
+        <f t="array" ref="M10">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!M10:Instances!M10),"median", MEDIAN(Instances!M10:Instances!M10),"min", MIN(Instances!M10:Instances!M10),"max", MAX(Instances!M10:Instances!M10),"diff", MAX(Instances!M10:Instances!M10)-MIN(Instances!M10:Instances!M10))</f>
+        <v>0</v>
+      </c>
+      <c r="N10" s="1" cm="1">
+        <f t="array" ref="N10">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!N10:Instances!N10),"median", MEDIAN(Instances!N10:Instances!N10),"min", MIN(Instances!N10:Instances!N10),"max", MAX(Instances!N10:Instances!N10),"diff", MAX(Instances!N10:Instances!N10)-MIN(Instances!N10:Instances!N10))</f>
+        <v>0</v>
+      </c>
       <c r="O10" s="1" cm="1">
         <f t="array" ref="O10">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!O10:Instances!O10),"median", MEDIAN(Instances!O10:Instances!O10),"min", MIN(Instances!O10:Instances!O10),"max", MAX(Instances!O10:Instances!O10),"diff", MAX(Instances!O10:Instances!O10)-MIN(Instances!O10:Instances!O10))</f>
         <v>0</v>
@@ -4806,11 +6345,23 @@
         <f t="array" ref="P10">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!P10:Instances!P10),"median", MEDIAN(Instances!P10:Instances!P10),"min", MIN(Instances!P10:Instances!P10),"max", MAX(Instances!P10:Instances!P10),"diff", MAX(Instances!P10:Instances!P10)-MIN(Instances!P10:Instances!P10))</f>
         <v>0</v>
       </c>
-      <c r="Q10" s="1"/>
+      <c r="Q10" s="1" cm="1">
+        <f t="array" ref="Q10">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!Q10:Instances!Q10),"median", MEDIAN(Instances!Q10:Instances!Q10),"min", MIN(Instances!Q10:Instances!Q10),"max", MAX(Instances!Q10:Instances!Q10),"diff", MAX(Instances!Q10:Instances!Q10)-MIN(Instances!Q10:Instances!Q10))</f>
+        <v>0</v>
+      </c>
       <c r="R10" s="1"/>
-      <c r="S10" s="1"/>
-      <c r="T10" s="1"/>
-      <c r="U10" s="1"/>
+      <c r="S10" s="1" cm="1">
+        <f t="array" ref="S10">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!S10:Instances!S10),"median", MEDIAN(Instances!S10:Instances!S10),"min", MIN(Instances!S10:Instances!S10),"max", MAX(Instances!S10:Instances!S10),"diff", MAX(Instances!S10:Instances!S10)-MIN(Instances!S10:Instances!S10))</f>
+        <v>0</v>
+      </c>
+      <c r="T10" s="1" cm="1">
+        <f t="array" ref="T10">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!T10:Instances!T10),"median", MEDIAN(Instances!T10:Instances!T10),"min", MIN(Instances!T10:Instances!T10),"max", MAX(Instances!T10:Instances!T10),"diff", MAX(Instances!T10:Instances!T10)-MIN(Instances!T10:Instances!T10))</f>
+        <v>0</v>
+      </c>
+      <c r="U10" s="1" cm="1">
+        <f t="array" ref="U10">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!U10:Instances!U10),"median", MEDIAN(Instances!U10:Instances!U10),"min", MIN(Instances!U10:Instances!U10),"max", MAX(Instances!U10:Instances!U10),"diff", MAX(Instances!U10:Instances!U10)-MIN(Instances!U10:Instances!U10))</f>
+        <v>0</v>
+      </c>
       <c r="V10" s="1" cm="1">
         <f t="array" ref="V10">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!V10:Instances!V10),"median", MEDIAN(Instances!V10:Instances!V10),"min", MIN(Instances!V10:Instances!V10),"max", MAX(Instances!V10:Instances!V10),"diff", MAX(Instances!V10:Instances!V10)-MIN(Instances!V10:Instances!V10))</f>
         <v>0</v>
@@ -4819,11 +6370,23 @@
         <f t="array" ref="W10">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!W10:Instances!W10),"median", MEDIAN(Instances!W10:Instances!W10),"min", MIN(Instances!W10:Instances!W10),"max", MAX(Instances!W10:Instances!W10),"diff", MAX(Instances!W10:Instances!W10)-MIN(Instances!W10:Instances!W10))</f>
         <v>0</v>
       </c>
-      <c r="X10" s="1"/>
+      <c r="X10" s="1" cm="1">
+        <f t="array" ref="X10">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!X10:Instances!X10),"median", MEDIAN(Instances!X10:Instances!X10),"min", MIN(Instances!X10:Instances!X10),"max", MAX(Instances!X10:Instances!X10),"diff", MAX(Instances!X10:Instances!X10)-MIN(Instances!X10:Instances!X10))</f>
+        <v>0</v>
+      </c>
       <c r="Y10" s="1"/>
-      <c r="Z10" s="1"/>
-      <c r="AA10" s="1"/>
-      <c r="AB10" s="1"/>
+      <c r="Z10" s="1" cm="1">
+        <f t="array" ref="Z10">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!Z10:Instances!Z10),"median", MEDIAN(Instances!Z10:Instances!Z10),"min", MIN(Instances!Z10:Instances!Z10),"max", MAX(Instances!Z10:Instances!Z10),"diff", MAX(Instances!Z10:Instances!Z10)-MIN(Instances!Z10:Instances!Z10))</f>
+        <v>0</v>
+      </c>
+      <c r="AA10" s="1" cm="1">
+        <f t="array" ref="AA10">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AA10:Instances!AA10),"median", MEDIAN(Instances!AA10:Instances!AA10),"min", MIN(Instances!AA10:Instances!AA10),"max", MAX(Instances!AA10:Instances!AA10),"diff", MAX(Instances!AA10:Instances!AA10)-MIN(Instances!AA10:Instances!AA10))</f>
+        <v>0</v>
+      </c>
+      <c r="AB10" s="1" cm="1">
+        <f t="array" ref="AB10">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AB10:Instances!AB10),"median", MEDIAN(Instances!AB10:Instances!AB10),"min", MIN(Instances!AB10:Instances!AB10),"max", MAX(Instances!AB10:Instances!AB10),"diff", MAX(Instances!AB10:Instances!AB10)-MIN(Instances!AB10:Instances!AB10))</f>
+        <v>0</v>
+      </c>
       <c r="AC10" s="1" cm="1">
         <f t="array" ref="AC10">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AC10:Instances!AC10),"median", MEDIAN(Instances!AC10:Instances!AC10),"min", MIN(Instances!AC10:Instances!AC10),"max", MAX(Instances!AC10:Instances!AC10),"diff", MAX(Instances!AC10:Instances!AC10)-MIN(Instances!AC10:Instances!AC10))</f>
         <v>0</v>
@@ -4832,11 +6395,23 @@
         <f t="array" ref="AD10">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AD10:Instances!AD10),"median", MEDIAN(Instances!AD10:Instances!AD10),"min", MIN(Instances!AD10:Instances!AD10),"max", MAX(Instances!AD10:Instances!AD10),"diff", MAX(Instances!AD10:Instances!AD10)-MIN(Instances!AD10:Instances!AD10))</f>
         <v>0</v>
       </c>
-      <c r="AE10" s="1"/>
+      <c r="AE10" s="1" cm="1">
+        <f t="array" ref="AE10">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AE10:Instances!AE10),"median", MEDIAN(Instances!AE10:Instances!AE10),"min", MIN(Instances!AE10:Instances!AE10),"max", MAX(Instances!AE10:Instances!AE10),"diff", MAX(Instances!AE10:Instances!AE10)-MIN(Instances!AE10:Instances!AE10))</f>
+        <v>0</v>
+      </c>
       <c r="AF10" s="1"/>
-      <c r="AG10" s="1"/>
-      <c r="AH10" s="1"/>
-      <c r="AI10" s="1"/>
+      <c r="AG10" s="1" cm="1">
+        <f t="array" ref="AG10">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AG10:Instances!AG10),"median", MEDIAN(Instances!AG10:Instances!AG10),"min", MIN(Instances!AG10:Instances!AG10),"max", MAX(Instances!AG10:Instances!AG10),"diff", MAX(Instances!AG10:Instances!AG10)-MIN(Instances!AG10:Instances!AG10))</f>
+        <v>0</v>
+      </c>
+      <c r="AH10" s="1" cm="1">
+        <f t="array" ref="AH10">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AH10:Instances!AH10),"median", MEDIAN(Instances!AH10:Instances!AH10),"min", MIN(Instances!AH10:Instances!AH10),"max", MAX(Instances!AH10:Instances!AH10),"diff", MAX(Instances!AH10:Instances!AH10)-MIN(Instances!AH10:Instances!AH10))</f>
+        <v>0</v>
+      </c>
+      <c r="AI10" s="1" cm="1">
+        <f t="array" ref="AI10">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AI10:Instances!AI10),"median", MEDIAN(Instances!AI10:Instances!AI10),"min", MIN(Instances!AI10:Instances!AI10),"max", MAX(Instances!AI10:Instances!AI10),"diff", MAX(Instances!AI10:Instances!AI10)-MIN(Instances!AI10:Instances!AI10))</f>
+        <v>0</v>
+      </c>
       <c r="AJ10" s="1" cm="1">
         <f t="array" ref="AJ10">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AJ10:Instances!AJ10),"median", MEDIAN(Instances!AJ10:Instances!AJ10),"min", MIN(Instances!AJ10:Instances!AJ10),"max", MAX(Instances!AJ10:Instances!AJ10),"diff", MAX(Instances!AJ10:Instances!AJ10)-MIN(Instances!AJ10:Instances!AJ10))</f>
         <v>0</v>
@@ -4845,11 +6420,23 @@
         <f t="array" ref="AK10">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AK10:Instances!AK10),"median", MEDIAN(Instances!AK10:Instances!AK10),"min", MIN(Instances!AK10:Instances!AK10),"max", MAX(Instances!AK10:Instances!AK10),"diff", MAX(Instances!AK10:Instances!AK10)-MIN(Instances!AK10:Instances!AK10))</f>
         <v>0</v>
       </c>
-      <c r="AL10" s="1"/>
+      <c r="AL10" s="1" cm="1">
+        <f t="array" ref="AL10">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AL10:Instances!AL10),"median", MEDIAN(Instances!AL10:Instances!AL10),"min", MIN(Instances!AL10:Instances!AL10),"max", MAX(Instances!AL10:Instances!AL10),"diff", MAX(Instances!AL10:Instances!AL10)-MIN(Instances!AL10:Instances!AL10))</f>
+        <v>0</v>
+      </c>
       <c r="AM10" s="1"/>
-      <c r="AN10" s="1"/>
-      <c r="AO10" s="1"/>
-      <c r="AP10" s="1"/>
+      <c r="AN10" s="1" cm="1">
+        <f t="array" ref="AN10">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AN10:Instances!AN10),"median", MEDIAN(Instances!AN10:Instances!AN10),"min", MIN(Instances!AN10:Instances!AN10),"max", MAX(Instances!AN10:Instances!AN10),"diff", MAX(Instances!AN10:Instances!AN10)-MIN(Instances!AN10:Instances!AN10))</f>
+        <v>0</v>
+      </c>
+      <c r="AO10" s="1" cm="1">
+        <f t="array" ref="AO10">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AO10:Instances!AO10),"median", MEDIAN(Instances!AO10:Instances!AO10),"min", MIN(Instances!AO10:Instances!AO10),"max", MAX(Instances!AO10:Instances!AO10),"diff", MAX(Instances!AO10:Instances!AO10)-MIN(Instances!AO10:Instances!AO10))</f>
+        <v>0</v>
+      </c>
+      <c r="AP10" s="1" cm="1">
+        <f t="array" ref="AP10">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AP10:Instances!AP10),"median", MEDIAN(Instances!AP10:Instances!AP10),"min", MIN(Instances!AP10:Instances!AP10),"max", MAX(Instances!AP10:Instances!AP10),"diff", MAX(Instances!AP10:Instances!AP10)-MIN(Instances!AP10:Instances!AP10))</f>
+        <v>0</v>
+      </c>
       <c r="AQ10" s="1" cm="1">
         <f t="array" ref="AQ10">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AQ10:Instances!AQ10),"median", MEDIAN(Instances!AQ10:Instances!AQ10),"min", MIN(Instances!AQ10:Instances!AQ10),"max", MAX(Instances!AQ10:Instances!AQ10),"diff", MAX(Instances!AQ10:Instances!AQ10)-MIN(Instances!AQ10:Instances!AQ10))</f>
         <v>0</v>
@@ -4858,10 +6445,22 @@
         <f>MIN($B10,$I10,$P10,$W10,$AD10,$AK10)</f>
         <v>0</v>
       </c>
-      <c r="AS10" s="1"/>
-      <c r="AT10" s="1"/>
-      <c r="AU10" s="1"/>
-      <c r="AV10" s="1"/>
+      <c r="AS10" s="1">
+        <f>MIN($C10,$J10,$Q10,$X10,$AE10,$AL10)</f>
+        <v>0</v>
+      </c>
+      <c r="AT10" s="1">
+        <f>MIN($E10,$L10,$S10,$Z10,$AG10,$AN10)</f>
+        <v>0</v>
+      </c>
+      <c r="AU10" s="1">
+        <f>MIN($F10,$M10,$T10,$AA10,$AH10,$AO10)</f>
+        <v>0</v>
+      </c>
+      <c r="AV10" s="1">
+        <f>MIN($G10,$N10,$U10,$AB10,$AI10,$AP10)</f>
+        <v>0</v>
+      </c>
       <c r="AW10" s="1">
         <f>MIN($H10,$O10,$V10,$AC10,$AJ10,$AQ10)</f>
         <v>0</v>
@@ -4870,10 +6469,22 @@
         <f>MEDIAN($B10,$I10,$P10,$W10,$AD10,$AK10)</f>
         <v>0</v>
       </c>
-      <c r="AY10" s="1"/>
-      <c r="AZ10" s="1"/>
-      <c r="BA10" s="1"/>
-      <c r="BB10" s="1"/>
+      <c r="AY10" s="1">
+        <f>MEDIAN($C10,$J10,$Q10,$X10,$AE10,$AL10)</f>
+        <v>0</v>
+      </c>
+      <c r="AZ10" s="1">
+        <f>MEDIAN($E10,$L10,$S10,$Z10,$AG10,$AN10)</f>
+        <v>0</v>
+      </c>
+      <c r="BA10" s="1">
+        <f>MEDIAN($F10,$M10,$T10,$AA10,$AH10,$AO10)</f>
+        <v>0</v>
+      </c>
+      <c r="BB10" s="1">
+        <f>MEDIAN($G10,$N10,$U10,$AB10,$AI10,$AP10)</f>
+        <v>0</v>
+      </c>
       <c r="BC10" s="1">
         <f>MEDIAN($H10,$O10,$V10,$AC10,$AJ10,$AQ10)</f>
         <v>0</v>
@@ -4882,10 +6493,22 @@
         <f>MAX($B10,$I10,$P10,$W10,$AD10,$AK10)</f>
         <v>0</v>
       </c>
-      <c r="BE10" s="1"/>
-      <c r="BF10" s="1"/>
-      <c r="BG10" s="1"/>
-      <c r="BH10" s="1"/>
+      <c r="BE10" s="1">
+        <f>MAX($C10,$J10,$Q10,$X10,$AE10,$AL10)</f>
+        <v>0</v>
+      </c>
+      <c r="BF10" s="1">
+        <f>MAX($E10,$L10,$S10,$Z10,$AG10,$AN10)</f>
+        <v>0</v>
+      </c>
+      <c r="BG10" s="1">
+        <f>MAX($F10,$M10,$T10,$AA10,$AH10,$AO10)</f>
+        <v>0</v>
+      </c>
+      <c r="BH10" s="1">
+        <f>MAX($G10,$N10,$U10,$AB10,$AI10,$AP10)</f>
+        <v>0</v>
+      </c>
       <c r="BI10" s="1">
         <f>MAX($H10,$O10,$V10,$AC10,$AJ10,$AQ10)</f>
         <v>0</v>
@@ -4899,11 +6522,23 @@
         <f t="array" ref="B11">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!B11:Instances!B11),"median", MEDIAN(Instances!B11:Instances!B11),"min", MIN(Instances!B11:Instances!B11),"max", MAX(Instances!B11:Instances!B11),"diff", MAX(Instances!B11:Instances!B11)-MIN(Instances!B11:Instances!B11))</f>
         <v>0</v>
       </c>
-      <c r="C11" s="1"/>
+      <c r="C11" s="1" cm="1">
+        <f t="array" ref="C11">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!C11:Instances!C11),"median", MEDIAN(Instances!C11:Instances!C11),"min", MIN(Instances!C11:Instances!C11),"max", MAX(Instances!C11:Instances!C11),"diff", MAX(Instances!C11:Instances!C11)-MIN(Instances!C11:Instances!C11))</f>
+        <v>0</v>
+      </c>
       <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
+      <c r="E11" s="1" cm="1">
+        <f t="array" ref="E11">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!E11:Instances!E11),"median", MEDIAN(Instances!E11:Instances!E11),"min", MIN(Instances!E11:Instances!E11),"max", MAX(Instances!E11:Instances!E11),"diff", MAX(Instances!E11:Instances!E11)-MIN(Instances!E11:Instances!E11))</f>
+        <v>0</v>
+      </c>
+      <c r="F11" s="1" cm="1">
+        <f t="array" ref="F11">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!F11:Instances!F11),"median", MEDIAN(Instances!F11:Instances!F11),"min", MIN(Instances!F11:Instances!F11),"max", MAX(Instances!F11:Instances!F11),"diff", MAX(Instances!F11:Instances!F11)-MIN(Instances!F11:Instances!F11))</f>
+        <v>0</v>
+      </c>
+      <c r="G11" s="1" cm="1">
+        <f t="array" ref="G11">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!G11:Instances!G11),"median", MEDIAN(Instances!G11:Instances!G11),"min", MIN(Instances!G11:Instances!G11),"max", MAX(Instances!G11:Instances!G11),"diff", MAX(Instances!G11:Instances!G11)-MIN(Instances!G11:Instances!G11))</f>
+        <v>0</v>
+      </c>
       <c r="H11" s="1" cm="1">
         <f t="array" ref="H11">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!H11:Instances!H11),"median", MEDIAN(Instances!H11:Instances!H11),"min", MIN(Instances!H11:Instances!H11),"max", MAX(Instances!H11:Instances!H11),"diff", MAX(Instances!H11:Instances!H11)-MIN(Instances!H11:Instances!H11))</f>
         <v>0</v>
@@ -4912,11 +6547,23 @@
         <f t="array" ref="I11">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!I11:Instances!I11),"median", MEDIAN(Instances!I11:Instances!I11),"min", MIN(Instances!I11:Instances!I11),"max", MAX(Instances!I11:Instances!I11),"diff", MAX(Instances!I11:Instances!I11)-MIN(Instances!I11:Instances!I11))</f>
         <v>0</v>
       </c>
-      <c r="J11" s="1"/>
+      <c r="J11" s="1" cm="1">
+        <f t="array" ref="J11">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!J11:Instances!J11),"median", MEDIAN(Instances!J11:Instances!J11),"min", MIN(Instances!J11:Instances!J11),"max", MAX(Instances!J11:Instances!J11),"diff", MAX(Instances!J11:Instances!J11)-MIN(Instances!J11:Instances!J11))</f>
+        <v>0</v>
+      </c>
       <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
-      <c r="N11" s="1"/>
+      <c r="L11" s="1" cm="1">
+        <f t="array" ref="L11">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!L11:Instances!L11),"median", MEDIAN(Instances!L11:Instances!L11),"min", MIN(Instances!L11:Instances!L11),"max", MAX(Instances!L11:Instances!L11),"diff", MAX(Instances!L11:Instances!L11)-MIN(Instances!L11:Instances!L11))</f>
+        <v>0</v>
+      </c>
+      <c r="M11" s="1" cm="1">
+        <f t="array" ref="M11">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!M11:Instances!M11),"median", MEDIAN(Instances!M11:Instances!M11),"min", MIN(Instances!M11:Instances!M11),"max", MAX(Instances!M11:Instances!M11),"diff", MAX(Instances!M11:Instances!M11)-MIN(Instances!M11:Instances!M11))</f>
+        <v>0</v>
+      </c>
+      <c r="N11" s="1" cm="1">
+        <f t="array" ref="N11">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!N11:Instances!N11),"median", MEDIAN(Instances!N11:Instances!N11),"min", MIN(Instances!N11:Instances!N11),"max", MAX(Instances!N11:Instances!N11),"diff", MAX(Instances!N11:Instances!N11)-MIN(Instances!N11:Instances!N11))</f>
+        <v>0</v>
+      </c>
       <c r="O11" s="1" cm="1">
         <f t="array" ref="O11">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!O11:Instances!O11),"median", MEDIAN(Instances!O11:Instances!O11),"min", MIN(Instances!O11:Instances!O11),"max", MAX(Instances!O11:Instances!O11),"diff", MAX(Instances!O11:Instances!O11)-MIN(Instances!O11:Instances!O11))</f>
         <v>0</v>
@@ -4925,11 +6572,23 @@
         <f t="array" ref="P11">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!P11:Instances!P11),"median", MEDIAN(Instances!P11:Instances!P11),"min", MIN(Instances!P11:Instances!P11),"max", MAX(Instances!P11:Instances!P11),"diff", MAX(Instances!P11:Instances!P11)-MIN(Instances!P11:Instances!P11))</f>
         <v>0</v>
       </c>
-      <c r="Q11" s="1"/>
+      <c r="Q11" s="1" cm="1">
+        <f t="array" ref="Q11">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!Q11:Instances!Q11),"median", MEDIAN(Instances!Q11:Instances!Q11),"min", MIN(Instances!Q11:Instances!Q11),"max", MAX(Instances!Q11:Instances!Q11),"diff", MAX(Instances!Q11:Instances!Q11)-MIN(Instances!Q11:Instances!Q11))</f>
+        <v>0</v>
+      </c>
       <c r="R11" s="1"/>
-      <c r="S11" s="1"/>
-      <c r="T11" s="1"/>
-      <c r="U11" s="1"/>
+      <c r="S11" s="1" cm="1">
+        <f t="array" ref="S11">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!S11:Instances!S11),"median", MEDIAN(Instances!S11:Instances!S11),"min", MIN(Instances!S11:Instances!S11),"max", MAX(Instances!S11:Instances!S11),"diff", MAX(Instances!S11:Instances!S11)-MIN(Instances!S11:Instances!S11))</f>
+        <v>0</v>
+      </c>
+      <c r="T11" s="1" cm="1">
+        <f t="array" ref="T11">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!T11:Instances!T11),"median", MEDIAN(Instances!T11:Instances!T11),"min", MIN(Instances!T11:Instances!T11),"max", MAX(Instances!T11:Instances!T11),"diff", MAX(Instances!T11:Instances!T11)-MIN(Instances!T11:Instances!T11))</f>
+        <v>0</v>
+      </c>
+      <c r="U11" s="1" cm="1">
+        <f t="array" ref="U11">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!U11:Instances!U11),"median", MEDIAN(Instances!U11:Instances!U11),"min", MIN(Instances!U11:Instances!U11),"max", MAX(Instances!U11:Instances!U11),"diff", MAX(Instances!U11:Instances!U11)-MIN(Instances!U11:Instances!U11))</f>
+        <v>0</v>
+      </c>
       <c r="V11" s="1" cm="1">
         <f t="array" ref="V11">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!V11:Instances!V11),"median", MEDIAN(Instances!V11:Instances!V11),"min", MIN(Instances!V11:Instances!V11),"max", MAX(Instances!V11:Instances!V11),"diff", MAX(Instances!V11:Instances!V11)-MIN(Instances!V11:Instances!V11))</f>
         <v>0</v>
@@ -4938,11 +6597,23 @@
         <f t="array" ref="W11">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!W11:Instances!W11),"median", MEDIAN(Instances!W11:Instances!W11),"min", MIN(Instances!W11:Instances!W11),"max", MAX(Instances!W11:Instances!W11),"diff", MAX(Instances!W11:Instances!W11)-MIN(Instances!W11:Instances!W11))</f>
         <v>0</v>
       </c>
-      <c r="X11" s="1"/>
+      <c r="X11" s="1" cm="1">
+        <f t="array" ref="X11">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!X11:Instances!X11),"median", MEDIAN(Instances!X11:Instances!X11),"min", MIN(Instances!X11:Instances!X11),"max", MAX(Instances!X11:Instances!X11),"diff", MAX(Instances!X11:Instances!X11)-MIN(Instances!X11:Instances!X11))</f>
+        <v>0</v>
+      </c>
       <c r="Y11" s="1"/>
-      <c r="Z11" s="1"/>
-      <c r="AA11" s="1"/>
-      <c r="AB11" s="1"/>
+      <c r="Z11" s="1" cm="1">
+        <f t="array" ref="Z11">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!Z11:Instances!Z11),"median", MEDIAN(Instances!Z11:Instances!Z11),"min", MIN(Instances!Z11:Instances!Z11),"max", MAX(Instances!Z11:Instances!Z11),"diff", MAX(Instances!Z11:Instances!Z11)-MIN(Instances!Z11:Instances!Z11))</f>
+        <v>0</v>
+      </c>
+      <c r="AA11" s="1" cm="1">
+        <f t="array" ref="AA11">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AA11:Instances!AA11),"median", MEDIAN(Instances!AA11:Instances!AA11),"min", MIN(Instances!AA11:Instances!AA11),"max", MAX(Instances!AA11:Instances!AA11),"diff", MAX(Instances!AA11:Instances!AA11)-MIN(Instances!AA11:Instances!AA11))</f>
+        <v>0</v>
+      </c>
+      <c r="AB11" s="1" cm="1">
+        <f t="array" ref="AB11">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AB11:Instances!AB11),"median", MEDIAN(Instances!AB11:Instances!AB11),"min", MIN(Instances!AB11:Instances!AB11),"max", MAX(Instances!AB11:Instances!AB11),"diff", MAX(Instances!AB11:Instances!AB11)-MIN(Instances!AB11:Instances!AB11))</f>
+        <v>0</v>
+      </c>
       <c r="AC11" s="1" cm="1">
         <f t="array" ref="AC11">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AC11:Instances!AC11),"median", MEDIAN(Instances!AC11:Instances!AC11),"min", MIN(Instances!AC11:Instances!AC11),"max", MAX(Instances!AC11:Instances!AC11),"diff", MAX(Instances!AC11:Instances!AC11)-MIN(Instances!AC11:Instances!AC11))</f>
         <v>0</v>
@@ -4951,11 +6622,23 @@
         <f t="array" ref="AD11">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AD11:Instances!AD11),"median", MEDIAN(Instances!AD11:Instances!AD11),"min", MIN(Instances!AD11:Instances!AD11),"max", MAX(Instances!AD11:Instances!AD11),"diff", MAX(Instances!AD11:Instances!AD11)-MIN(Instances!AD11:Instances!AD11))</f>
         <v>0</v>
       </c>
-      <c r="AE11" s="1"/>
+      <c r="AE11" s="1" cm="1">
+        <f t="array" ref="AE11">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AE11:Instances!AE11),"median", MEDIAN(Instances!AE11:Instances!AE11),"min", MIN(Instances!AE11:Instances!AE11),"max", MAX(Instances!AE11:Instances!AE11),"diff", MAX(Instances!AE11:Instances!AE11)-MIN(Instances!AE11:Instances!AE11))</f>
+        <v>0</v>
+      </c>
       <c r="AF11" s="1"/>
-      <c r="AG11" s="1"/>
-      <c r="AH11" s="1"/>
-      <c r="AI11" s="1"/>
+      <c r="AG11" s="1" cm="1">
+        <f t="array" ref="AG11">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AG11:Instances!AG11),"median", MEDIAN(Instances!AG11:Instances!AG11),"min", MIN(Instances!AG11:Instances!AG11),"max", MAX(Instances!AG11:Instances!AG11),"diff", MAX(Instances!AG11:Instances!AG11)-MIN(Instances!AG11:Instances!AG11))</f>
+        <v>0</v>
+      </c>
+      <c r="AH11" s="1" cm="1">
+        <f t="array" ref="AH11">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AH11:Instances!AH11),"median", MEDIAN(Instances!AH11:Instances!AH11),"min", MIN(Instances!AH11:Instances!AH11),"max", MAX(Instances!AH11:Instances!AH11),"diff", MAX(Instances!AH11:Instances!AH11)-MIN(Instances!AH11:Instances!AH11))</f>
+        <v>0</v>
+      </c>
+      <c r="AI11" s="1" cm="1">
+        <f t="array" ref="AI11">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AI11:Instances!AI11),"median", MEDIAN(Instances!AI11:Instances!AI11),"min", MIN(Instances!AI11:Instances!AI11),"max", MAX(Instances!AI11:Instances!AI11),"diff", MAX(Instances!AI11:Instances!AI11)-MIN(Instances!AI11:Instances!AI11))</f>
+        <v>0</v>
+      </c>
       <c r="AJ11" s="1" cm="1">
         <f t="array" ref="AJ11">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AJ11:Instances!AJ11),"median", MEDIAN(Instances!AJ11:Instances!AJ11),"min", MIN(Instances!AJ11:Instances!AJ11),"max", MAX(Instances!AJ11:Instances!AJ11),"diff", MAX(Instances!AJ11:Instances!AJ11)-MIN(Instances!AJ11:Instances!AJ11))</f>
         <v>0</v>
@@ -4964,11 +6647,23 @@
         <f t="array" ref="AK11">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AK11:Instances!AK11),"median", MEDIAN(Instances!AK11:Instances!AK11),"min", MIN(Instances!AK11:Instances!AK11),"max", MAX(Instances!AK11:Instances!AK11),"diff", MAX(Instances!AK11:Instances!AK11)-MIN(Instances!AK11:Instances!AK11))</f>
         <v>0</v>
       </c>
-      <c r="AL11" s="1"/>
+      <c r="AL11" s="1" cm="1">
+        <f t="array" ref="AL11">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AL11:Instances!AL11),"median", MEDIAN(Instances!AL11:Instances!AL11),"min", MIN(Instances!AL11:Instances!AL11),"max", MAX(Instances!AL11:Instances!AL11),"diff", MAX(Instances!AL11:Instances!AL11)-MIN(Instances!AL11:Instances!AL11))</f>
+        <v>0</v>
+      </c>
       <c r="AM11" s="1"/>
-      <c r="AN11" s="1"/>
-      <c r="AO11" s="1"/>
-      <c r="AP11" s="1"/>
+      <c r="AN11" s="1" cm="1">
+        <f t="array" ref="AN11">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AN11:Instances!AN11),"median", MEDIAN(Instances!AN11:Instances!AN11),"min", MIN(Instances!AN11:Instances!AN11),"max", MAX(Instances!AN11:Instances!AN11),"diff", MAX(Instances!AN11:Instances!AN11)-MIN(Instances!AN11:Instances!AN11))</f>
+        <v>0</v>
+      </c>
+      <c r="AO11" s="1" cm="1">
+        <f t="array" ref="AO11">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AO11:Instances!AO11),"median", MEDIAN(Instances!AO11:Instances!AO11),"min", MIN(Instances!AO11:Instances!AO11),"max", MAX(Instances!AO11:Instances!AO11),"diff", MAX(Instances!AO11:Instances!AO11)-MIN(Instances!AO11:Instances!AO11))</f>
+        <v>0</v>
+      </c>
+      <c r="AP11" s="1" cm="1">
+        <f t="array" ref="AP11">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AP11:Instances!AP11),"median", MEDIAN(Instances!AP11:Instances!AP11),"min", MIN(Instances!AP11:Instances!AP11),"max", MAX(Instances!AP11:Instances!AP11),"diff", MAX(Instances!AP11:Instances!AP11)-MIN(Instances!AP11:Instances!AP11))</f>
+        <v>0</v>
+      </c>
       <c r="AQ11" s="1" cm="1">
         <f t="array" ref="AQ11">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AQ11:Instances!AQ11),"median", MEDIAN(Instances!AQ11:Instances!AQ11),"min", MIN(Instances!AQ11:Instances!AQ11),"max", MAX(Instances!AQ11:Instances!AQ11),"diff", MAX(Instances!AQ11:Instances!AQ11)-MIN(Instances!AQ11:Instances!AQ11))</f>
         <v>0</v>
@@ -4977,10 +6672,22 @@
         <f>MIN($B11,$I11,$P11,$W11,$AD11,$AK11)</f>
         <v>0</v>
       </c>
-      <c r="AS11" s="1"/>
-      <c r="AT11" s="1"/>
-      <c r="AU11" s="1"/>
-      <c r="AV11" s="1"/>
+      <c r="AS11" s="1">
+        <f>MIN($C11,$J11,$Q11,$X11,$AE11,$AL11)</f>
+        <v>0</v>
+      </c>
+      <c r="AT11" s="1">
+        <f>MIN($E11,$L11,$S11,$Z11,$AG11,$AN11)</f>
+        <v>0</v>
+      </c>
+      <c r="AU11" s="1">
+        <f>MIN($F11,$M11,$T11,$AA11,$AH11,$AO11)</f>
+        <v>0</v>
+      </c>
+      <c r="AV11" s="1">
+        <f>MIN($G11,$N11,$U11,$AB11,$AI11,$AP11)</f>
+        <v>0</v>
+      </c>
       <c r="AW11" s="1">
         <f>MIN($H11,$O11,$V11,$AC11,$AJ11,$AQ11)</f>
         <v>0</v>
@@ -4989,10 +6696,22 @@
         <f>MEDIAN($B11,$I11,$P11,$W11,$AD11,$AK11)</f>
         <v>0</v>
       </c>
-      <c r="AY11" s="1"/>
-      <c r="AZ11" s="1"/>
-      <c r="BA11" s="1"/>
-      <c r="BB11" s="1"/>
+      <c r="AY11" s="1">
+        <f>MEDIAN($C11,$J11,$Q11,$X11,$AE11,$AL11)</f>
+        <v>0</v>
+      </c>
+      <c r="AZ11" s="1">
+        <f>MEDIAN($E11,$L11,$S11,$Z11,$AG11,$AN11)</f>
+        <v>0</v>
+      </c>
+      <c r="BA11" s="1">
+        <f>MEDIAN($F11,$M11,$T11,$AA11,$AH11,$AO11)</f>
+        <v>0</v>
+      </c>
+      <c r="BB11" s="1">
+        <f>MEDIAN($G11,$N11,$U11,$AB11,$AI11,$AP11)</f>
+        <v>0</v>
+      </c>
       <c r="BC11" s="1">
         <f>MEDIAN($H11,$O11,$V11,$AC11,$AJ11,$AQ11)</f>
         <v>0</v>
@@ -5001,10 +6720,22 @@
         <f>MAX($B11,$I11,$P11,$W11,$AD11,$AK11)</f>
         <v>0</v>
       </c>
-      <c r="BE11" s="1"/>
-      <c r="BF11" s="1"/>
-      <c r="BG11" s="1"/>
-      <c r="BH11" s="1"/>
+      <c r="BE11" s="1">
+        <f>MAX($C11,$J11,$Q11,$X11,$AE11,$AL11)</f>
+        <v>0</v>
+      </c>
+      <c r="BF11" s="1">
+        <f>MAX($E11,$L11,$S11,$Z11,$AG11,$AN11)</f>
+        <v>0</v>
+      </c>
+      <c r="BG11" s="1">
+        <f>MAX($F11,$M11,$T11,$AA11,$AH11,$AO11)</f>
+        <v>0</v>
+      </c>
+      <c r="BH11" s="1">
+        <f>MAX($G11,$N11,$U11,$AB11,$AI11,$AP11)</f>
+        <v>0</v>
+      </c>
       <c r="BI11" s="1">
         <f>MAX($H11,$O11,$V11,$AC11,$AJ11,$AQ11)</f>
         <v>0</v>
@@ -5018,11 +6749,23 @@
         <f t="array" ref="B12">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!B12:Instances!B12),"median", MEDIAN(Instances!B12:Instances!B12),"min", MIN(Instances!B12:Instances!B12),"max", MAX(Instances!B12:Instances!B12),"diff", MAX(Instances!B12:Instances!B12)-MIN(Instances!B12:Instances!B12))</f>
         <v>0</v>
       </c>
-      <c r="C12" s="1"/>
+      <c r="C12" s="1" cm="1">
+        <f t="array" ref="C12">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!C12:Instances!C12),"median", MEDIAN(Instances!C12:Instances!C12),"min", MIN(Instances!C12:Instances!C12),"max", MAX(Instances!C12:Instances!C12),"diff", MAX(Instances!C12:Instances!C12)-MIN(Instances!C12:Instances!C12))</f>
+        <v>0</v>
+      </c>
       <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
+      <c r="E12" s="1" cm="1">
+        <f t="array" ref="E12">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!E12:Instances!E12),"median", MEDIAN(Instances!E12:Instances!E12),"min", MIN(Instances!E12:Instances!E12),"max", MAX(Instances!E12:Instances!E12),"diff", MAX(Instances!E12:Instances!E12)-MIN(Instances!E12:Instances!E12))</f>
+        <v>0</v>
+      </c>
+      <c r="F12" s="1" cm="1">
+        <f t="array" ref="F12">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!F12:Instances!F12),"median", MEDIAN(Instances!F12:Instances!F12),"min", MIN(Instances!F12:Instances!F12),"max", MAX(Instances!F12:Instances!F12),"diff", MAX(Instances!F12:Instances!F12)-MIN(Instances!F12:Instances!F12))</f>
+        <v>0</v>
+      </c>
+      <c r="G12" s="1" cm="1">
+        <f t="array" ref="G12">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!G12:Instances!G12),"median", MEDIAN(Instances!G12:Instances!G12),"min", MIN(Instances!G12:Instances!G12),"max", MAX(Instances!G12:Instances!G12),"diff", MAX(Instances!G12:Instances!G12)-MIN(Instances!G12:Instances!G12))</f>
+        <v>0</v>
+      </c>
       <c r="H12" s="1" cm="1">
         <f t="array" ref="H12">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!H12:Instances!H12),"median", MEDIAN(Instances!H12:Instances!H12),"min", MIN(Instances!H12:Instances!H12),"max", MAX(Instances!H12:Instances!H12),"diff", MAX(Instances!H12:Instances!H12)-MIN(Instances!H12:Instances!H12))</f>
         <v>0</v>
@@ -5031,11 +6774,23 @@
         <f t="array" ref="I12">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!I12:Instances!I12),"median", MEDIAN(Instances!I12:Instances!I12),"min", MIN(Instances!I12:Instances!I12),"max", MAX(Instances!I12:Instances!I12),"diff", MAX(Instances!I12:Instances!I12)-MIN(Instances!I12:Instances!I12))</f>
         <v>0</v>
       </c>
-      <c r="J12" s="1"/>
+      <c r="J12" s="1" cm="1">
+        <f t="array" ref="J12">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!J12:Instances!J12),"median", MEDIAN(Instances!J12:Instances!J12),"min", MIN(Instances!J12:Instances!J12),"max", MAX(Instances!J12:Instances!J12),"diff", MAX(Instances!J12:Instances!J12)-MIN(Instances!J12:Instances!J12))</f>
+        <v>0</v>
+      </c>
       <c r="K12" s="1"/>
-      <c r="L12" s="1"/>
-      <c r="M12" s="1"/>
-      <c r="N12" s="1"/>
+      <c r="L12" s="1" cm="1">
+        <f t="array" ref="L12">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!L12:Instances!L12),"median", MEDIAN(Instances!L12:Instances!L12),"min", MIN(Instances!L12:Instances!L12),"max", MAX(Instances!L12:Instances!L12),"diff", MAX(Instances!L12:Instances!L12)-MIN(Instances!L12:Instances!L12))</f>
+        <v>0</v>
+      </c>
+      <c r="M12" s="1" cm="1">
+        <f t="array" ref="M12">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!M12:Instances!M12),"median", MEDIAN(Instances!M12:Instances!M12),"min", MIN(Instances!M12:Instances!M12),"max", MAX(Instances!M12:Instances!M12),"diff", MAX(Instances!M12:Instances!M12)-MIN(Instances!M12:Instances!M12))</f>
+        <v>0</v>
+      </c>
+      <c r="N12" s="1" cm="1">
+        <f t="array" ref="N12">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!N12:Instances!N12),"median", MEDIAN(Instances!N12:Instances!N12),"min", MIN(Instances!N12:Instances!N12),"max", MAX(Instances!N12:Instances!N12),"diff", MAX(Instances!N12:Instances!N12)-MIN(Instances!N12:Instances!N12))</f>
+        <v>0</v>
+      </c>
       <c r="O12" s="1" cm="1">
         <f t="array" ref="O12">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!O12:Instances!O12),"median", MEDIAN(Instances!O12:Instances!O12),"min", MIN(Instances!O12:Instances!O12),"max", MAX(Instances!O12:Instances!O12),"diff", MAX(Instances!O12:Instances!O12)-MIN(Instances!O12:Instances!O12))</f>
         <v>0</v>
@@ -5044,11 +6799,23 @@
         <f t="array" ref="P12">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!P12:Instances!P12),"median", MEDIAN(Instances!P12:Instances!P12),"min", MIN(Instances!P12:Instances!P12),"max", MAX(Instances!P12:Instances!P12),"diff", MAX(Instances!P12:Instances!P12)-MIN(Instances!P12:Instances!P12))</f>
         <v>0</v>
       </c>
-      <c r="Q12" s="1"/>
+      <c r="Q12" s="1" cm="1">
+        <f t="array" ref="Q12">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!Q12:Instances!Q12),"median", MEDIAN(Instances!Q12:Instances!Q12),"min", MIN(Instances!Q12:Instances!Q12),"max", MAX(Instances!Q12:Instances!Q12),"diff", MAX(Instances!Q12:Instances!Q12)-MIN(Instances!Q12:Instances!Q12))</f>
+        <v>0</v>
+      </c>
       <c r="R12" s="1"/>
-      <c r="S12" s="1"/>
-      <c r="T12" s="1"/>
-      <c r="U12" s="1"/>
+      <c r="S12" s="1" cm="1">
+        <f t="array" ref="S12">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!S12:Instances!S12),"median", MEDIAN(Instances!S12:Instances!S12),"min", MIN(Instances!S12:Instances!S12),"max", MAX(Instances!S12:Instances!S12),"diff", MAX(Instances!S12:Instances!S12)-MIN(Instances!S12:Instances!S12))</f>
+        <v>0</v>
+      </c>
+      <c r="T12" s="1" cm="1">
+        <f t="array" ref="T12">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!T12:Instances!T12),"median", MEDIAN(Instances!T12:Instances!T12),"min", MIN(Instances!T12:Instances!T12),"max", MAX(Instances!T12:Instances!T12),"diff", MAX(Instances!T12:Instances!T12)-MIN(Instances!T12:Instances!T12))</f>
+        <v>0</v>
+      </c>
+      <c r="U12" s="1" cm="1">
+        <f t="array" ref="U12">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!U12:Instances!U12),"median", MEDIAN(Instances!U12:Instances!U12),"min", MIN(Instances!U12:Instances!U12),"max", MAX(Instances!U12:Instances!U12),"diff", MAX(Instances!U12:Instances!U12)-MIN(Instances!U12:Instances!U12))</f>
+        <v>0</v>
+      </c>
       <c r="V12" s="1" cm="1">
         <f t="array" ref="V12">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!V12:Instances!V12),"median", MEDIAN(Instances!V12:Instances!V12),"min", MIN(Instances!V12:Instances!V12),"max", MAX(Instances!V12:Instances!V12),"diff", MAX(Instances!V12:Instances!V12)-MIN(Instances!V12:Instances!V12))</f>
         <v>0</v>
@@ -5057,11 +6824,23 @@
         <f t="array" ref="W12">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!W12:Instances!W12),"median", MEDIAN(Instances!W12:Instances!W12),"min", MIN(Instances!W12:Instances!W12),"max", MAX(Instances!W12:Instances!W12),"diff", MAX(Instances!W12:Instances!W12)-MIN(Instances!W12:Instances!W12))</f>
         <v>0</v>
       </c>
-      <c r="X12" s="1"/>
+      <c r="X12" s="1" cm="1">
+        <f t="array" ref="X12">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!X12:Instances!X12),"median", MEDIAN(Instances!X12:Instances!X12),"min", MIN(Instances!X12:Instances!X12),"max", MAX(Instances!X12:Instances!X12),"diff", MAX(Instances!X12:Instances!X12)-MIN(Instances!X12:Instances!X12))</f>
+        <v>0</v>
+      </c>
       <c r="Y12" s="1"/>
-      <c r="Z12" s="1"/>
-      <c r="AA12" s="1"/>
-      <c r="AB12" s="1"/>
+      <c r="Z12" s="1" cm="1">
+        <f t="array" ref="Z12">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!Z12:Instances!Z12),"median", MEDIAN(Instances!Z12:Instances!Z12),"min", MIN(Instances!Z12:Instances!Z12),"max", MAX(Instances!Z12:Instances!Z12),"diff", MAX(Instances!Z12:Instances!Z12)-MIN(Instances!Z12:Instances!Z12))</f>
+        <v>0</v>
+      </c>
+      <c r="AA12" s="1" cm="1">
+        <f t="array" ref="AA12">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AA12:Instances!AA12),"median", MEDIAN(Instances!AA12:Instances!AA12),"min", MIN(Instances!AA12:Instances!AA12),"max", MAX(Instances!AA12:Instances!AA12),"diff", MAX(Instances!AA12:Instances!AA12)-MIN(Instances!AA12:Instances!AA12))</f>
+        <v>0</v>
+      </c>
+      <c r="AB12" s="1" cm="1">
+        <f t="array" ref="AB12">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AB12:Instances!AB12),"median", MEDIAN(Instances!AB12:Instances!AB12),"min", MIN(Instances!AB12:Instances!AB12),"max", MAX(Instances!AB12:Instances!AB12),"diff", MAX(Instances!AB12:Instances!AB12)-MIN(Instances!AB12:Instances!AB12))</f>
+        <v>0</v>
+      </c>
       <c r="AC12" s="1" cm="1">
         <f t="array" ref="AC12">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AC12:Instances!AC12),"median", MEDIAN(Instances!AC12:Instances!AC12),"min", MIN(Instances!AC12:Instances!AC12),"max", MAX(Instances!AC12:Instances!AC12),"diff", MAX(Instances!AC12:Instances!AC12)-MIN(Instances!AC12:Instances!AC12))</f>
         <v>0</v>
@@ -5070,11 +6849,23 @@
         <f t="array" ref="AD12">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AD12:Instances!AD12),"median", MEDIAN(Instances!AD12:Instances!AD12),"min", MIN(Instances!AD12:Instances!AD12),"max", MAX(Instances!AD12:Instances!AD12),"diff", MAX(Instances!AD12:Instances!AD12)-MIN(Instances!AD12:Instances!AD12))</f>
         <v>0</v>
       </c>
-      <c r="AE12" s="1"/>
+      <c r="AE12" s="1" cm="1">
+        <f t="array" ref="AE12">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AE12:Instances!AE12),"median", MEDIAN(Instances!AE12:Instances!AE12),"min", MIN(Instances!AE12:Instances!AE12),"max", MAX(Instances!AE12:Instances!AE12),"diff", MAX(Instances!AE12:Instances!AE12)-MIN(Instances!AE12:Instances!AE12))</f>
+        <v>0</v>
+      </c>
       <c r="AF12" s="1"/>
-      <c r="AG12" s="1"/>
-      <c r="AH12" s="1"/>
-      <c r="AI12" s="1"/>
+      <c r="AG12" s="1" cm="1">
+        <f t="array" ref="AG12">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AG12:Instances!AG12),"median", MEDIAN(Instances!AG12:Instances!AG12),"min", MIN(Instances!AG12:Instances!AG12),"max", MAX(Instances!AG12:Instances!AG12),"diff", MAX(Instances!AG12:Instances!AG12)-MIN(Instances!AG12:Instances!AG12))</f>
+        <v>0</v>
+      </c>
+      <c r="AH12" s="1" cm="1">
+        <f t="array" ref="AH12">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AH12:Instances!AH12),"median", MEDIAN(Instances!AH12:Instances!AH12),"min", MIN(Instances!AH12:Instances!AH12),"max", MAX(Instances!AH12:Instances!AH12),"diff", MAX(Instances!AH12:Instances!AH12)-MIN(Instances!AH12:Instances!AH12))</f>
+        <v>0</v>
+      </c>
+      <c r="AI12" s="1" cm="1">
+        <f t="array" ref="AI12">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AI12:Instances!AI12),"median", MEDIAN(Instances!AI12:Instances!AI12),"min", MIN(Instances!AI12:Instances!AI12),"max", MAX(Instances!AI12:Instances!AI12),"diff", MAX(Instances!AI12:Instances!AI12)-MIN(Instances!AI12:Instances!AI12))</f>
+        <v>0</v>
+      </c>
       <c r="AJ12" s="1" cm="1">
         <f t="array" ref="AJ12">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AJ12:Instances!AJ12),"median", MEDIAN(Instances!AJ12:Instances!AJ12),"min", MIN(Instances!AJ12:Instances!AJ12),"max", MAX(Instances!AJ12:Instances!AJ12),"diff", MAX(Instances!AJ12:Instances!AJ12)-MIN(Instances!AJ12:Instances!AJ12))</f>
         <v>0</v>
@@ -5083,11 +6874,23 @@
         <f t="array" ref="AK12">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AK12:Instances!AK12),"median", MEDIAN(Instances!AK12:Instances!AK12),"min", MIN(Instances!AK12:Instances!AK12),"max", MAX(Instances!AK12:Instances!AK12),"diff", MAX(Instances!AK12:Instances!AK12)-MIN(Instances!AK12:Instances!AK12))</f>
         <v>0</v>
       </c>
-      <c r="AL12" s="1"/>
+      <c r="AL12" s="1" cm="1">
+        <f t="array" ref="AL12">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AL12:Instances!AL12),"median", MEDIAN(Instances!AL12:Instances!AL12),"min", MIN(Instances!AL12:Instances!AL12),"max", MAX(Instances!AL12:Instances!AL12),"diff", MAX(Instances!AL12:Instances!AL12)-MIN(Instances!AL12:Instances!AL12))</f>
+        <v>0</v>
+      </c>
       <c r="AM12" s="1"/>
-      <c r="AN12" s="1"/>
-      <c r="AO12" s="1"/>
-      <c r="AP12" s="1"/>
+      <c r="AN12" s="1" cm="1">
+        <f t="array" ref="AN12">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AN12:Instances!AN12),"median", MEDIAN(Instances!AN12:Instances!AN12),"min", MIN(Instances!AN12:Instances!AN12),"max", MAX(Instances!AN12:Instances!AN12),"diff", MAX(Instances!AN12:Instances!AN12)-MIN(Instances!AN12:Instances!AN12))</f>
+        <v>0</v>
+      </c>
+      <c r="AO12" s="1" cm="1">
+        <f t="array" ref="AO12">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AO12:Instances!AO12),"median", MEDIAN(Instances!AO12:Instances!AO12),"min", MIN(Instances!AO12:Instances!AO12),"max", MAX(Instances!AO12:Instances!AO12),"diff", MAX(Instances!AO12:Instances!AO12)-MIN(Instances!AO12:Instances!AO12))</f>
+        <v>0</v>
+      </c>
+      <c r="AP12" s="1" cm="1">
+        <f t="array" ref="AP12">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AP12:Instances!AP12),"median", MEDIAN(Instances!AP12:Instances!AP12),"min", MIN(Instances!AP12:Instances!AP12),"max", MAX(Instances!AP12:Instances!AP12),"diff", MAX(Instances!AP12:Instances!AP12)-MIN(Instances!AP12:Instances!AP12))</f>
+        <v>0</v>
+      </c>
       <c r="AQ12" s="1" cm="1">
         <f t="array" ref="AQ12">_xlfn.SWITCH($A$2,"average", AVERAGE(Instances!AQ12:Instances!AQ12),"median", MEDIAN(Instances!AQ12:Instances!AQ12),"min", MIN(Instances!AQ12:Instances!AQ12),"max", MAX(Instances!AQ12:Instances!AQ12),"diff", MAX(Instances!AQ12:Instances!AQ12)-MIN(Instances!AQ12:Instances!AQ12))</f>
         <v>0</v>
@@ -5096,10 +6899,22 @@
         <f>MIN($B12,$I12,$P12,$W12,$AD12,$AK12)</f>
         <v>0</v>
       </c>
-      <c r="AS12" s="1"/>
-      <c r="AT12" s="1"/>
-      <c r="AU12" s="1"/>
-      <c r="AV12" s="1"/>
+      <c r="AS12" s="1">
+        <f>MIN($C12,$J12,$Q12,$X12,$AE12,$AL12)</f>
+        <v>0</v>
+      </c>
+      <c r="AT12" s="1">
+        <f>MIN($E12,$L12,$S12,$Z12,$AG12,$AN12)</f>
+        <v>0</v>
+      </c>
+      <c r="AU12" s="1">
+        <f>MIN($F12,$M12,$T12,$AA12,$AH12,$AO12)</f>
+        <v>0</v>
+      </c>
+      <c r="AV12" s="1">
+        <f>MIN($G12,$N12,$U12,$AB12,$AI12,$AP12)</f>
+        <v>0</v>
+      </c>
       <c r="AW12" s="1">
         <f>MIN($H12,$O12,$V12,$AC12,$AJ12,$AQ12)</f>
         <v>0</v>
@@ -5108,10 +6923,22 @@
         <f>MEDIAN($B12,$I12,$P12,$W12,$AD12,$AK12)</f>
         <v>0</v>
       </c>
-      <c r="AY12" s="1"/>
-      <c r="AZ12" s="1"/>
-      <c r="BA12" s="1"/>
-      <c r="BB12" s="1"/>
+      <c r="AY12" s="1">
+        <f>MEDIAN($C12,$J12,$Q12,$X12,$AE12,$AL12)</f>
+        <v>0</v>
+      </c>
+      <c r="AZ12" s="1">
+        <f>MEDIAN($E12,$L12,$S12,$Z12,$AG12,$AN12)</f>
+        <v>0</v>
+      </c>
+      <c r="BA12" s="1">
+        <f>MEDIAN($F12,$M12,$T12,$AA12,$AH12,$AO12)</f>
+        <v>0</v>
+      </c>
+      <c r="BB12" s="1">
+        <f>MEDIAN($G12,$N12,$U12,$AB12,$AI12,$AP12)</f>
+        <v>0</v>
+      </c>
       <c r="BC12" s="1">
         <f>MEDIAN($H12,$O12,$V12,$AC12,$AJ12,$AQ12)</f>
         <v>0</v>
@@ -5120,10 +6947,22 @@
         <f>MAX($B12,$I12,$P12,$W12,$AD12,$AK12)</f>
         <v>0</v>
       </c>
-      <c r="BE12" s="1"/>
-      <c r="BF12" s="1"/>
-      <c r="BG12" s="1"/>
-      <c r="BH12" s="1"/>
+      <c r="BE12" s="1">
+        <f>MAX($C12,$J12,$Q12,$X12,$AE12,$AL12)</f>
+        <v>0</v>
+      </c>
+      <c r="BF12" s="1">
+        <f>MAX($E12,$L12,$S12,$Z12,$AG12,$AN12)</f>
+        <v>0</v>
+      </c>
+      <c r="BG12" s="1">
+        <f>MAX($F12,$M12,$T12,$AA12,$AH12,$AO12)</f>
+        <v>0</v>
+      </c>
+      <c r="BH12" s="1">
+        <f>MAX($G12,$N12,$U12,$AB12,$AI12,$AP12)</f>
+        <v>0</v>
+      </c>
       <c r="BI12" s="1">
         <f>MAX($H12,$O12,$V12,$AC12,$AJ12,$AQ12)</f>
         <v>0</v>
@@ -6768,7 +8607,7 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -6777,7 +8616,7 @@
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
       <c r="P1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
@@ -6786,7 +8625,7 @@
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
       <c r="W1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X1" s="1"/>
       <c r="Y1" s="1"/>
@@ -6795,7 +8634,7 @@
       <c r="AB1" s="1"/>
       <c r="AC1" s="1"/>
       <c r="AD1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AE1" s="1"/>
       <c r="AF1" s="1"/>
@@ -6804,7 +8643,7 @@
       <c r="AI1" s="1"/>
       <c r="AJ1" s="1"/>
       <c r="AK1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AL1" s="1"/>
       <c r="AM1" s="1"/>
@@ -6813,7 +8652,7 @@
       <c r="AP1" s="1"/>
       <c r="AQ1" s="1"/>
       <c r="AR1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AS1" s="1"/>
       <c r="AT1" s="1"/>
@@ -6821,7 +8660,7 @@
       <c r="AV1" s="1"/>
       <c r="AW1" s="1"/>
       <c r="AX1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AY1" s="1"/>
       <c r="AZ1" s="1"/>
@@ -6829,7 +8668,7 @@
       <c r="BB1" s="1"/>
       <c r="BC1" s="1"/>
       <c r="BD1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="BE1" s="1"/>
       <c r="BF1" s="1"/>
@@ -6849,16 +8688,16 @@
         <v>21</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>19</v>
@@ -6870,16 +8709,16 @@
         <v>21</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P2" s="1" t="s">
         <v>19</v>
@@ -6891,16 +8730,16 @@
         <v>21</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="W2" s="1" t="s">
         <v>19</v>
@@ -6912,16 +8751,16 @@
         <v>21</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA2" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AB2" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AC2" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AD2" s="1" t="s">
         <v>19</v>
@@ -6933,16 +8772,16 @@
         <v>21</v>
       </c>
       <c r="AG2" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AH2" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI2" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AJ2" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AK2" s="1" t="s">
         <v>19</v>
@@ -6954,16 +8793,16 @@
         <v>21</v>
       </c>
       <c r="AN2" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO2" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AP2" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ2" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AR2" s="1" t="s">
         <v>19</v>
@@ -6972,16 +8811,16 @@
         <v>20</v>
       </c>
       <c r="AT2" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AU2" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AV2" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AW2" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AX2" s="1" t="s">
         <v>19</v>
@@ -6990,16 +8829,16 @@
         <v>20</v>
       </c>
       <c r="AZ2" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BA2" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BB2" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BC2" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BD2" s="1" t="s">
         <v>19</v>
@@ -7008,21 +8847,21 @@
         <v>20</v>
       </c>
       <c r="BF2" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BG2" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BH2" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BI2" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:61">
       <c r="A3" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B3" s="1">
         <f>AVERAGE(Instances!B3:Instances!B12)</f>
